--- a/storage/app/templates/plantilla_cronograma_mantenimiento_equipos.xlsx
+++ b/storage/app/templates/plantilla_cronograma_mantenimiento_equipos.xlsx
@@ -1,65 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1iedoUhultPedVJGoc7E05Uo7Pv-COTdE\CALIDAD\PROCESO SISTEMAS CALIDAD 2026\2_Formatos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12286E65-7BB1-45A3-BBE4-D438F627CC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="CRONOGRAMA I SEMESTRE" sheetId="1" r:id="rId1"/>
+    <sheet name="CRONOGRAMA I SEMESTRE" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRONOGRAMA I SEMESTRE'!$A$8:$AC$103</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CeWvXf8s0jadxsGNCrD2Z+aWuyuc9Nvg5JJyadrydlc="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -122,6 +80,9 @@
     03 REALIZADO</t>
   </si>
   <si>
+    <t>FECHA DE ULTIMO MANTENIMIENTO 2024</t>
+  </si>
+  <si>
     <t>HOY</t>
   </si>
   <si>
@@ -137,113 +98,102 @@
     <t>EJECUCIÓN</t>
   </si>
   <si>
-    <t>ESTADO MANTENIMIENTO</t>
-  </si>
-  <si>
-    <t>MP26SSDQ</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>8i+7i''7h,5 ,ykhykkykhyo kh ty  ly,lh ,hl ,. ´plrhn</t>
-  </si>
-  <si>
-    <t>fr</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>FECHA DE ULTIMO MANTENIMIENTO 2024</t>
-  </si>
-  <si>
     <t>FECHA DE ULTIMO MANTENIMIENTO 2025 ll SEMESTRE</t>
   </si>
   <si>
     <t>FECHA DE ULTIMO MANTENIMIENTO 2026 I SEMESTRE</t>
   </si>
+  <si>
+    <t>ESTADO MANTENIMIENTO</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="21"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FF0F1111"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,12 +208,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -271,11 +215,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99CCFF"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -287,24 +231,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -312,30 +238,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -360,50 +262,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -417,19 +275,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -464,19 +309,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -526,196 +362,236 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="78">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="3" fillId="0" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="4" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="4" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="14" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -725,10 +601,11 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6AD05C"/>
-          <bgColor rgb="FF6AD05C"/>
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
       <fill>
@@ -737,25 +614,19 @@
           <bgColor rgb="FFA83330"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
+          <fgColor rgb="FF6AD05C"/>
+          <bgColor rgb="FF6AD05C"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -771,42 +642,38 @@
     <xdr:ext cx="1133475" cy="561975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.jpg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPr id="1" name="image1.jpg" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm rot="0"/>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -860,131 +727,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -995,32 +891,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:AC1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
-    <col min="2" max="2" width="4.25" customWidth="1"/>
-    <col min="3" max="3" width="24.625" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="6" width="39.875" customWidth="1"/>
-    <col min="7" max="7" width="41.375" customWidth="1"/>
-    <col min="8" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="25.5" customWidth="1"/>
-    <col min="10" max="10" width="18.375" customWidth="1"/>
-    <col min="11" max="11" width="18.75" customWidth="1"/>
-    <col min="12" max="12" width="44.125" customWidth="1"/>
-    <col min="13" max="13" width="16.375" customWidth="1"/>
-    <col min="14" max="14" width="31" customWidth="1"/>
-    <col min="15" max="15" width="18.25" customWidth="1"/>
-    <col min="16" max="17" width="11.125" customWidth="1"/>
-    <col min="18" max="18" width="16.25" customWidth="1"/>
-    <col min="19" max="19" width="17.125" customWidth="1"/>
-    <col min="20" max="23" width="22.75" customWidth="1"/>
-    <col min="24" max="26" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="2.125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="4.25" customWidth="true" style="0"/>
+    <col min="3" max="3" width="24.625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="19.75" customWidth="true" style="0"/>
+    <col min="5" max="5" width="39.875" customWidth="true" style="0"/>
+    <col min="6" max="6" width="39.875" customWidth="true" style="0"/>
+    <col min="7" max="7" width="41.375" customWidth="true" style="0"/>
+    <col min="8" max="8" width="26.75" customWidth="true" style="0"/>
+    <col min="9" max="9" width="25.5" customWidth="true" style="0"/>
+    <col min="10" max="10" width="18.375" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.75" customWidth="true" style="0"/>
+    <col min="12" max="12" width="44.125" customWidth="true" style="0"/>
+    <col min="13" max="13" width="16.375" customWidth="true" style="0"/>
+    <col min="14" max="14" width="31" customWidth="true" style="0"/>
+    <col min="15" max="15" width="18.25" customWidth="true" style="0"/>
+    <col min="16" max="16" width="11.125" customWidth="true" style="0"/>
+    <col min="17" max="17" width="11.125" customWidth="true" style="0"/>
+    <col min="18" max="18" width="16.25" customWidth="true" style="0"/>
+    <col min="19" max="19" width="17.125" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.75" customWidth="true" style="0"/>
+    <col min="21" max="21" width="22.75" customWidth="true" style="0"/>
+    <col min="22" max="22" width="22.75" customWidth="true" style="0"/>
+    <col min="23" max="23" width="22.75" customWidth="true" style="0"/>
+    <col min="24" max="24" width="10.75" customWidth="true" style="0"/>
+    <col min="25" max="25" width="10.75" customWidth="true" style="0"/>
+    <col min="26" max="26" width="10.75" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" customHeight="1" ht="6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +956,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" customHeight="1" ht="17.25">
       <c r="A2" s="4"/>
       <c r="B2" s="65"/>
       <c r="C2" s="66"/>
@@ -1082,7 +988,7 @@
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
-    <row r="3" spans="1:26" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" customHeight="1" ht="9">
       <c r="A3" s="4"/>
       <c r="B3" s="67"/>
       <c r="C3" s="68"/>
@@ -1112,7 +1018,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" customHeight="1" ht="21">
       <c r="A4" s="4"/>
       <c r="B4" s="67"/>
       <c r="C4" s="68"/>
@@ -1140,7 +1046,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" customHeight="1" ht="6">
       <c r="A5" s="4"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -1172,7 +1078,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" customHeight="1" ht="9.75">
       <c r="A6" s="4"/>
       <c r="B6" s="69"/>
       <c r="C6" s="70"/>
@@ -1200,7 +1106,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" customHeight="1" ht="4.5">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1228,7 +1134,7 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:26" ht="63.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" customHeight="1" ht="63.75">
       <c r="A8" s="4"/>
       <c r="B8" s="9" t="s">
         <v>6</v>
@@ -1270,36 +1176,36 @@
         <v>18</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S8" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U8" s="63" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="V8" s="64" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
     </row>
-    <row r="9" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" customHeight="1" ht="19.5">
       <c r="A9" s="4"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -1327,7 +1233,7 @@
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" customHeight="1" ht="19.5">
       <c r="A10" s="4"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -1355,7 +1261,7 @@
       <c r="Y10" s="21"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" customHeight="1" ht="19.5">
       <c r="A11" s="4"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -1383,7 +1289,7 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" customHeight="1" ht="19.5">
       <c r="A12" s="4"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1411,7 +1317,7 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" customHeight="1" ht="19.5">
       <c r="A13" s="4"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1439,7 +1345,7 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" customHeight="1" ht="19.5">
       <c r="A14" s="4"/>
       <c r="B14" s="14"/>
       <c r="C14" s="24"/>
@@ -1467,7 +1373,7 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" customHeight="1" ht="19.5">
       <c r="A15" s="29"/>
       <c r="B15" s="14"/>
       <c r="C15" s="15"/>
@@ -1495,7 +1401,7 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" customHeight="1" ht="19.5">
       <c r="A16" s="29"/>
       <c r="B16" s="14"/>
       <c r="C16" s="15"/>
@@ -1523,7 +1429,7 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" customHeight="1" ht="19.5">
       <c r="A17" s="30"/>
       <c r="B17" s="31"/>
       <c r="C17" s="22"/>
@@ -1554,7 +1460,7 @@
       <c r="AB17" s="36"/>
       <c r="AC17" s="36"/>
     </row>
-    <row r="18" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" customHeight="1" ht="19.5">
       <c r="A18" s="30"/>
       <c r="B18" s="31"/>
       <c r="C18" s="22"/>
@@ -1585,7 +1491,7 @@
       <c r="AB18" s="36"/>
       <c r="AC18" s="36"/>
     </row>
-    <row r="19" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" customHeight="1" ht="19.5">
       <c r="A19" s="30"/>
       <c r="B19" s="31"/>
       <c r="C19" s="22"/>
@@ -1616,7 +1522,7 @@
       <c r="AB19" s="36"/>
       <c r="AC19" s="36"/>
     </row>
-    <row r="20" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" customHeight="1" ht="19.5">
       <c r="A20" s="29"/>
       <c r="B20" s="14"/>
       <c r="C20" s="15"/>
@@ -1644,7 +1550,7 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" customHeight="1" ht="19.5">
       <c r="A21" s="29"/>
       <c r="B21" s="14"/>
       <c r="C21" s="15"/>
@@ -1672,7 +1578,7 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" customHeight="1" ht="19.5">
       <c r="A22" s="30"/>
       <c r="B22" s="31"/>
       <c r="C22" s="22"/>
@@ -1703,7 +1609,7 @@
       <c r="AB22" s="36"/>
       <c r="AC22" s="36"/>
     </row>
-    <row r="23" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" customHeight="1" ht="19.5">
       <c r="A23" s="29"/>
       <c r="B23" s="14"/>
       <c r="C23" s="15"/>
@@ -1731,7 +1637,7 @@
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" customHeight="1" ht="19.5">
       <c r="A24" s="29"/>
       <c r="B24" s="14"/>
       <c r="C24" s="15"/>
@@ -1759,7 +1665,7 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" customHeight="1" ht="19.5">
       <c r="A25" s="29"/>
       <c r="B25" s="14"/>
       <c r="C25" s="15"/>
@@ -1787,7 +1693,7 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" customHeight="1" ht="19.5">
       <c r="A26" s="29"/>
       <c r="B26" s="14"/>
       <c r="C26" s="15"/>
@@ -1815,7 +1721,7 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" customHeight="1" ht="19.5">
       <c r="A27" s="29"/>
       <c r="B27" s="14"/>
       <c r="C27" s="15"/>
@@ -1843,7 +1749,7 @@
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" customHeight="1" ht="19.5">
       <c r="A28" s="29"/>
       <c r="B28" s="14"/>
       <c r="C28" s="15"/>
@@ -1871,7 +1777,7 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" customHeight="1" ht="19.5">
       <c r="A29" s="30"/>
       <c r="B29" s="31"/>
       <c r="C29" s="22"/>
@@ -1902,7 +1808,7 @@
       <c r="AB29" s="36"/>
       <c r="AC29" s="36"/>
     </row>
-    <row r="30" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" customHeight="1" ht="19.5">
       <c r="A30" s="29"/>
       <c r="B30" s="14"/>
       <c r="C30" s="15"/>
@@ -1930,7 +1836,7 @@
       <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
-    <row r="31" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" customHeight="1" ht="19.5">
       <c r="A31" s="29"/>
       <c r="B31" s="14"/>
       <c r="C31" s="15"/>
@@ -1958,7 +1864,7 @@
       <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
-    <row r="32" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" customHeight="1" ht="19.5">
       <c r="A32" s="4"/>
       <c r="B32" s="14"/>
       <c r="C32" s="37"/>
@@ -1986,7 +1892,7 @@
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" customHeight="1" ht="19.5">
       <c r="A33" s="4"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2014,7 +1920,7 @@
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" customHeight="1" ht="19.5">
       <c r="A34" s="4"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -2042,7 +1948,7 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" customHeight="1" ht="19.5">
       <c r="A35" s="4"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2070,7 +1976,7 @@
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
-    <row r="36" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" customHeight="1" ht="19.5">
       <c r="A36" s="4"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -2098,7 +2004,7 @@
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
-    <row r="37" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" customHeight="1" ht="19.5">
       <c r="A37" s="4"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -2126,7 +2032,7 @@
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
-    <row r="38" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" customHeight="1" ht="19.5">
       <c r="A38" s="4"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -2154,7 +2060,7 @@
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
-    <row r="39" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" customHeight="1" ht="19.5">
       <c r="A39" s="4"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -2182,7 +2088,7 @@
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
     </row>
-    <row r="40" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" customHeight="1" ht="19.5">
       <c r="A40" s="4"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -2210,7 +2116,7 @@
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" customHeight="1" ht="19.5">
       <c r="A41" s="4"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -2238,7 +2144,7 @@
       <c r="Y41" s="4"/>
       <c r="Z41" s="4"/>
     </row>
-    <row r="42" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" customHeight="1" ht="19.5">
       <c r="A42" s="4"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -2266,7 +2172,7 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" customHeight="1" ht="19.5">
       <c r="A43" s="4"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2294,7 +2200,7 @@
       <c r="Y43" s="4"/>
       <c r="Z43" s="4"/>
     </row>
-    <row r="44" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" customHeight="1" ht="19.5">
       <c r="A44" s="4"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2322,7 +2228,7 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" customHeight="1" ht="19.5">
       <c r="A45" s="4"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2350,7 +2256,7 @@
       <c r="Y45" s="4"/>
       <c r="Z45" s="4"/>
     </row>
-    <row r="46" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" customHeight="1" ht="19.5">
       <c r="A46" s="4"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2378,7 +2284,7 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" customHeight="1" ht="19.5">
       <c r="A47" s="4"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2406,7 +2312,7 @@
       <c r="Y47" s="4"/>
       <c r="Z47" s="4"/>
     </row>
-    <row r="48" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" customHeight="1" ht="19.5">
       <c r="A48" s="4"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2434,7 +2340,7 @@
       <c r="Y48" s="4"/>
       <c r="Z48" s="4"/>
     </row>
-    <row r="49" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" customHeight="1" ht="19.5">
       <c r="A49" s="4"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2462,7 +2368,7 @@
       <c r="Y49" s="35"/>
       <c r="Z49" s="4"/>
     </row>
-    <row r="50" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" customHeight="1" ht="19.5">
       <c r="A50" s="4"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2490,7 +2396,7 @@
       <c r="Y50" s="4"/>
       <c r="Z50" s="4"/>
     </row>
-    <row r="51" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" customHeight="1" ht="19.5">
       <c r="A51" s="4"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2518,7 +2424,7 @@
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
     </row>
-    <row r="52" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" customHeight="1" ht="19.5">
       <c r="A52" s="4">
         <v>0</v>
       </c>
@@ -2548,7 +2454,7 @@
       <c r="Y52" s="4"/>
       <c r="Z52" s="4"/>
     </row>
-    <row r="53" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" customHeight="1" ht="19.5">
       <c r="A53" s="4"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2576,7 +2482,7 @@
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
     </row>
-    <row r="54" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" customHeight="1" ht="19.5">
       <c r="A54" s="4"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2604,7 +2510,7 @@
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
     </row>
-    <row r="55" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" customHeight="1" ht="19.5">
       <c r="A55" s="4"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2632,7 +2538,7 @@
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
     </row>
-    <row r="56" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" customHeight="1" ht="19.5">
       <c r="A56" s="4"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2660,7 +2566,7 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" customHeight="1" ht="19.5">
       <c r="A57" s="4"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2688,7 +2594,7 @@
       <c r="Y57" s="4"/>
       <c r="Z57" s="4"/>
     </row>
-    <row r="58" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" customHeight="1" ht="19.5">
       <c r="A58" s="4"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2716,7 +2622,7 @@
       <c r="Y58" s="4"/>
       <c r="Z58" s="4"/>
     </row>
-    <row r="59" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" customHeight="1" ht="19.5">
       <c r="A59" s="4"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2744,7 +2650,7 @@
       <c r="Y59" s="4"/>
       <c r="Z59" s="4"/>
     </row>
-    <row r="60" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" customHeight="1" ht="19.5">
       <c r="A60" s="4"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2772,7 +2678,7 @@
       <c r="Y60" s="4"/>
       <c r="Z60" s="4"/>
     </row>
-    <row r="61" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" customHeight="1" ht="19.5">
       <c r="A61" s="4"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2800,7 +2706,7 @@
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
     </row>
-    <row r="62" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" customHeight="1" ht="19.5">
       <c r="A62" s="4"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2828,7 +2734,7 @@
       <c r="Y62" s="4"/>
       <c r="Z62" s="4"/>
     </row>
-    <row r="63" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" customHeight="1" ht="19.5">
       <c r="A63" s="4"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2856,7 +2762,7 @@
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
     </row>
-    <row r="64" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" customHeight="1" ht="19.5">
       <c r="A64" s="4"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2884,7 +2790,7 @@
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
     </row>
-    <row r="65" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" customHeight="1" ht="19.5">
       <c r="A65" s="4"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2912,7 +2818,7 @@
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
     </row>
-    <row r="66" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:29" customHeight="1" ht="19.5">
       <c r="A66" s="4"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2940,7 +2846,7 @@
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
     </row>
-    <row r="67" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" customHeight="1" ht="19.5">
       <c r="A67" s="4"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2968,7 +2874,7 @@
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
     </row>
-    <row r="68" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" customHeight="1" ht="19.5">
       <c r="A68" s="4"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2996,7 +2902,7 @@
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" customHeight="1" ht="19.5">
       <c r="A69" s="4"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -3024,7 +2930,7 @@
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" customHeight="1" ht="19.5">
       <c r="A70" s="4"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -3052,7 +2958,7 @@
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" customHeight="1" ht="19.5">
       <c r="A71" s="4"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3077,7 +2983,7 @@
       <c r="V71" s="20"/>
       <c r="W71" s="17"/>
     </row>
-    <row r="72" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" customHeight="1" ht="19.5">
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="15"/>
@@ -3101,7 +3007,7 @@
       <c r="V72" s="20"/>
       <c r="W72" s="17"/>
     </row>
-    <row r="73" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" customHeight="1" ht="19.5">
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="15"/>
@@ -3125,7 +3031,7 @@
       <c r="V73" s="20"/>
       <c r="W73" s="17"/>
     </row>
-    <row r="74" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" customHeight="1" ht="19.5">
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="15"/>
@@ -3149,7 +3055,7 @@
       <c r="V74" s="20"/>
       <c r="W74" s="17"/>
     </row>
-    <row r="75" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" customHeight="1" ht="19.5">
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="15"/>
@@ -3173,7 +3079,7 @@
       <c r="V75" s="20"/>
       <c r="W75" s="17"/>
     </row>
-    <row r="76" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" customHeight="1" ht="19.5">
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="15"/>
@@ -3199,7 +3105,7 @@
       <c r="X76" s="49"/>
       <c r="Y76" s="49"/>
     </row>
-    <row r="77" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" customHeight="1" ht="19.5">
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="15"/>
@@ -3223,7 +3129,7 @@
       <c r="V77" s="20"/>
       <c r="W77" s="17"/>
     </row>
-    <row r="78" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" customHeight="1" ht="19.5">
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="15"/>
@@ -3247,7 +3153,7 @@
       <c r="V78" s="20"/>
       <c r="W78" s="17"/>
     </row>
-    <row r="79" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" customHeight="1" ht="19.5">
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="15"/>
@@ -3271,7 +3177,7 @@
       <c r="V79" s="20"/>
       <c r="W79" s="17"/>
     </row>
-    <row r="80" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" customHeight="1" ht="19.5">
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="15"/>
@@ -3295,7 +3201,7 @@
       <c r="V80" s="20"/>
       <c r="W80" s="17"/>
     </row>
-    <row r="81" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" customHeight="1" ht="19.5">
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="15"/>
@@ -3319,7 +3225,7 @@
       <c r="V81" s="20"/>
       <c r="W81" s="17"/>
     </row>
-    <row r="82" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" customHeight="1" ht="19.5">
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="15"/>
@@ -3343,7 +3249,7 @@
       <c r="V82" s="20"/>
       <c r="W82" s="17"/>
     </row>
-    <row r="83" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" customHeight="1" ht="19.5">
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="15"/>
@@ -3367,7 +3273,7 @@
       <c r="V83" s="20"/>
       <c r="W83" s="17"/>
     </row>
-    <row r="84" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" customHeight="1" ht="19.5">
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="15"/>
@@ -3391,7 +3297,7 @@
       <c r="V84" s="20"/>
       <c r="W84" s="17"/>
     </row>
-    <row r="85" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" customHeight="1" ht="19.5">
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="15"/>
@@ -3415,7 +3321,7 @@
       <c r="V85" s="20"/>
       <c r="W85" s="17"/>
     </row>
-    <row r="86" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" customHeight="1" ht="19.5">
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="15"/>
@@ -3439,7 +3345,7 @@
       <c r="V86" s="20"/>
       <c r="W86" s="17"/>
     </row>
-    <row r="87" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" customHeight="1" ht="19.5">
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="15"/>
@@ -3463,7 +3369,7 @@
       <c r="V87" s="20"/>
       <c r="W87" s="17"/>
     </row>
-    <row r="88" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" customHeight="1" ht="19.5">
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="15"/>
@@ -3487,7 +3393,7 @@
       <c r="V88" s="20"/>
       <c r="W88" s="17"/>
     </row>
-    <row r="89" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" customHeight="1" ht="19.5">
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="15"/>
@@ -3511,7 +3417,7 @@
       <c r="V89" s="20"/>
       <c r="W89" s="17"/>
     </row>
-    <row r="90" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" customHeight="1" ht="19.5">
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="15"/>
@@ -3535,7 +3441,7 @@
       <c r="V90" s="20"/>
       <c r="W90" s="17"/>
     </row>
-    <row r="91" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" customHeight="1" ht="19.5">
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="15"/>
@@ -3559,7 +3465,7 @@
       <c r="V91" s="20"/>
       <c r="W91" s="17"/>
     </row>
-    <row r="92" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" customHeight="1" ht="19.5">
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="15"/>
@@ -3583,7 +3489,7 @@
       <c r="V92" s="20"/>
       <c r="W92" s="17"/>
     </row>
-    <row r="93" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" customHeight="1" ht="19.5">
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="15"/>
@@ -3607,7 +3513,7 @@
       <c r="V93" s="20"/>
       <c r="W93" s="17"/>
     </row>
-    <row r="94" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" customHeight="1" ht="19.5">
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
       <c r="D94" s="15"/>
@@ -3631,7 +3537,7 @@
       <c r="V94" s="20"/>
       <c r="W94" s="17"/>
     </row>
-    <row r="95" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" customHeight="1" ht="19.5">
       <c r="B95" s="51"/>
       <c r="C95" s="15"/>
       <c r="D95" s="15"/>
@@ -3655,7 +3561,7 @@
       <c r="V95" s="20"/>
       <c r="W95" s="17"/>
     </row>
-    <row r="96" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" customHeight="1" ht="19.5">
       <c r="B96" s="51"/>
       <c r="C96" s="15"/>
       <c r="D96" s="15"/>
@@ -3679,7 +3585,7 @@
       <c r="V96" s="20"/>
       <c r="W96" s="17"/>
     </row>
-    <row r="97" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" customHeight="1" ht="19.5">
       <c r="B97" s="51"/>
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
@@ -3703,7 +3609,7 @@
       <c r="V97" s="20"/>
       <c r="W97" s="17"/>
     </row>
-    <row r="98" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" customHeight="1" ht="19.5">
       <c r="B98" s="51"/>
       <c r="C98" s="15"/>
       <c r="D98" s="15"/>
@@ -3727,7 +3633,7 @@
       <c r="V98" s="20"/>
       <c r="W98" s="17"/>
     </row>
-    <row r="99" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" customHeight="1" ht="19.5">
       <c r="B99" s="55"/>
       <c r="C99" s="14"/>
       <c r="D99" s="15"/>
@@ -3751,7 +3657,7 @@
       <c r="V99" s="20"/>
       <c r="W99" s="17"/>
     </row>
-    <row r="100" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" customHeight="1" ht="19.5">
       <c r="B100" s="51"/>
       <c r="C100" s="51"/>
       <c r="D100" s="51"/>
@@ -3775,9 +3681,9 @@
       <c r="V100" s="20"/>
       <c r="W100" s="17"/>
     </row>
-    <row r="101" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" customHeight="1" ht="19.5">
       <c r="A101" s="49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B101" s="51"/>
       <c r="C101" s="15"/>
@@ -3802,9 +3708,9 @@
       <c r="V101" s="20"/>
       <c r="W101" s="17"/>
     </row>
-    <row r="102" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" customHeight="1" ht="19.5">
       <c r="A102" s="49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B102" s="51"/>
       <c r="C102" s="15"/>
@@ -3829,9 +3735,9 @@
       <c r="V102" s="20"/>
       <c r="W102" s="17"/>
     </row>
-    <row r="103" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:29" customHeight="1" ht="19.5">
       <c r="A103" s="49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B103" s="51"/>
       <c r="C103" s="15"/>
@@ -3856,7 +3762,7 @@
       <c r="V103" s="20"/>
       <c r="W103" s="17"/>
     </row>
-    <row r="104" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:29" customHeight="1" ht="15.75">
       <c r="B104" s="57"/>
       <c r="C104" s="57"/>
       <c r="D104" s="57"/>
@@ -3880,7 +3786,7 @@
       <c r="V104" s="60"/>
       <c r="W104" s="57"/>
     </row>
-    <row r="105" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:29" customHeight="1" ht="15.75">
       <c r="B105" s="57"/>
       <c r="C105" s="57"/>
       <c r="D105" s="57"/>
@@ -3904,7 +3810,7 @@
       <c r="V105" s="60"/>
       <c r="W105" s="57"/>
     </row>
-    <row r="106" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:29" customHeight="1" ht="15.75">
       <c r="B106" s="57"/>
       <c r="C106" s="57"/>
       <c r="D106" s="57"/>
@@ -3928,7 +3834,7 @@
       <c r="V106" s="60"/>
       <c r="W106" s="57"/>
     </row>
-    <row r="107" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:29" customHeight="1" ht="15.75">
       <c r="B107" s="57"/>
       <c r="C107" s="57"/>
       <c r="D107" s="57"/>
@@ -3952,7 +3858,7 @@
       <c r="V107" s="60"/>
       <c r="W107" s="57"/>
     </row>
-    <row r="108" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:29" customHeight="1" ht="15.75">
       <c r="B108" s="57"/>
       <c r="C108" s="57"/>
       <c r="D108" s="57"/>
@@ -3976,13 +3882,11 @@
       <c r="V108" s="60"/>
       <c r="W108" s="57"/>
     </row>
-    <row r="109" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:29" customHeight="1" ht="15.75">
       <c r="B109" s="57"/>
       <c r="C109" s="57"/>
       <c r="D109" s="57"/>
-      <c r="E109" s="57">
-        <v>93</v>
-      </c>
+      <c r="E109" s="57"/>
       <c r="F109" s="57"/>
       <c r="G109" s="57"/>
       <c r="H109" s="57"/>
@@ -4002,13 +3906,11 @@
       <c r="V109" s="60"/>
       <c r="W109" s="57"/>
     </row>
-    <row r="110" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:29" customHeight="1" ht="15.75">
       <c r="B110" s="57"/>
       <c r="C110" s="57"/>
       <c r="D110" s="57"/>
-      <c r="E110" s="57">
-        <v>86</v>
-      </c>
+      <c r="E110" s="57"/>
       <c r="F110" s="57"/>
       <c r="G110" s="57"/>
       <c r="H110" s="57"/>
@@ -4028,14 +3930,11 @@
       <c r="V110" s="60"/>
       <c r="W110" s="57"/>
     </row>
-    <row r="111" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:29" customHeight="1" ht="15.75">
       <c r="B111" s="57"/>
       <c r="C111" s="57"/>
       <c r="D111" s="57"/>
-      <c r="E111" s="57">
-        <f>E109-E110</f>
-        <v>7</v>
-      </c>
+      <c r="E111" s="57"/>
       <c r="F111" s="57"/>
       <c r="G111" s="57"/>
       <c r="H111" s="57"/>
@@ -4055,7 +3954,7 @@
       <c r="V111" s="60"/>
       <c r="W111" s="57"/>
     </row>
-    <row r="112" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:29" customHeight="1" ht="15.75">
       <c r="B112" s="57"/>
       <c r="C112" s="57"/>
       <c r="D112" s="57"/>
@@ -4079,7 +3978,7 @@
       <c r="V112" s="60"/>
       <c r="W112" s="57"/>
     </row>
-    <row r="113" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:29" customHeight="1" ht="15.75">
       <c r="B113" s="57"/>
       <c r="C113" s="57"/>
       <c r="D113" s="57"/>
@@ -4103,7 +4002,7 @@
       <c r="V113" s="60"/>
       <c r="W113" s="57"/>
     </row>
-    <row r="114" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:29" customHeight="1" ht="15.75">
       <c r="B114" s="57"/>
       <c r="C114" s="57"/>
       <c r="D114" s="57"/>
@@ -4127,7 +4026,7 @@
       <c r="V114" s="60"/>
       <c r="W114" s="57"/>
     </row>
-    <row r="115" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:29" customHeight="1" ht="15.75">
       <c r="B115" s="57"/>
       <c r="C115" s="57"/>
       <c r="D115" s="57"/>
@@ -4151,7 +4050,7 @@
       <c r="V115" s="60"/>
       <c r="W115" s="57"/>
     </row>
-    <row r="116" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:29" customHeight="1" ht="15.75">
       <c r="B116" s="57"/>
       <c r="C116" s="57"/>
       <c r="D116" s="57"/>
@@ -4175,7 +4074,7 @@
       <c r="V116" s="60"/>
       <c r="W116" s="57"/>
     </row>
-    <row r="117" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:29" customHeight="1" ht="15.75">
       <c r="B117" s="57"/>
       <c r="C117" s="57"/>
       <c r="D117" s="57"/>
@@ -4199,7 +4098,7 @@
       <c r="V117" s="60"/>
       <c r="W117" s="57"/>
     </row>
-    <row r="118" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:29" customHeight="1" ht="15.75">
       <c r="B118" s="57"/>
       <c r="C118" s="57"/>
       <c r="D118" s="57"/>
@@ -4210,9 +4109,7 @@
       <c r="I118" s="57"/>
       <c r="J118" s="57"/>
       <c r="K118" s="57"/>
-      <c r="L118" s="57" t="s">
-        <v>25</v>
-      </c>
+      <c r="L118" s="57"/>
       <c r="M118" s="57"/>
       <c r="N118" s="58"/>
       <c r="O118" s="59"/>
@@ -4225,7 +4122,7 @@
       <c r="V118" s="60"/>
       <c r="W118" s="57"/>
     </row>
-    <row r="119" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:29" customHeight="1" ht="15.75">
       <c r="B119" s="57"/>
       <c r="C119" s="57"/>
       <c r="D119" s="57"/>
@@ -4249,7 +4146,7 @@
       <c r="V119" s="60"/>
       <c r="W119" s="57"/>
     </row>
-    <row r="120" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:29" customHeight="1" ht="15.75">
       <c r="B120" s="57"/>
       <c r="C120" s="57"/>
       <c r="D120" s="57"/>
@@ -4273,7 +4170,7 @@
       <c r="V120" s="60"/>
       <c r="W120" s="57"/>
     </row>
-    <row r="121" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:29" customHeight="1" ht="15.75">
       <c r="B121" s="57"/>
       <c r="C121" s="57"/>
       <c r="D121" s="57"/>
@@ -4297,7 +4194,7 @@
       <c r="V121" s="60"/>
       <c r="W121" s="57"/>
     </row>
-    <row r="122" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:29" customHeight="1" ht="15.75">
       <c r="B122" s="57"/>
       <c r="C122" s="57"/>
       <c r="D122" s="57"/>
@@ -4321,14 +4218,12 @@
       <c r="V122" s="60"/>
       <c r="W122" s="57"/>
     </row>
-    <row r="123" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:29" customHeight="1" ht="15.75">
       <c r="B123" s="57"/>
       <c r="C123" s="57"/>
       <c r="D123" s="57"/>
       <c r="E123" s="57"/>
-      <c r="F123" s="57" t="s">
-        <v>27</v>
-      </c>
+      <c r="F123" s="57"/>
       <c r="G123" s="57"/>
       <c r="H123" s="57"/>
       <c r="I123" s="57"/>
@@ -4347,15 +4242,12 @@
       <c r="V123" s="60"/>
       <c r="W123" s="57"/>
     </row>
-    <row r="124" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:29" customHeight="1" ht="15.75">
       <c r="B124" s="57"/>
       <c r="C124" s="57"/>
       <c r="D124" s="57"/>
       <c r="E124" s="57"/>
-      <c r="F124" s="57" t="e" cm="1">
-        <f t="array" ref="F124">-jtuñ h75yu gt thvghcvft´¿</f>
-        <v>#NAME?</v>
-      </c>
+      <c r="F124" s="57"/>
       <c r="G124" s="57"/>
       <c r="H124" s="57"/>
       <c r="I124" s="57"/>
@@ -4374,7 +4266,7 @@
       <c r="V124" s="60"/>
       <c r="W124" s="57"/>
     </row>
-    <row r="125" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:29" customHeight="1" ht="15.75">
       <c r="B125" s="57"/>
       <c r="C125" s="57"/>
       <c r="D125" s="57"/>
@@ -4398,14 +4290,12 @@
       <c r="V125" s="60"/>
       <c r="W125" s="57"/>
     </row>
-    <row r="126" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:29" customHeight="1" ht="15.75">
       <c r="B126" s="57"/>
       <c r="C126" s="57"/>
       <c r="D126" s="57"/>
       <c r="E126" s="57"/>
-      <c r="F126" s="57" t="s">
-        <v>29</v>
-      </c>
+      <c r="F126" s="57"/>
       <c r="G126" s="57"/>
       <c r="H126" s="57"/>
       <c r="I126" s="57"/>
@@ -4424,14 +4314,12 @@
       <c r="V126" s="60"/>
       <c r="W126" s="57"/>
     </row>
-    <row r="127" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:29" customHeight="1" ht="15.75">
       <c r="B127" s="57"/>
       <c r="C127" s="57"/>
       <c r="D127" s="57"/>
       <c r="E127" s="57"/>
-      <c r="F127" s="57" t="s">
-        <v>28</v>
-      </c>
+      <c r="F127" s="57"/>
       <c r="G127" s="57"/>
       <c r="H127" s="57"/>
       <c r="I127" s="57"/>
@@ -4450,7 +4338,7 @@
       <c r="V127" s="60"/>
       <c r="W127" s="57"/>
     </row>
-    <row r="128" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:29" customHeight="1" ht="15.75">
       <c r="B128" s="57"/>
       <c r="C128" s="57"/>
       <c r="D128" s="57"/>
@@ -4474,7 +4362,7 @@
       <c r="V128" s="60"/>
       <c r="W128" s="57"/>
     </row>
-    <row r="129" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:29" customHeight="1" ht="15.75">
       <c r="B129" s="57"/>
       <c r="C129" s="57"/>
       <c r="D129" s="57"/>
@@ -4498,7 +4386,7 @@
       <c r="V129" s="60"/>
       <c r="W129" s="57"/>
     </row>
-    <row r="130" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:29" customHeight="1" ht="15.75">
       <c r="B130" s="57"/>
       <c r="C130" s="57"/>
       <c r="D130" s="57"/>
@@ -4522,7 +4410,7 @@
       <c r="V130" s="60"/>
       <c r="W130" s="57"/>
     </row>
-    <row r="131" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:29" customHeight="1" ht="15.75">
       <c r="B131" s="57"/>
       <c r="C131" s="57"/>
       <c r="D131" s="57"/>
@@ -4546,7 +4434,7 @@
       <c r="V131" s="60"/>
       <c r="W131" s="57"/>
     </row>
-    <row r="132" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:29" customHeight="1" ht="15.75">
       <c r="B132" s="57"/>
       <c r="C132" s="57"/>
       <c r="D132" s="57"/>
@@ -4570,7 +4458,7 @@
       <c r="V132" s="60"/>
       <c r="W132" s="57"/>
     </row>
-    <row r="133" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:29" customHeight="1" ht="15.75">
       <c r="B133" s="57"/>
       <c r="C133" s="57"/>
       <c r="D133" s="57"/>
@@ -4594,7 +4482,7 @@
       <c r="V133" s="60"/>
       <c r="W133" s="57"/>
     </row>
-    <row r="134" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:29" customHeight="1" ht="15.75">
       <c r="B134" s="57"/>
       <c r="C134" s="57"/>
       <c r="D134" s="57"/>
@@ -4618,7 +4506,7 @@
       <c r="V134" s="60"/>
       <c r="W134" s="57"/>
     </row>
-    <row r="135" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:29" customHeight="1" ht="15.75">
       <c r="B135" s="57"/>
       <c r="C135" s="57"/>
       <c r="D135" s="57"/>
@@ -4642,7 +4530,7 @@
       <c r="V135" s="60"/>
       <c r="W135" s="57"/>
     </row>
-    <row r="136" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:29" customHeight="1" ht="15.75">
       <c r="B136" s="57"/>
       <c r="C136" s="57"/>
       <c r="D136" s="57"/>
@@ -4666,7 +4554,7 @@
       <c r="V136" s="60"/>
       <c r="W136" s="57"/>
     </row>
-    <row r="137" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:29" customHeight="1" ht="15.75">
       <c r="B137" s="57"/>
       <c r="C137" s="57"/>
       <c r="D137" s="57"/>
@@ -4690,7 +4578,7 @@
       <c r="V137" s="60"/>
       <c r="W137" s="57"/>
     </row>
-    <row r="138" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:29" customHeight="1" ht="15.75">
       <c r="B138" s="57"/>
       <c r="C138" s="57"/>
       <c r="D138" s="57"/>
@@ -4714,7 +4602,7 @@
       <c r="V138" s="60"/>
       <c r="W138" s="57"/>
     </row>
-    <row r="139" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:29" customHeight="1" ht="15.75">
       <c r="B139" s="57"/>
       <c r="C139" s="57"/>
       <c r="D139" s="57"/>
@@ -4738,7 +4626,7 @@
       <c r="V139" s="60"/>
       <c r="W139" s="57"/>
     </row>
-    <row r="140" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:29" customHeight="1" ht="15.75">
       <c r="B140" s="57"/>
       <c r="C140" s="57"/>
       <c r="D140" s="57"/>
@@ -4762,7 +4650,7 @@
       <c r="V140" s="60"/>
       <c r="W140" s="57"/>
     </row>
-    <row r="141" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:29" customHeight="1" ht="15.75">
       <c r="B141" s="57"/>
       <c r="C141" s="57"/>
       <c r="D141" s="57"/>
@@ -4786,7 +4674,7 @@
       <c r="V141" s="60"/>
       <c r="W141" s="57"/>
     </row>
-    <row r="142" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:29" customHeight="1" ht="15.75">
       <c r="B142" s="57"/>
       <c r="C142" s="57"/>
       <c r="D142" s="57"/>
@@ -4810,7 +4698,7 @@
       <c r="V142" s="60"/>
       <c r="W142" s="57"/>
     </row>
-    <row r="143" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:29" customHeight="1" ht="15.75">
       <c r="B143" s="57"/>
       <c r="C143" s="57"/>
       <c r="D143" s="57"/>
@@ -4834,7 +4722,7 @@
       <c r="V143" s="60"/>
       <c r="W143" s="57"/>
     </row>
-    <row r="144" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:29" customHeight="1" ht="15.75">
       <c r="B144" s="57"/>
       <c r="C144" s="57"/>
       <c r="D144" s="57"/>
@@ -4858,7 +4746,7 @@
       <c r="V144" s="60"/>
       <c r="W144" s="57"/>
     </row>
-    <row r="145" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:29" customHeight="1" ht="15.75">
       <c r="B145" s="57"/>
       <c r="C145" s="57"/>
       <c r="D145" s="57"/>
@@ -4882,7 +4770,7 @@
       <c r="V145" s="60"/>
       <c r="W145" s="57"/>
     </row>
-    <row r="146" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:29" customHeight="1" ht="15.75">
       <c r="B146" s="57"/>
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
@@ -4906,7 +4794,7 @@
       <c r="V146" s="60"/>
       <c r="W146" s="57"/>
     </row>
-    <row r="147" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:29" customHeight="1" ht="15.75">
       <c r="B147" s="57"/>
       <c r="C147" s="57"/>
       <c r="D147" s="57"/>
@@ -4930,7 +4818,7 @@
       <c r="V147" s="60"/>
       <c r="W147" s="57"/>
     </row>
-    <row r="148" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:29" customHeight="1" ht="15.75">
       <c r="B148" s="57"/>
       <c r="C148" s="57"/>
       <c r="D148" s="57"/>
@@ -4954,7 +4842,7 @@
       <c r="V148" s="60"/>
       <c r="W148" s="57"/>
     </row>
-    <row r="149" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:29" customHeight="1" ht="15.75">
       <c r="B149" s="57"/>
       <c r="C149" s="57"/>
       <c r="D149" s="57"/>
@@ -4978,7 +4866,7 @@
       <c r="V149" s="60"/>
       <c r="W149" s="57"/>
     </row>
-    <row r="150" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:29" customHeight="1" ht="15.75">
       <c r="B150" s="57"/>
       <c r="C150" s="57"/>
       <c r="D150" s="57"/>
@@ -5002,7 +4890,7 @@
       <c r="V150" s="60"/>
       <c r="W150" s="57"/>
     </row>
-    <row r="151" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:29" customHeight="1" ht="15.75">
       <c r="B151" s="57"/>
       <c r="C151" s="57"/>
       <c r="D151" s="57"/>
@@ -5026,14 +4914,12 @@
       <c r="V151" s="60"/>
       <c r="W151" s="57"/>
     </row>
-    <row r="152" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:29" customHeight="1" ht="15.75">
       <c r="B152" s="57"/>
       <c r="C152" s="57"/>
       <c r="D152" s="57"/>
       <c r="E152" s="57"/>
-      <c r="F152" s="57" t="s">
-        <v>0</v>
-      </c>
+      <c r="F152" s="57"/>
       <c r="G152" s="57"/>
       <c r="H152" s="57"/>
       <c r="I152" s="57"/>
@@ -5052,7 +4938,7 @@
       <c r="V152" s="60"/>
       <c r="W152" s="57"/>
     </row>
-    <row r="153" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:29" customHeight="1" ht="15.75">
       <c r="B153" s="57"/>
       <c r="C153" s="57"/>
       <c r="D153" s="57"/>
@@ -5076,7 +4962,7 @@
       <c r="V153" s="60"/>
       <c r="W153" s="57"/>
     </row>
-    <row r="154" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:29" customHeight="1" ht="15.75">
       <c r="B154" s="57"/>
       <c r="C154" s="57"/>
       <c r="D154" s="57"/>
@@ -5100,7 +4986,7 @@
       <c r="V154" s="60"/>
       <c r="W154" s="57"/>
     </row>
-    <row r="155" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:29" customHeight="1" ht="15.75">
       <c r="B155" s="57"/>
       <c r="C155" s="57"/>
       <c r="D155" s="57"/>
@@ -5124,7 +5010,7 @@
       <c r="V155" s="60"/>
       <c r="W155" s="57"/>
     </row>
-    <row r="156" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:29" customHeight="1" ht="15.75">
       <c r="B156" s="57"/>
       <c r="C156" s="57"/>
       <c r="D156" s="57"/>
@@ -5148,7 +5034,7 @@
       <c r="V156" s="60"/>
       <c r="W156" s="57"/>
     </row>
-    <row r="157" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:29" customHeight="1" ht="15.75">
       <c r="B157" s="57"/>
       <c r="C157" s="57"/>
       <c r="D157" s="57"/>
@@ -5172,7 +5058,7 @@
       <c r="V157" s="60"/>
       <c r="W157" s="57"/>
     </row>
-    <row r="158" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:29" customHeight="1" ht="15.75">
       <c r="B158" s="57"/>
       <c r="C158" s="57"/>
       <c r="D158" s="57"/>
@@ -5196,7 +5082,7 @@
       <c r="V158" s="60"/>
       <c r="W158" s="57"/>
     </row>
-    <row r="159" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:29" customHeight="1" ht="15.75">
       <c r="B159" s="57"/>
       <c r="C159" s="57"/>
       <c r="D159" s="57"/>
@@ -5220,7 +5106,7 @@
       <c r="V159" s="60"/>
       <c r="W159" s="57"/>
     </row>
-    <row r="160" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:29" customHeight="1" ht="15.75">
       <c r="B160" s="57"/>
       <c r="C160" s="57"/>
       <c r="D160" s="57"/>
@@ -5244,7 +5130,7 @@
       <c r="V160" s="60"/>
       <c r="W160" s="57"/>
     </row>
-    <row r="161" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:29" customHeight="1" ht="15.75">
       <c r="B161" s="57"/>
       <c r="C161" s="57"/>
       <c r="D161" s="57"/>
@@ -5268,7 +5154,7 @@
       <c r="V161" s="60"/>
       <c r="W161" s="57"/>
     </row>
-    <row r="162" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:29" customHeight="1" ht="15.75">
       <c r="B162" s="57"/>
       <c r="C162" s="57"/>
       <c r="D162" s="57"/>
@@ -5292,7 +5178,7 @@
       <c r="V162" s="60"/>
       <c r="W162" s="57"/>
     </row>
-    <row r="163" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:29" customHeight="1" ht="15.75">
       <c r="B163" s="57"/>
       <c r="C163" s="57"/>
       <c r="D163" s="57"/>
@@ -5316,7 +5202,7 @@
       <c r="V163" s="60"/>
       <c r="W163" s="57"/>
     </row>
-    <row r="164" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:29" customHeight="1" ht="15.75">
       <c r="B164" s="57"/>
       <c r="C164" s="57"/>
       <c r="D164" s="57"/>
@@ -5340,7 +5226,7 @@
       <c r="V164" s="60"/>
       <c r="W164" s="57"/>
     </row>
-    <row r="165" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:29" customHeight="1" ht="15.75">
       <c r="B165" s="57"/>
       <c r="C165" s="57"/>
       <c r="D165" s="57"/>
@@ -5364,7 +5250,7 @@
       <c r="V165" s="60"/>
       <c r="W165" s="57"/>
     </row>
-    <row r="166" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:29" customHeight="1" ht="15.75">
       <c r="B166" s="57"/>
       <c r="C166" s="57"/>
       <c r="D166" s="57"/>
@@ -5388,7 +5274,7 @@
       <c r="V166" s="60"/>
       <c r="W166" s="57"/>
     </row>
-    <row r="167" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:29" customHeight="1" ht="15.75">
       <c r="B167" s="57"/>
       <c r="C167" s="57"/>
       <c r="D167" s="57"/>
@@ -5412,7 +5298,7 @@
       <c r="V167" s="60"/>
       <c r="W167" s="57"/>
     </row>
-    <row r="168" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:29" customHeight="1" ht="15.75">
       <c r="B168" s="57"/>
       <c r="C168" s="57"/>
       <c r="D168" s="57"/>
@@ -5436,7 +5322,7 @@
       <c r="V168" s="60"/>
       <c r="W168" s="57"/>
     </row>
-    <row r="169" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:29" customHeight="1" ht="15.75">
       <c r="B169" s="57"/>
       <c r="C169" s="57"/>
       <c r="D169" s="57"/>
@@ -5460,7 +5346,7 @@
       <c r="V169" s="60"/>
       <c r="W169" s="57"/>
     </row>
-    <row r="170" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:29" customHeight="1" ht="15.75">
       <c r="B170" s="57"/>
       <c r="C170" s="57"/>
       <c r="D170" s="57"/>
@@ -5484,7 +5370,7 @@
       <c r="V170" s="60"/>
       <c r="W170" s="57"/>
     </row>
-    <row r="171" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:29" customHeight="1" ht="15.75">
       <c r="B171" s="57"/>
       <c r="C171" s="57"/>
       <c r="D171" s="57"/>
@@ -5508,7 +5394,7 @@
       <c r="V171" s="60"/>
       <c r="W171" s="57"/>
     </row>
-    <row r="172" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:29" customHeight="1" ht="15.75">
       <c r="B172" s="57"/>
       <c r="C172" s="57"/>
       <c r="D172" s="57"/>
@@ -5532,7 +5418,7 @@
       <c r="V172" s="60"/>
       <c r="W172" s="57"/>
     </row>
-    <row r="173" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:29" customHeight="1" ht="15.75">
       <c r="B173" s="57"/>
       <c r="C173" s="57"/>
       <c r="D173" s="57"/>
@@ -5556,7 +5442,7 @@
       <c r="V173" s="60"/>
       <c r="W173" s="57"/>
     </row>
-    <row r="174" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:29" customHeight="1" ht="15.75">
       <c r="B174" s="57"/>
       <c r="C174" s="57"/>
       <c r="D174" s="57"/>
@@ -5580,7 +5466,7 @@
       <c r="V174" s="60"/>
       <c r="W174" s="57"/>
     </row>
-    <row r="175" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:29" customHeight="1" ht="15.75">
       <c r="B175" s="57"/>
       <c r="C175" s="57"/>
       <c r="D175" s="57"/>
@@ -5604,7 +5490,7 @@
       <c r="V175" s="60"/>
       <c r="W175" s="57"/>
     </row>
-    <row r="176" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:29" customHeight="1" ht="15.75">
       <c r="B176" s="57"/>
       <c r="C176" s="57"/>
       <c r="D176" s="57"/>
@@ -5628,7 +5514,7 @@
       <c r="V176" s="60"/>
       <c r="W176" s="57"/>
     </row>
-    <row r="177" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:29" customHeight="1" ht="15.75">
       <c r="B177" s="57"/>
       <c r="C177" s="57"/>
       <c r="D177" s="57"/>
@@ -5652,7 +5538,7 @@
       <c r="V177" s="60"/>
       <c r="W177" s="57"/>
     </row>
-    <row r="178" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:29" customHeight="1" ht="15.75">
       <c r="B178" s="57"/>
       <c r="C178" s="57"/>
       <c r="D178" s="57"/>
@@ -5676,7 +5562,7 @@
       <c r="V178" s="60"/>
       <c r="W178" s="57"/>
     </row>
-    <row r="179" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:29" customHeight="1" ht="15.75">
       <c r="B179" s="57"/>
       <c r="C179" s="57"/>
       <c r="D179" s="57"/>
@@ -5700,7 +5586,7 @@
       <c r="V179" s="60"/>
       <c r="W179" s="57"/>
     </row>
-    <row r="180" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:29" customHeight="1" ht="15.75">
       <c r="B180" s="57"/>
       <c r="C180" s="57"/>
       <c r="D180" s="57"/>
@@ -5724,7 +5610,7 @@
       <c r="V180" s="60"/>
       <c r="W180" s="57"/>
     </row>
-    <row r="181" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:29" customHeight="1" ht="15.75">
       <c r="B181" s="57"/>
       <c r="C181" s="57"/>
       <c r="D181" s="57"/>
@@ -5748,7 +5634,7 @@
       <c r="V181" s="60"/>
       <c r="W181" s="57"/>
     </row>
-    <row r="182" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:29" customHeight="1" ht="15.75">
       <c r="B182" s="57"/>
       <c r="C182" s="57"/>
       <c r="D182" s="57"/>
@@ -5772,7 +5658,7 @@
       <c r="V182" s="60"/>
       <c r="W182" s="57"/>
     </row>
-    <row r="183" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:29" customHeight="1" ht="15.75">
       <c r="B183" s="57"/>
       <c r="C183" s="57"/>
       <c r="D183" s="57"/>
@@ -5796,7 +5682,7 @@
       <c r="V183" s="60"/>
       <c r="W183" s="57"/>
     </row>
-    <row r="184" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:29" customHeight="1" ht="15.75">
       <c r="B184" s="57"/>
       <c r="C184" s="57"/>
       <c r="D184" s="57"/>
@@ -5820,7 +5706,7 @@
       <c r="V184" s="60"/>
       <c r="W184" s="57"/>
     </row>
-    <row r="185" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:29" customHeight="1" ht="15.75">
       <c r="B185" s="57"/>
       <c r="C185" s="57"/>
       <c r="D185" s="57"/>
@@ -5844,7 +5730,7 @@
       <c r="V185" s="60"/>
       <c r="W185" s="57"/>
     </row>
-    <row r="186" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:29" customHeight="1" ht="15.75">
       <c r="B186" s="57"/>
       <c r="C186" s="57"/>
       <c r="D186" s="57"/>
@@ -5868,7 +5754,7 @@
       <c r="V186" s="60"/>
       <c r="W186" s="57"/>
     </row>
-    <row r="187" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:29" customHeight="1" ht="15.75">
       <c r="B187" s="57"/>
       <c r="C187" s="57"/>
       <c r="D187" s="57"/>
@@ -5892,7 +5778,7 @@
       <c r="V187" s="60"/>
       <c r="W187" s="57"/>
     </row>
-    <row r="188" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:29" customHeight="1" ht="15.75">
       <c r="B188" s="57"/>
       <c r="C188" s="57"/>
       <c r="D188" s="57"/>
@@ -5916,7 +5802,7 @@
       <c r="V188" s="60"/>
       <c r="W188" s="57"/>
     </row>
-    <row r="189" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:29" customHeight="1" ht="15.75">
       <c r="B189" s="57"/>
       <c r="C189" s="57"/>
       <c r="D189" s="57"/>
@@ -5940,7 +5826,7 @@
       <c r="V189" s="60"/>
       <c r="W189" s="57"/>
     </row>
-    <row r="190" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:29" customHeight="1" ht="15.75">
       <c r="B190" s="57"/>
       <c r="C190" s="57"/>
       <c r="D190" s="57"/>
@@ -5964,7 +5850,7 @@
       <c r="V190" s="60"/>
       <c r="W190" s="57"/>
     </row>
-    <row r="191" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:29" customHeight="1" ht="15.75">
       <c r="B191" s="57"/>
       <c r="C191" s="57"/>
       <c r="D191" s="57"/>
@@ -5988,7 +5874,7 @@
       <c r="V191" s="60"/>
       <c r="W191" s="57"/>
     </row>
-    <row r="192" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:29" customHeight="1" ht="15.75">
       <c r="B192" s="57"/>
       <c r="C192" s="57"/>
       <c r="D192" s="57"/>
@@ -6012,7 +5898,7 @@
       <c r="V192" s="60"/>
       <c r="W192" s="57"/>
     </row>
-    <row r="193" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:29" customHeight="1" ht="15.75">
       <c r="B193" s="57"/>
       <c r="C193" s="57"/>
       <c r="D193" s="57"/>
@@ -6036,7 +5922,7 @@
       <c r="V193" s="60"/>
       <c r="W193" s="57"/>
     </row>
-    <row r="194" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:29" customHeight="1" ht="15.75">
       <c r="B194" s="57"/>
       <c r="C194" s="57"/>
       <c r="D194" s="57"/>
@@ -6060,7 +5946,7 @@
       <c r="V194" s="60"/>
       <c r="W194" s="57"/>
     </row>
-    <row r="195" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:29" customHeight="1" ht="15.75">
       <c r="B195" s="57"/>
       <c r="C195" s="57"/>
       <c r="D195" s="57"/>
@@ -6084,7 +5970,7 @@
       <c r="V195" s="60"/>
       <c r="W195" s="57"/>
     </row>
-    <row r="196" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:29" customHeight="1" ht="15.75">
       <c r="B196" s="57"/>
       <c r="C196" s="57"/>
       <c r="D196" s="57"/>
@@ -6108,7 +5994,7 @@
       <c r="V196" s="60"/>
       <c r="W196" s="57"/>
     </row>
-    <row r="197" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:29" customHeight="1" ht="15.75">
       <c r="B197" s="57"/>
       <c r="C197" s="57"/>
       <c r="D197" s="57"/>
@@ -6132,7 +6018,7 @@
       <c r="V197" s="60"/>
       <c r="W197" s="57"/>
     </row>
-    <row r="198" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:29" customHeight="1" ht="15.75">
       <c r="B198" s="57"/>
       <c r="C198" s="57"/>
       <c r="D198" s="57"/>
@@ -6156,7 +6042,7 @@
       <c r="V198" s="60"/>
       <c r="W198" s="57"/>
     </row>
-    <row r="199" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:29" customHeight="1" ht="15.75">
       <c r="B199" s="57"/>
       <c r="C199" s="57"/>
       <c r="D199" s="57"/>
@@ -6180,7 +6066,7 @@
       <c r="V199" s="60"/>
       <c r="W199" s="57"/>
     </row>
-    <row r="200" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:29" customHeight="1" ht="15.75">
       <c r="B200" s="57"/>
       <c r="C200" s="57"/>
       <c r="D200" s="57"/>
@@ -6204,7 +6090,7 @@
       <c r="V200" s="60"/>
       <c r="W200" s="57"/>
     </row>
-    <row r="201" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:29" customHeight="1" ht="15.75">
       <c r="B201" s="57"/>
       <c r="C201" s="57"/>
       <c r="D201" s="57"/>
@@ -6228,7 +6114,7 @@
       <c r="V201" s="60"/>
       <c r="W201" s="57"/>
     </row>
-    <row r="202" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:29" customHeight="1" ht="15.75">
       <c r="B202" s="57"/>
       <c r="C202" s="57"/>
       <c r="D202" s="57"/>
@@ -6252,7 +6138,7 @@
       <c r="V202" s="60"/>
       <c r="W202" s="57"/>
     </row>
-    <row r="203" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:29" customHeight="1" ht="15.75">
       <c r="B203" s="57"/>
       <c r="C203" s="57"/>
       <c r="D203" s="57"/>
@@ -6276,7 +6162,7 @@
       <c r="V203" s="60"/>
       <c r="W203" s="57"/>
     </row>
-    <row r="204" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:29" customHeight="1" ht="15.75">
       <c r="B204" s="57"/>
       <c r="C204" s="57"/>
       <c r="D204" s="57"/>
@@ -6300,7 +6186,7 @@
       <c r="V204" s="60"/>
       <c r="W204" s="57"/>
     </row>
-    <row r="205" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:29" customHeight="1" ht="15.75">
       <c r="B205" s="57"/>
       <c r="C205" s="57"/>
       <c r="D205" s="57"/>
@@ -6324,7 +6210,7 @@
       <c r="V205" s="60"/>
       <c r="W205" s="57"/>
     </row>
-    <row r="206" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:29" customHeight="1" ht="15.75">
       <c r="B206" s="57"/>
       <c r="C206" s="57"/>
       <c r="D206" s="57"/>
@@ -6348,7 +6234,7 @@
       <c r="V206" s="60"/>
       <c r="W206" s="57"/>
     </row>
-    <row r="207" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:29" customHeight="1" ht="15.75">
       <c r="B207" s="57"/>
       <c r="C207" s="57"/>
       <c r="D207" s="57"/>
@@ -6372,7 +6258,7 @@
       <c r="V207" s="60"/>
       <c r="W207" s="57"/>
     </row>
-    <row r="208" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:29" customHeight="1" ht="15.75">
       <c r="B208" s="57"/>
       <c r="C208" s="57"/>
       <c r="D208" s="57"/>
@@ -6396,7 +6282,7 @@
       <c r="V208" s="60"/>
       <c r="W208" s="57"/>
     </row>
-    <row r="209" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:29" customHeight="1" ht="15.75">
       <c r="B209" s="57"/>
       <c r="C209" s="57"/>
       <c r="D209" s="57"/>
@@ -6420,7 +6306,7 @@
       <c r="V209" s="60"/>
       <c r="W209" s="57"/>
     </row>
-    <row r="210" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:29" customHeight="1" ht="15.75">
       <c r="B210" s="57"/>
       <c r="C210" s="57"/>
       <c r="D210" s="57"/>
@@ -6444,7 +6330,7 @@
       <c r="V210" s="60"/>
       <c r="W210" s="57"/>
     </row>
-    <row r="211" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:29" customHeight="1" ht="15.75">
       <c r="B211" s="57"/>
       <c r="C211" s="57"/>
       <c r="D211" s="57"/>
@@ -6468,7 +6354,7 @@
       <c r="V211" s="60"/>
       <c r="W211" s="57"/>
     </row>
-    <row r="212" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:29" customHeight="1" ht="15.75">
       <c r="B212" s="57"/>
       <c r="C212" s="57"/>
       <c r="D212" s="57"/>
@@ -6492,7 +6378,7 @@
       <c r="V212" s="60"/>
       <c r="W212" s="57"/>
     </row>
-    <row r="213" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:29" customHeight="1" ht="15.75">
       <c r="B213" s="57"/>
       <c r="C213" s="57"/>
       <c r="D213" s="57"/>
@@ -6516,7 +6402,7 @@
       <c r="V213" s="60"/>
       <c r="W213" s="57"/>
     </row>
-    <row r="214" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:29" customHeight="1" ht="15.75">
       <c r="B214" s="57"/>
       <c r="C214" s="57"/>
       <c r="D214" s="57"/>
@@ -6540,7 +6426,7 @@
       <c r="V214" s="60"/>
       <c r="W214" s="57"/>
     </row>
-    <row r="215" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:29" customHeight="1" ht="15.75">
       <c r="B215" s="57"/>
       <c r="C215" s="57"/>
       <c r="D215" s="57"/>
@@ -6564,7 +6450,7 @@
       <c r="V215" s="60"/>
       <c r="W215" s="57"/>
     </row>
-    <row r="216" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:29" customHeight="1" ht="15.75">
       <c r="B216" s="57"/>
       <c r="C216" s="57"/>
       <c r="D216" s="57"/>
@@ -6588,7 +6474,7 @@
       <c r="V216" s="60"/>
       <c r="W216" s="57"/>
     </row>
-    <row r="217" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:29" customHeight="1" ht="15.75">
       <c r="B217" s="57"/>
       <c r="C217" s="57"/>
       <c r="D217" s="57"/>
@@ -6612,7 +6498,7 @@
       <c r="V217" s="60"/>
       <c r="W217" s="57"/>
     </row>
-    <row r="218" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:29" customHeight="1" ht="15.75">
       <c r="B218" s="57"/>
       <c r="C218" s="57"/>
       <c r="D218" s="57"/>
@@ -6636,7 +6522,7 @@
       <c r="V218" s="60"/>
       <c r="W218" s="57"/>
     </row>
-    <row r="219" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:29" customHeight="1" ht="15.75">
       <c r="B219" s="57"/>
       <c r="C219" s="57"/>
       <c r="D219" s="57"/>
@@ -6660,7 +6546,7 @@
       <c r="V219" s="60"/>
       <c r="W219" s="57"/>
     </row>
-    <row r="220" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:29" customHeight="1" ht="15.75">
       <c r="B220" s="57"/>
       <c r="C220" s="57"/>
       <c r="D220" s="57"/>
@@ -6684,7 +6570,7 @@
       <c r="V220" s="60"/>
       <c r="W220" s="57"/>
     </row>
-    <row r="221" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:29" customHeight="1" ht="15.75">
       <c r="B221" s="57"/>
       <c r="C221" s="57"/>
       <c r="D221" s="57"/>
@@ -6708,7 +6594,7 @@
       <c r="V221" s="60"/>
       <c r="W221" s="57"/>
     </row>
-    <row r="222" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:29" customHeight="1" ht="15.75">
       <c r="B222" s="57"/>
       <c r="C222" s="57"/>
       <c r="D222" s="57"/>
@@ -6732,7 +6618,7 @@
       <c r="V222" s="60"/>
       <c r="W222" s="57"/>
     </row>
-    <row r="223" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:29" customHeight="1" ht="15.75">
       <c r="B223" s="57"/>
       <c r="C223" s="57"/>
       <c r="D223" s="57"/>
@@ -6756,7 +6642,7 @@
       <c r="V223" s="60"/>
       <c r="W223" s="57"/>
     </row>
-    <row r="224" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:29" customHeight="1" ht="15.75">
       <c r="B224" s="57"/>
       <c r="C224" s="57"/>
       <c r="D224" s="57"/>
@@ -6780,7 +6666,7 @@
       <c r="V224" s="60"/>
       <c r="W224" s="57"/>
     </row>
-    <row r="225" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:29" customHeight="1" ht="15.75">
       <c r="B225" s="57"/>
       <c r="C225" s="57"/>
       <c r="D225" s="57"/>
@@ -6804,7 +6690,7 @@
       <c r="V225" s="60"/>
       <c r="W225" s="57"/>
     </row>
-    <row r="226" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:29" customHeight="1" ht="15.75">
       <c r="B226" s="57"/>
       <c r="C226" s="57"/>
       <c r="D226" s="57"/>
@@ -6828,7 +6714,7 @@
       <c r="V226" s="60"/>
       <c r="W226" s="57"/>
     </row>
-    <row r="227" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:29" customHeight="1" ht="15.75">
       <c r="B227" s="57"/>
       <c r="C227" s="57"/>
       <c r="D227" s="57"/>
@@ -6852,7 +6738,7 @@
       <c r="V227" s="60"/>
       <c r="W227" s="57"/>
     </row>
-    <row r="228" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:29" customHeight="1" ht="15.75">
       <c r="B228" s="57"/>
       <c r="C228" s="57"/>
       <c r="D228" s="57"/>
@@ -6876,7 +6762,7 @@
       <c r="V228" s="60"/>
       <c r="W228" s="57"/>
     </row>
-    <row r="229" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:29" customHeight="1" ht="15.75">
       <c r="B229" s="57"/>
       <c r="C229" s="57"/>
       <c r="D229" s="57"/>
@@ -6900,7 +6786,7 @@
       <c r="V229" s="60"/>
       <c r="W229" s="57"/>
     </row>
-    <row r="230" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:29" customHeight="1" ht="15.75">
       <c r="B230" s="57"/>
       <c r="C230" s="57"/>
       <c r="D230" s="57"/>
@@ -6924,7 +6810,7 @@
       <c r="V230" s="60"/>
       <c r="W230" s="57"/>
     </row>
-    <row r="231" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:29" customHeight="1" ht="15.75">
       <c r="B231" s="57"/>
       <c r="C231" s="57"/>
       <c r="D231" s="57"/>
@@ -6948,7 +6834,7 @@
       <c r="V231" s="60"/>
       <c r="W231" s="57"/>
     </row>
-    <row r="232" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:29" customHeight="1" ht="15.75">
       <c r="B232" s="57"/>
       <c r="C232" s="57"/>
       <c r="D232" s="57"/>
@@ -6972,7 +6858,7 @@
       <c r="V232" s="60"/>
       <c r="W232" s="57"/>
     </row>
-    <row r="233" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:29" customHeight="1" ht="15.75">
       <c r="B233" s="57"/>
       <c r="C233" s="57"/>
       <c r="D233" s="57"/>
@@ -6996,7 +6882,7 @@
       <c r="V233" s="60"/>
       <c r="W233" s="57"/>
     </row>
-    <row r="234" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:29" customHeight="1" ht="15.75">
       <c r="B234" s="57"/>
       <c r="C234" s="57"/>
       <c r="D234" s="57"/>
@@ -7020,7 +6906,7 @@
       <c r="V234" s="60"/>
       <c r="W234" s="57"/>
     </row>
-    <row r="235" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:29" customHeight="1" ht="15.75">
       <c r="B235" s="57"/>
       <c r="C235" s="57"/>
       <c r="D235" s="57"/>
@@ -7044,7 +6930,7 @@
       <c r="V235" s="60"/>
       <c r="W235" s="57"/>
     </row>
-    <row r="236" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:29" customHeight="1" ht="15.75">
       <c r="B236" s="57"/>
       <c r="C236" s="57"/>
       <c r="D236" s="57"/>
@@ -7068,7 +6954,7 @@
       <c r="V236" s="60"/>
       <c r="W236" s="57"/>
     </row>
-    <row r="237" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:29" customHeight="1" ht="15.75">
       <c r="B237" s="57"/>
       <c r="C237" s="57"/>
       <c r="D237" s="57"/>
@@ -7092,7 +6978,7 @@
       <c r="V237" s="60"/>
       <c r="W237" s="57"/>
     </row>
-    <row r="238" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:29" customHeight="1" ht="15.75">
       <c r="B238" s="57"/>
       <c r="C238" s="57"/>
       <c r="D238" s="57"/>
@@ -7116,7 +7002,7 @@
       <c r="V238" s="60"/>
       <c r="W238" s="57"/>
     </row>
-    <row r="239" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:29" customHeight="1" ht="15.75">
       <c r="B239" s="57"/>
       <c r="C239" s="57"/>
       <c r="D239" s="57"/>
@@ -7140,7 +7026,7 @@
       <c r="V239" s="60"/>
       <c r="W239" s="57"/>
     </row>
-    <row r="240" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:29" customHeight="1" ht="15.75">
       <c r="B240" s="57"/>
       <c r="C240" s="57"/>
       <c r="D240" s="57"/>
@@ -7164,7 +7050,7 @@
       <c r="V240" s="60"/>
       <c r="W240" s="57"/>
     </row>
-    <row r="241" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:29" customHeight="1" ht="15.75">
       <c r="B241" s="57"/>
       <c r="C241" s="57"/>
       <c r="D241" s="57"/>
@@ -7188,7 +7074,7 @@
       <c r="V241" s="60"/>
       <c r="W241" s="57"/>
     </row>
-    <row r="242" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:29" customHeight="1" ht="15.75">
       <c r="B242" s="57"/>
       <c r="C242" s="57"/>
       <c r="D242" s="57"/>
@@ -7212,7 +7098,7 @@
       <c r="V242" s="60"/>
       <c r="W242" s="57"/>
     </row>
-    <row r="243" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:29" customHeight="1" ht="15.75">
       <c r="B243" s="57"/>
       <c r="C243" s="57"/>
       <c r="D243" s="57"/>
@@ -7236,7 +7122,7 @@
       <c r="V243" s="60"/>
       <c r="W243" s="57"/>
     </row>
-    <row r="244" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:29" customHeight="1" ht="15.75">
       <c r="B244" s="57"/>
       <c r="C244" s="57"/>
       <c r="D244" s="57"/>
@@ -7260,7 +7146,7 @@
       <c r="V244" s="60"/>
       <c r="W244" s="57"/>
     </row>
-    <row r="245" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:29" customHeight="1" ht="15.75">
       <c r="B245" s="57"/>
       <c r="C245" s="57"/>
       <c r="D245" s="57"/>
@@ -7284,7 +7170,7 @@
       <c r="V245" s="60"/>
       <c r="W245" s="57"/>
     </row>
-    <row r="246" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:29" customHeight="1" ht="15.75">
       <c r="B246" s="57"/>
       <c r="C246" s="57"/>
       <c r="D246" s="57"/>
@@ -7308,7 +7194,7 @@
       <c r="V246" s="60"/>
       <c r="W246" s="57"/>
     </row>
-    <row r="247" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:29" customHeight="1" ht="15.75">
       <c r="B247" s="57"/>
       <c r="C247" s="57"/>
       <c r="D247" s="57"/>
@@ -7332,7 +7218,7 @@
       <c r="V247" s="60"/>
       <c r="W247" s="57"/>
     </row>
-    <row r="248" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:29" customHeight="1" ht="15.75">
       <c r="B248" s="57"/>
       <c r="C248" s="57"/>
       <c r="D248" s="57"/>
@@ -7356,7 +7242,7 @@
       <c r="V248" s="60"/>
       <c r="W248" s="57"/>
     </row>
-    <row r="249" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:29" customHeight="1" ht="15.75">
       <c r="B249" s="57"/>
       <c r="C249" s="57"/>
       <c r="D249" s="57"/>
@@ -7380,7 +7266,7 @@
       <c r="V249" s="60"/>
       <c r="W249" s="57"/>
     </row>
-    <row r="250" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:29" customHeight="1" ht="15.75">
       <c r="B250" s="57"/>
       <c r="C250" s="57"/>
       <c r="D250" s="57"/>
@@ -7404,7 +7290,7 @@
       <c r="V250" s="60"/>
       <c r="W250" s="57"/>
     </row>
-    <row r="251" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:29" customHeight="1" ht="15.75">
       <c r="B251" s="57"/>
       <c r="C251" s="57"/>
       <c r="D251" s="57"/>
@@ -7428,7 +7314,7 @@
       <c r="V251" s="60"/>
       <c r="W251" s="57"/>
     </row>
-    <row r="252" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:29" customHeight="1" ht="15.75">
       <c r="B252" s="57"/>
       <c r="C252" s="57"/>
       <c r="D252" s="57"/>
@@ -7452,7 +7338,7 @@
       <c r="V252" s="60"/>
       <c r="W252" s="57"/>
     </row>
-    <row r="253" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:29" customHeight="1" ht="15.75">
       <c r="B253" s="57"/>
       <c r="C253" s="57"/>
       <c r="D253" s="57"/>
@@ -7476,7 +7362,7 @@
       <c r="V253" s="60"/>
       <c r="W253" s="57"/>
     </row>
-    <row r="254" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:29" customHeight="1" ht="15.75">
       <c r="B254" s="57"/>
       <c r="C254" s="57"/>
       <c r="D254" s="57"/>
@@ -7500,7 +7386,7 @@
       <c r="V254" s="60"/>
       <c r="W254" s="57"/>
     </row>
-    <row r="255" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:29" customHeight="1" ht="15.75">
       <c r="B255" s="57"/>
       <c r="C255" s="57"/>
       <c r="D255" s="57"/>
@@ -7524,7 +7410,7 @@
       <c r="V255" s="60"/>
       <c r="W255" s="57"/>
     </row>
-    <row r="256" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:29" customHeight="1" ht="15.75">
       <c r="B256" s="57"/>
       <c r="C256" s="57"/>
       <c r="D256" s="57"/>
@@ -7548,7 +7434,7 @@
       <c r="V256" s="60"/>
       <c r="W256" s="57"/>
     </row>
-    <row r="257" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:29" customHeight="1" ht="15.75">
       <c r="B257" s="57"/>
       <c r="C257" s="57"/>
       <c r="D257" s="57"/>
@@ -7572,7 +7458,7 @@
       <c r="V257" s="60"/>
       <c r="W257" s="57"/>
     </row>
-    <row r="258" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:29" customHeight="1" ht="15.75">
       <c r="B258" s="57"/>
       <c r="C258" s="57"/>
       <c r="D258" s="57"/>
@@ -7596,7 +7482,7 @@
       <c r="V258" s="60"/>
       <c r="W258" s="57"/>
     </row>
-    <row r="259" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:29" customHeight="1" ht="15.75">
       <c r="B259" s="57"/>
       <c r="C259" s="57"/>
       <c r="D259" s="57"/>
@@ -7620,7 +7506,7 @@
       <c r="V259" s="60"/>
       <c r="W259" s="57"/>
     </row>
-    <row r="260" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:29" customHeight="1" ht="15.75">
       <c r="B260" s="57"/>
       <c r="C260" s="57"/>
       <c r="D260" s="57"/>
@@ -7644,7 +7530,7 @@
       <c r="V260" s="60"/>
       <c r="W260" s="57"/>
     </row>
-    <row r="261" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:29" customHeight="1" ht="15.75">
       <c r="B261" s="57"/>
       <c r="C261" s="57"/>
       <c r="D261" s="57"/>
@@ -7668,7 +7554,7 @@
       <c r="V261" s="60"/>
       <c r="W261" s="57"/>
     </row>
-    <row r="262" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:29" customHeight="1" ht="15.75">
       <c r="B262" s="57"/>
       <c r="C262" s="57"/>
       <c r="D262" s="57"/>
@@ -7692,7 +7578,7 @@
       <c r="V262" s="60"/>
       <c r="W262" s="57"/>
     </row>
-    <row r="263" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:29" customHeight="1" ht="15.75">
       <c r="B263" s="57"/>
       <c r="C263" s="57"/>
       <c r="D263" s="57"/>
@@ -7716,7 +7602,7 @@
       <c r="V263" s="60"/>
       <c r="W263" s="57"/>
     </row>
-    <row r="264" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:29" customHeight="1" ht="15.75">
       <c r="B264" s="57"/>
       <c r="C264" s="57"/>
       <c r="D264" s="57"/>
@@ -7740,7 +7626,7 @@
       <c r="V264" s="60"/>
       <c r="W264" s="57"/>
     </row>
-    <row r="265" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:29" customHeight="1" ht="15.75">
       <c r="B265" s="57"/>
       <c r="C265" s="57"/>
       <c r="D265" s="57"/>
@@ -7764,7 +7650,7 @@
       <c r="V265" s="60"/>
       <c r="W265" s="57"/>
     </row>
-    <row r="266" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:29" customHeight="1" ht="15.75">
       <c r="B266" s="57"/>
       <c r="C266" s="57"/>
       <c r="D266" s="57"/>
@@ -7788,7 +7674,7 @@
       <c r="V266" s="60"/>
       <c r="W266" s="57"/>
     </row>
-    <row r="267" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:29" customHeight="1" ht="15.75">
       <c r="B267" s="57"/>
       <c r="C267" s="57"/>
       <c r="D267" s="57"/>
@@ -7812,7 +7698,7 @@
       <c r="V267" s="60"/>
       <c r="W267" s="57"/>
     </row>
-    <row r="268" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:29" customHeight="1" ht="15.75">
       <c r="B268" s="57"/>
       <c r="C268" s="57"/>
       <c r="D268" s="57"/>
@@ -7836,7 +7722,7 @@
       <c r="V268" s="60"/>
       <c r="W268" s="57"/>
     </row>
-    <row r="269" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:29" customHeight="1" ht="15.75">
       <c r="B269" s="57"/>
       <c r="C269" s="57"/>
       <c r="D269" s="57"/>
@@ -7860,7 +7746,7 @@
       <c r="V269" s="60"/>
       <c r="W269" s="57"/>
     </row>
-    <row r="270" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:29" customHeight="1" ht="15.75">
       <c r="B270" s="57"/>
       <c r="C270" s="57"/>
       <c r="D270" s="57"/>
@@ -7884,7 +7770,7 @@
       <c r="V270" s="60"/>
       <c r="W270" s="57"/>
     </row>
-    <row r="271" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:29" customHeight="1" ht="15.75">
       <c r="B271" s="57"/>
       <c r="C271" s="57"/>
       <c r="D271" s="57"/>
@@ -7908,7 +7794,7 @@
       <c r="V271" s="60"/>
       <c r="W271" s="57"/>
     </row>
-    <row r="272" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:29" customHeight="1" ht="15.75">
       <c r="B272" s="57"/>
       <c r="C272" s="57"/>
       <c r="D272" s="57"/>
@@ -7932,7 +7818,7 @@
       <c r="V272" s="60"/>
       <c r="W272" s="57"/>
     </row>
-    <row r="273" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:29" customHeight="1" ht="15.75">
       <c r="B273" s="57"/>
       <c r="C273" s="57"/>
       <c r="D273" s="57"/>
@@ -7956,7 +7842,7 @@
       <c r="V273" s="60"/>
       <c r="W273" s="57"/>
     </row>
-    <row r="274" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:29" customHeight="1" ht="15.75">
       <c r="B274" s="57"/>
       <c r="C274" s="57"/>
       <c r="D274" s="57"/>
@@ -7980,7 +7866,7 @@
       <c r="V274" s="60"/>
       <c r="W274" s="57"/>
     </row>
-    <row r="275" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:29" customHeight="1" ht="15.75">
       <c r="B275" s="57"/>
       <c r="C275" s="57"/>
       <c r="D275" s="57"/>
@@ -8004,7 +7890,7 @@
       <c r="V275" s="60"/>
       <c r="W275" s="57"/>
     </row>
-    <row r="276" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:29" customHeight="1" ht="15.75">
       <c r="B276" s="57"/>
       <c r="C276" s="57"/>
       <c r="D276" s="57"/>
@@ -8028,7 +7914,7 @@
       <c r="V276" s="60"/>
       <c r="W276" s="57"/>
     </row>
-    <row r="277" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:29" customHeight="1" ht="15.75">
       <c r="B277" s="57"/>
       <c r="C277" s="57"/>
       <c r="D277" s="57"/>
@@ -8052,7 +7938,7 @@
       <c r="V277" s="60"/>
       <c r="W277" s="57"/>
     </row>
-    <row r="278" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:29" customHeight="1" ht="15.75">
       <c r="B278" s="57"/>
       <c r="C278" s="57"/>
       <c r="D278" s="57"/>
@@ -8076,7 +7962,7 @@
       <c r="V278" s="60"/>
       <c r="W278" s="57"/>
     </row>
-    <row r="279" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:29" customHeight="1" ht="15.75">
       <c r="B279" s="57"/>
       <c r="C279" s="57"/>
       <c r="D279" s="57"/>
@@ -8100,7 +7986,7 @@
       <c r="V279" s="60"/>
       <c r="W279" s="57"/>
     </row>
-    <row r="280" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:29" customHeight="1" ht="15.75">
       <c r="B280" s="57"/>
       <c r="C280" s="57"/>
       <c r="D280" s="57"/>
@@ -8124,7 +8010,7 @@
       <c r="V280" s="60"/>
       <c r="W280" s="57"/>
     </row>
-    <row r="281" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:29" customHeight="1" ht="15.75">
       <c r="B281" s="57"/>
       <c r="C281" s="57"/>
       <c r="D281" s="57"/>
@@ -8148,7 +8034,7 @@
       <c r="V281" s="60"/>
       <c r="W281" s="57"/>
     </row>
-    <row r="282" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:29" customHeight="1" ht="15.75">
       <c r="B282" s="57"/>
       <c r="C282" s="57"/>
       <c r="D282" s="57"/>
@@ -8172,7 +8058,7 @@
       <c r="V282" s="60"/>
       <c r="W282" s="57"/>
     </row>
-    <row r="283" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:29" customHeight="1" ht="15.75">
       <c r="B283" s="57"/>
       <c r="C283" s="57"/>
       <c r="D283" s="57"/>
@@ -8196,7 +8082,7 @@
       <c r="V283" s="60"/>
       <c r="W283" s="57"/>
     </row>
-    <row r="284" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:29" customHeight="1" ht="15.75">
       <c r="B284" s="57"/>
       <c r="C284" s="57"/>
       <c r="D284" s="57"/>
@@ -8220,7 +8106,7 @@
       <c r="V284" s="60"/>
       <c r="W284" s="57"/>
     </row>
-    <row r="285" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:29" customHeight="1" ht="15.75">
       <c r="B285" s="57"/>
       <c r="C285" s="57"/>
       <c r="D285" s="57"/>
@@ -8244,7 +8130,7 @@
       <c r="V285" s="60"/>
       <c r="W285" s="57"/>
     </row>
-    <row r="286" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:29" customHeight="1" ht="15.75">
       <c r="B286" s="57"/>
       <c r="C286" s="57"/>
       <c r="D286" s="57"/>
@@ -8268,7 +8154,7 @@
       <c r="V286" s="60"/>
       <c r="W286" s="57"/>
     </row>
-    <row r="287" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:29" customHeight="1" ht="15.75">
       <c r="B287" s="57"/>
       <c r="C287" s="57"/>
       <c r="D287" s="57"/>
@@ -8292,7 +8178,7 @@
       <c r="V287" s="60"/>
       <c r="W287" s="57"/>
     </row>
-    <row r="288" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:29" customHeight="1" ht="15.75">
       <c r="B288" s="57"/>
       <c r="C288" s="57"/>
       <c r="D288" s="57"/>
@@ -8316,7 +8202,7 @@
       <c r="V288" s="60"/>
       <c r="W288" s="57"/>
     </row>
-    <row r="289" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:29" customHeight="1" ht="15.75">
       <c r="B289" s="57"/>
       <c r="C289" s="57"/>
       <c r="D289" s="57"/>
@@ -8340,7 +8226,7 @@
       <c r="V289" s="60"/>
       <c r="W289" s="57"/>
     </row>
-    <row r="290" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:29" customHeight="1" ht="15.75">
       <c r="B290" s="57"/>
       <c r="C290" s="57"/>
       <c r="D290" s="57"/>
@@ -8364,7 +8250,7 @@
       <c r="V290" s="60"/>
       <c r="W290" s="57"/>
     </row>
-    <row r="291" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:29" customHeight="1" ht="15.75">
       <c r="B291" s="57"/>
       <c r="C291" s="57"/>
       <c r="D291" s="57"/>
@@ -8388,7 +8274,7 @@
       <c r="V291" s="60"/>
       <c r="W291" s="57"/>
     </row>
-    <row r="292" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:29" customHeight="1" ht="15.75">
       <c r="B292" s="57"/>
       <c r="C292" s="57"/>
       <c r="D292" s="57"/>
@@ -8412,7 +8298,7 @@
       <c r="V292" s="60"/>
       <c r="W292" s="57"/>
     </row>
-    <row r="293" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:29" customHeight="1" ht="15.75">
       <c r="B293" s="57"/>
       <c r="C293" s="57"/>
       <c r="D293" s="57"/>
@@ -8436,7 +8322,7 @@
       <c r="V293" s="60"/>
       <c r="W293" s="57"/>
     </row>
-    <row r="294" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:29" customHeight="1" ht="15.75">
       <c r="B294" s="57"/>
       <c r="C294" s="57"/>
       <c r="D294" s="57"/>
@@ -8460,7 +8346,7 @@
       <c r="V294" s="60"/>
       <c r="W294" s="57"/>
     </row>
-    <row r="295" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:29" customHeight="1" ht="15.75">
       <c r="B295" s="57"/>
       <c r="C295" s="57"/>
       <c r="D295" s="57"/>
@@ -8484,7 +8370,7 @@
       <c r="V295" s="60"/>
       <c r="W295" s="57"/>
     </row>
-    <row r="296" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:29" customHeight="1" ht="15.75">
       <c r="B296" s="57"/>
       <c r="C296" s="57"/>
       <c r="D296" s="57"/>
@@ -8508,7 +8394,7 @@
       <c r="V296" s="60"/>
       <c r="W296" s="57"/>
     </row>
-    <row r="297" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:29" customHeight="1" ht="15.75">
       <c r="B297" s="57"/>
       <c r="C297" s="57"/>
       <c r="D297" s="57"/>
@@ -8532,7 +8418,7 @@
       <c r="V297" s="60"/>
       <c r="W297" s="57"/>
     </row>
-    <row r="298" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:29" customHeight="1" ht="15.75">
       <c r="B298" s="57"/>
       <c r="C298" s="57"/>
       <c r="D298" s="57"/>
@@ -8556,7 +8442,7 @@
       <c r="V298" s="60"/>
       <c r="W298" s="57"/>
     </row>
-    <row r="299" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:29" customHeight="1" ht="15.75">
       <c r="B299" s="57"/>
       <c r="C299" s="57"/>
       <c r="D299" s="57"/>
@@ -8580,7 +8466,7 @@
       <c r="V299" s="60"/>
       <c r="W299" s="57"/>
     </row>
-    <row r="300" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:29" customHeight="1" ht="15.75">
       <c r="B300" s="57"/>
       <c r="C300" s="57"/>
       <c r="D300" s="57"/>
@@ -8604,7 +8490,7 @@
       <c r="V300" s="60"/>
       <c r="W300" s="57"/>
     </row>
-    <row r="301" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:29" customHeight="1" ht="15.75">
       <c r="B301" s="57"/>
       <c r="C301" s="57"/>
       <c r="D301" s="57"/>
@@ -8628,7 +8514,7 @@
       <c r="V301" s="60"/>
       <c r="W301" s="57"/>
     </row>
-    <row r="302" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:29" customHeight="1" ht="15.75">
       <c r="B302" s="57"/>
       <c r="C302" s="57"/>
       <c r="D302" s="57"/>
@@ -8652,7 +8538,7 @@
       <c r="V302" s="60"/>
       <c r="W302" s="57"/>
     </row>
-    <row r="303" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:29" customHeight="1" ht="15.75">
       <c r="B303" s="57"/>
       <c r="C303" s="57"/>
       <c r="D303" s="57"/>
@@ -8676,7 +8562,7 @@
       <c r="V303" s="60"/>
       <c r="W303" s="57"/>
     </row>
-    <row r="304" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:29" customHeight="1" ht="15.75">
       <c r="B304" s="57"/>
       <c r="C304" s="57"/>
       <c r="D304" s="57"/>
@@ -8700,7 +8586,7 @@
       <c r="V304" s="60"/>
       <c r="W304" s="57"/>
     </row>
-    <row r="305" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:29" customHeight="1" ht="15.75">
       <c r="B305" s="57"/>
       <c r="C305" s="57"/>
       <c r="D305" s="57"/>
@@ -8724,7 +8610,7 @@
       <c r="V305" s="60"/>
       <c r="W305" s="57"/>
     </row>
-    <row r="306" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:29" customHeight="1" ht="15.75">
       <c r="B306" s="57"/>
       <c r="C306" s="57"/>
       <c r="D306" s="57"/>
@@ -8748,7 +8634,7 @@
       <c r="V306" s="60"/>
       <c r="W306" s="57"/>
     </row>
-    <row r="307" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:29" customHeight="1" ht="15.75">
       <c r="B307" s="57"/>
       <c r="C307" s="57"/>
       <c r="D307" s="57"/>
@@ -8772,7 +8658,7 @@
       <c r="V307" s="60"/>
       <c r="W307" s="57"/>
     </row>
-    <row r="308" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:29" customHeight="1" ht="15.75">
       <c r="B308" s="57"/>
       <c r="C308" s="57"/>
       <c r="D308" s="57"/>
@@ -8796,7 +8682,7 @@
       <c r="V308" s="60"/>
       <c r="W308" s="57"/>
     </row>
-    <row r="309" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:29" customHeight="1" ht="15.75">
       <c r="B309" s="57"/>
       <c r="C309" s="57"/>
       <c r="D309" s="57"/>
@@ -8820,7 +8706,7 @@
       <c r="V309" s="60"/>
       <c r="W309" s="57"/>
     </row>
-    <row r="310" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:29" customHeight="1" ht="15.75">
       <c r="B310" s="57"/>
       <c r="C310" s="57"/>
       <c r="D310" s="57"/>
@@ -8844,7 +8730,7 @@
       <c r="V310" s="60"/>
       <c r="W310" s="57"/>
     </row>
-    <row r="311" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:29" customHeight="1" ht="15.75">
       <c r="B311" s="57"/>
       <c r="C311" s="57"/>
       <c r="D311" s="57"/>
@@ -8868,4823 +8754,4823 @@
       <c r="V311" s="60"/>
       <c r="W311" s="57"/>
     </row>
-    <row r="312" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:29" customHeight="1" ht="15.75">
       <c r="P312" s="61"/>
       <c r="Q312" s="61"/>
       <c r="S312" s="61"/>
       <c r="U312" s="62"/>
       <c r="V312" s="62"/>
     </row>
-    <row r="313" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:29" customHeight="1" ht="15.75">
       <c r="P313" s="61"/>
       <c r="Q313" s="61"/>
       <c r="S313" s="61"/>
       <c r="U313" s="62"/>
       <c r="V313" s="62"/>
     </row>
-    <row r="314" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:29" customHeight="1" ht="15.75">
       <c r="P314" s="61"/>
       <c r="Q314" s="61"/>
       <c r="S314" s="61"/>
       <c r="U314" s="62"/>
       <c r="V314" s="62"/>
     </row>
-    <row r="315" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:29" customHeight="1" ht="15.75">
       <c r="P315" s="61"/>
       <c r="Q315" s="61"/>
       <c r="S315" s="61"/>
       <c r="U315" s="62"/>
       <c r="V315" s="62"/>
     </row>
-    <row r="316" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:29" customHeight="1" ht="15.75">
       <c r="P316" s="61"/>
       <c r="Q316" s="61"/>
       <c r="S316" s="61"/>
       <c r="U316" s="62"/>
       <c r="V316" s="62"/>
     </row>
-    <row r="317" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:29" customHeight="1" ht="15.75">
       <c r="P317" s="61"/>
       <c r="Q317" s="61"/>
       <c r="S317" s="61"/>
       <c r="U317" s="62"/>
       <c r="V317" s="62"/>
     </row>
-    <row r="318" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:29" customHeight="1" ht="15.75">
       <c r="P318" s="61"/>
       <c r="Q318" s="61"/>
       <c r="S318" s="61"/>
       <c r="U318" s="62"/>
       <c r="V318" s="62"/>
     </row>
-    <row r="319" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:29" customHeight="1" ht="15.75">
       <c r="P319" s="61"/>
       <c r="Q319" s="61"/>
       <c r="S319" s="61"/>
       <c r="U319" s="62"/>
       <c r="V319" s="62"/>
     </row>
-    <row r="320" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:29" customHeight="1" ht="15.75">
       <c r="P320" s="61"/>
       <c r="Q320" s="61"/>
       <c r="S320" s="61"/>
       <c r="U320" s="62"/>
       <c r="V320" s="62"/>
     </row>
-    <row r="321" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:29" customHeight="1" ht="15.75">
       <c r="P321" s="61"/>
       <c r="Q321" s="61"/>
       <c r="S321" s="61"/>
       <c r="U321" s="62"/>
       <c r="V321" s="62"/>
     </row>
-    <row r="322" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:29" customHeight="1" ht="15.75">
       <c r="P322" s="61"/>
       <c r="Q322" s="61"/>
       <c r="S322" s="61"/>
       <c r="U322" s="62"/>
       <c r="V322" s="62"/>
     </row>
-    <row r="323" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:29" customHeight="1" ht="15.75">
       <c r="P323" s="61"/>
       <c r="Q323" s="61"/>
       <c r="S323" s="61"/>
       <c r="U323" s="62"/>
       <c r="V323" s="62"/>
     </row>
-    <row r="324" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:29" customHeight="1" ht="15.75">
       <c r="P324" s="61"/>
       <c r="Q324" s="61"/>
       <c r="S324" s="61"/>
       <c r="U324" s="62"/>
       <c r="V324" s="62"/>
     </row>
-    <row r="325" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:29" customHeight="1" ht="15.75">
       <c r="P325" s="61"/>
       <c r="Q325" s="61"/>
       <c r="S325" s="61"/>
       <c r="U325" s="62"/>
       <c r="V325" s="62"/>
     </row>
-    <row r="326" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:29" customHeight="1" ht="15.75">
       <c r="P326" s="61"/>
       <c r="Q326" s="61"/>
       <c r="S326" s="61"/>
       <c r="U326" s="62"/>
       <c r="V326" s="62"/>
     </row>
-    <row r="327" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:29" customHeight="1" ht="15.75">
       <c r="P327" s="61"/>
       <c r="Q327" s="61"/>
       <c r="S327" s="61"/>
       <c r="U327" s="62"/>
       <c r="V327" s="62"/>
     </row>
-    <row r="328" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:29" customHeight="1" ht="15.75">
       <c r="P328" s="61"/>
       <c r="Q328" s="61"/>
       <c r="S328" s="61"/>
       <c r="U328" s="62"/>
       <c r="V328" s="62"/>
     </row>
-    <row r="329" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:29" customHeight="1" ht="15.75">
       <c r="P329" s="61"/>
       <c r="Q329" s="61"/>
       <c r="S329" s="61"/>
       <c r="U329" s="62"/>
       <c r="V329" s="62"/>
     </row>
-    <row r="330" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:29" customHeight="1" ht="15.75">
       <c r="P330" s="61"/>
       <c r="Q330" s="61"/>
       <c r="S330" s="61"/>
       <c r="U330" s="62"/>
       <c r="V330" s="62"/>
     </row>
-    <row r="331" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:29" customHeight="1" ht="15.75">
       <c r="P331" s="61"/>
       <c r="Q331" s="61"/>
       <c r="S331" s="61"/>
       <c r="U331" s="62"/>
       <c r="V331" s="62"/>
     </row>
-    <row r="332" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:29" customHeight="1" ht="15.75">
       <c r="P332" s="61"/>
       <c r="Q332" s="61"/>
       <c r="S332" s="61"/>
       <c r="U332" s="62"/>
       <c r="V332" s="62"/>
     </row>
-    <row r="333" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:29" customHeight="1" ht="15.75">
       <c r="P333" s="61"/>
       <c r="Q333" s="61"/>
       <c r="S333" s="61"/>
       <c r="U333" s="62"/>
       <c r="V333" s="62"/>
     </row>
-    <row r="334" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:29" customHeight="1" ht="15.75">
       <c r="P334" s="61"/>
       <c r="Q334" s="61"/>
       <c r="S334" s="61"/>
       <c r="U334" s="62"/>
       <c r="V334" s="62"/>
     </row>
-    <row r="335" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:29" customHeight="1" ht="15.75">
       <c r="P335" s="61"/>
       <c r="Q335" s="61"/>
       <c r="S335" s="61"/>
       <c r="U335" s="62"/>
       <c r="V335" s="62"/>
     </row>
-    <row r="336" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:29" customHeight="1" ht="15.75">
       <c r="P336" s="61"/>
       <c r="Q336" s="61"/>
       <c r="S336" s="61"/>
       <c r="U336" s="62"/>
       <c r="V336" s="62"/>
     </row>
-    <row r="337" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:29" customHeight="1" ht="15.75">
       <c r="P337" s="61"/>
       <c r="Q337" s="61"/>
       <c r="S337" s="61"/>
       <c r="U337" s="62"/>
       <c r="V337" s="62"/>
     </row>
-    <row r="338" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:29" customHeight="1" ht="15.75">
       <c r="P338" s="61"/>
       <c r="Q338" s="61"/>
       <c r="S338" s="61"/>
       <c r="U338" s="62"/>
       <c r="V338" s="62"/>
     </row>
-    <row r="339" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:29" customHeight="1" ht="15.75">
       <c r="P339" s="61"/>
       <c r="Q339" s="61"/>
       <c r="S339" s="61"/>
       <c r="U339" s="62"/>
       <c r="V339" s="62"/>
     </row>
-    <row r="340" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:29" customHeight="1" ht="15.75">
       <c r="P340" s="61"/>
       <c r="Q340" s="61"/>
       <c r="S340" s="61"/>
       <c r="U340" s="62"/>
       <c r="V340" s="62"/>
     </row>
-    <row r="341" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:29" customHeight="1" ht="15.75">
       <c r="P341" s="61"/>
       <c r="Q341" s="61"/>
       <c r="S341" s="61"/>
       <c r="U341" s="62"/>
       <c r="V341" s="62"/>
     </row>
-    <row r="342" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:29" customHeight="1" ht="15.75">
       <c r="P342" s="61"/>
       <c r="Q342" s="61"/>
       <c r="S342" s="61"/>
       <c r="U342" s="62"/>
       <c r="V342" s="62"/>
     </row>
-    <row r="343" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:29" customHeight="1" ht="15.75">
       <c r="P343" s="61"/>
       <c r="Q343" s="61"/>
       <c r="S343" s="61"/>
       <c r="U343" s="62"/>
       <c r="V343" s="62"/>
     </row>
-    <row r="344" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:29" customHeight="1" ht="15.75">
       <c r="P344" s="61"/>
       <c r="Q344" s="61"/>
       <c r="S344" s="61"/>
       <c r="U344" s="62"/>
       <c r="V344" s="62"/>
     </row>
-    <row r="345" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:29" customHeight="1" ht="15.75">
       <c r="P345" s="61"/>
       <c r="Q345" s="61"/>
       <c r="S345" s="61"/>
       <c r="U345" s="62"/>
       <c r="V345" s="62"/>
     </row>
-    <row r="346" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:29" customHeight="1" ht="15.75">
       <c r="P346" s="61"/>
       <c r="Q346" s="61"/>
       <c r="S346" s="61"/>
       <c r="U346" s="62"/>
       <c r="V346" s="62"/>
     </row>
-    <row r="347" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:29" customHeight="1" ht="15.75">
       <c r="P347" s="61"/>
       <c r="Q347" s="61"/>
       <c r="S347" s="61"/>
       <c r="U347" s="62"/>
       <c r="V347" s="62"/>
     </row>
-    <row r="348" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:29" customHeight="1" ht="15.75">
       <c r="P348" s="61"/>
       <c r="Q348" s="61"/>
       <c r="S348" s="61"/>
       <c r="U348" s="62"/>
       <c r="V348" s="62"/>
     </row>
-    <row r="349" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:29" customHeight="1" ht="15.75">
       <c r="P349" s="61"/>
       <c r="Q349" s="61"/>
       <c r="S349" s="61"/>
       <c r="U349" s="62"/>
       <c r="V349" s="62"/>
     </row>
-    <row r="350" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:29" customHeight="1" ht="15.75">
       <c r="P350" s="61"/>
       <c r="Q350" s="61"/>
       <c r="S350" s="61"/>
       <c r="U350" s="62"/>
       <c r="V350" s="62"/>
     </row>
-    <row r="351" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:29" customHeight="1" ht="15.75">
       <c r="P351" s="61"/>
       <c r="Q351" s="61"/>
       <c r="S351" s="61"/>
       <c r="U351" s="62"/>
       <c r="V351" s="62"/>
     </row>
-    <row r="352" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:29" customHeight="1" ht="15.75">
       <c r="P352" s="61"/>
       <c r="Q352" s="61"/>
       <c r="S352" s="61"/>
       <c r="U352" s="62"/>
       <c r="V352" s="62"/>
     </row>
-    <row r="353" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:29" customHeight="1" ht="15.75">
       <c r="P353" s="61"/>
       <c r="Q353" s="61"/>
       <c r="S353" s="61"/>
       <c r="U353" s="62"/>
       <c r="V353" s="62"/>
     </row>
-    <row r="354" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:29" customHeight="1" ht="15.75">
       <c r="P354" s="61"/>
       <c r="Q354" s="61"/>
       <c r="S354" s="61"/>
       <c r="U354" s="62"/>
       <c r="V354" s="62"/>
     </row>
-    <row r="355" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:29" customHeight="1" ht="15.75">
       <c r="P355" s="61"/>
       <c r="Q355" s="61"/>
       <c r="S355" s="61"/>
       <c r="U355" s="62"/>
       <c r="V355" s="62"/>
     </row>
-    <row r="356" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:29" customHeight="1" ht="15.75">
       <c r="P356" s="61"/>
       <c r="Q356" s="61"/>
       <c r="S356" s="61"/>
       <c r="U356" s="62"/>
       <c r="V356" s="62"/>
     </row>
-    <row r="357" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:29" customHeight="1" ht="15.75">
       <c r="P357" s="61"/>
       <c r="Q357" s="61"/>
       <c r="S357" s="61"/>
       <c r="U357" s="62"/>
       <c r="V357" s="62"/>
     </row>
-    <row r="358" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:29" customHeight="1" ht="15.75">
       <c r="P358" s="61"/>
       <c r="Q358" s="61"/>
       <c r="S358" s="61"/>
       <c r="U358" s="62"/>
       <c r="V358" s="62"/>
     </row>
-    <row r="359" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:29" customHeight="1" ht="15.75">
       <c r="P359" s="61"/>
       <c r="Q359" s="61"/>
       <c r="S359" s="61"/>
       <c r="U359" s="62"/>
       <c r="V359" s="62"/>
     </row>
-    <row r="360" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:29" customHeight="1" ht="15.75">
       <c r="P360" s="61"/>
       <c r="Q360" s="61"/>
       <c r="S360" s="61"/>
       <c r="U360" s="62"/>
       <c r="V360" s="62"/>
     </row>
-    <row r="361" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:29" customHeight="1" ht="15.75">
       <c r="P361" s="61"/>
       <c r="Q361" s="61"/>
       <c r="S361" s="61"/>
       <c r="U361" s="62"/>
       <c r="V361" s="62"/>
     </row>
-    <row r="362" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:29" customHeight="1" ht="15.75">
       <c r="P362" s="61"/>
       <c r="Q362" s="61"/>
       <c r="S362" s="61"/>
       <c r="U362" s="62"/>
       <c r="V362" s="62"/>
     </row>
-    <row r="363" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:29" customHeight="1" ht="15.75">
       <c r="P363" s="61"/>
       <c r="Q363" s="61"/>
       <c r="S363" s="61"/>
       <c r="U363" s="62"/>
       <c r="V363" s="62"/>
     </row>
-    <row r="364" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:29" customHeight="1" ht="15.75">
       <c r="P364" s="61"/>
       <c r="Q364" s="61"/>
       <c r="S364" s="61"/>
       <c r="U364" s="62"/>
       <c r="V364" s="62"/>
     </row>
-    <row r="365" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:29" customHeight="1" ht="15.75">
       <c r="P365" s="61"/>
       <c r="Q365" s="61"/>
       <c r="S365" s="61"/>
       <c r="U365" s="62"/>
       <c r="V365" s="62"/>
     </row>
-    <row r="366" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:29" customHeight="1" ht="15.75">
       <c r="P366" s="61"/>
       <c r="Q366" s="61"/>
       <c r="S366" s="61"/>
       <c r="U366" s="62"/>
       <c r="V366" s="62"/>
     </row>
-    <row r="367" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:29" customHeight="1" ht="15.75">
       <c r="P367" s="61"/>
       <c r="Q367" s="61"/>
       <c r="S367" s="61"/>
       <c r="U367" s="62"/>
       <c r="V367" s="62"/>
     </row>
-    <row r="368" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:29" customHeight="1" ht="15.75">
       <c r="P368" s="61"/>
       <c r="Q368" s="61"/>
       <c r="S368" s="61"/>
       <c r="U368" s="62"/>
       <c r="V368" s="62"/>
     </row>
-    <row r="369" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:29" customHeight="1" ht="15.75">
       <c r="P369" s="61"/>
       <c r="Q369" s="61"/>
       <c r="S369" s="61"/>
       <c r="U369" s="62"/>
       <c r="V369" s="62"/>
     </row>
-    <row r="370" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:29" customHeight="1" ht="15.75">
       <c r="P370" s="61"/>
       <c r="Q370" s="61"/>
       <c r="S370" s="61"/>
       <c r="U370" s="62"/>
       <c r="V370" s="62"/>
     </row>
-    <row r="371" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:29" customHeight="1" ht="15.75">
       <c r="P371" s="61"/>
       <c r="Q371" s="61"/>
       <c r="S371" s="61"/>
       <c r="U371" s="62"/>
       <c r="V371" s="62"/>
     </row>
-    <row r="372" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:29" customHeight="1" ht="15.75">
       <c r="P372" s="61"/>
       <c r="Q372" s="61"/>
       <c r="S372" s="61"/>
       <c r="U372" s="62"/>
       <c r="V372" s="62"/>
     </row>
-    <row r="373" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:29" customHeight="1" ht="15.75">
       <c r="P373" s="61"/>
       <c r="Q373" s="61"/>
       <c r="S373" s="61"/>
       <c r="U373" s="62"/>
       <c r="V373" s="62"/>
     </row>
-    <row r="374" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:29" customHeight="1" ht="15.75">
       <c r="P374" s="61"/>
       <c r="Q374" s="61"/>
       <c r="S374" s="61"/>
       <c r="U374" s="62"/>
       <c r="V374" s="62"/>
     </row>
-    <row r="375" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:29" customHeight="1" ht="15.75">
       <c r="P375" s="61"/>
       <c r="Q375" s="61"/>
       <c r="S375" s="61"/>
       <c r="U375" s="62"/>
       <c r="V375" s="62"/>
     </row>
-    <row r="376" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:29" customHeight="1" ht="15.75">
       <c r="P376" s="61"/>
       <c r="Q376" s="61"/>
       <c r="S376" s="61"/>
       <c r="U376" s="62"/>
       <c r="V376" s="62"/>
     </row>
-    <row r="377" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:29" customHeight="1" ht="15.75">
       <c r="P377" s="61"/>
       <c r="Q377" s="61"/>
       <c r="S377" s="61"/>
       <c r="U377" s="62"/>
       <c r="V377" s="62"/>
     </row>
-    <row r="378" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:29" customHeight="1" ht="15.75">
       <c r="P378" s="61"/>
       <c r="Q378" s="61"/>
       <c r="S378" s="61"/>
       <c r="U378" s="62"/>
       <c r="V378" s="62"/>
     </row>
-    <row r="379" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:29" customHeight="1" ht="15.75">
       <c r="P379" s="61"/>
       <c r="Q379" s="61"/>
       <c r="S379" s="61"/>
       <c r="U379" s="62"/>
       <c r="V379" s="62"/>
     </row>
-    <row r="380" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:29" customHeight="1" ht="15.75">
       <c r="P380" s="61"/>
       <c r="Q380" s="61"/>
       <c r="S380" s="61"/>
       <c r="U380" s="62"/>
       <c r="V380" s="62"/>
     </row>
-    <row r="381" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:29" customHeight="1" ht="15.75">
       <c r="P381" s="61"/>
       <c r="Q381" s="61"/>
       <c r="S381" s="61"/>
       <c r="U381" s="62"/>
       <c r="V381" s="62"/>
     </row>
-    <row r="382" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:29" customHeight="1" ht="15.75">
       <c r="P382" s="61"/>
       <c r="Q382" s="61"/>
       <c r="S382" s="61"/>
       <c r="U382" s="62"/>
       <c r="V382" s="62"/>
     </row>
-    <row r="383" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:29" customHeight="1" ht="15.75">
       <c r="P383" s="61"/>
       <c r="Q383" s="61"/>
       <c r="S383" s="61"/>
       <c r="U383" s="62"/>
       <c r="V383" s="62"/>
     </row>
-    <row r="384" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:29" customHeight="1" ht="15.75">
       <c r="P384" s="61"/>
       <c r="Q384" s="61"/>
       <c r="S384" s="61"/>
       <c r="U384" s="62"/>
       <c r="V384" s="62"/>
     </row>
-    <row r="385" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:29" customHeight="1" ht="15.75">
       <c r="P385" s="61"/>
       <c r="Q385" s="61"/>
       <c r="S385" s="61"/>
       <c r="U385" s="62"/>
       <c r="V385" s="62"/>
     </row>
-    <row r="386" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:29" customHeight="1" ht="15.75">
       <c r="P386" s="61"/>
       <c r="Q386" s="61"/>
       <c r="S386" s="61"/>
       <c r="U386" s="62"/>
       <c r="V386" s="62"/>
     </row>
-    <row r="387" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:29" customHeight="1" ht="15.75">
       <c r="P387" s="61"/>
       <c r="Q387" s="61"/>
       <c r="S387" s="61"/>
       <c r="U387" s="62"/>
       <c r="V387" s="62"/>
     </row>
-    <row r="388" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:29" customHeight="1" ht="15.75">
       <c r="P388" s="61"/>
       <c r="Q388" s="61"/>
       <c r="S388" s="61"/>
       <c r="U388" s="62"/>
       <c r="V388" s="62"/>
     </row>
-    <row r="389" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:29" customHeight="1" ht="15.75">
       <c r="P389" s="61"/>
       <c r="Q389" s="61"/>
       <c r="S389" s="61"/>
       <c r="U389" s="62"/>
       <c r="V389" s="62"/>
     </row>
-    <row r="390" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:29" customHeight="1" ht="15.75">
       <c r="P390" s="61"/>
       <c r="Q390" s="61"/>
       <c r="S390" s="61"/>
       <c r="U390" s="62"/>
       <c r="V390" s="62"/>
     </row>
-    <row r="391" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:29" customHeight="1" ht="15.75">
       <c r="P391" s="61"/>
       <c r="Q391" s="61"/>
       <c r="S391" s="61"/>
       <c r="U391" s="62"/>
       <c r="V391" s="62"/>
     </row>
-    <row r="392" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:29" customHeight="1" ht="15.75">
       <c r="P392" s="61"/>
       <c r="Q392" s="61"/>
       <c r="S392" s="61"/>
       <c r="U392" s="62"/>
       <c r="V392" s="62"/>
     </row>
-    <row r="393" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:29" customHeight="1" ht="15.75">
       <c r="P393" s="61"/>
       <c r="Q393" s="61"/>
       <c r="S393" s="61"/>
       <c r="U393" s="62"/>
       <c r="V393" s="62"/>
     </row>
-    <row r="394" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:29" customHeight="1" ht="15.75">
       <c r="P394" s="61"/>
       <c r="Q394" s="61"/>
       <c r="S394" s="61"/>
       <c r="U394" s="62"/>
       <c r="V394" s="62"/>
     </row>
-    <row r="395" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:29" customHeight="1" ht="15.75">
       <c r="P395" s="61"/>
       <c r="Q395" s="61"/>
       <c r="S395" s="61"/>
       <c r="U395" s="62"/>
       <c r="V395" s="62"/>
     </row>
-    <row r="396" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:29" customHeight="1" ht="15.75">
       <c r="P396" s="61"/>
       <c r="Q396" s="61"/>
       <c r="S396" s="61"/>
       <c r="U396" s="62"/>
       <c r="V396" s="62"/>
     </row>
-    <row r="397" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:29" customHeight="1" ht="15.75">
       <c r="P397" s="61"/>
       <c r="Q397" s="61"/>
       <c r="S397" s="61"/>
       <c r="U397" s="62"/>
       <c r="V397" s="62"/>
     </row>
-    <row r="398" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:29" customHeight="1" ht="15.75">
       <c r="P398" s="61"/>
       <c r="Q398" s="61"/>
       <c r="S398" s="61"/>
       <c r="U398" s="62"/>
       <c r="V398" s="62"/>
     </row>
-    <row r="399" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:29" customHeight="1" ht="15.75">
       <c r="P399" s="61"/>
       <c r="Q399" s="61"/>
       <c r="S399" s="61"/>
       <c r="U399" s="62"/>
       <c r="V399" s="62"/>
     </row>
-    <row r="400" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:29" customHeight="1" ht="15.75">
       <c r="P400" s="61"/>
       <c r="Q400" s="61"/>
       <c r="S400" s="61"/>
       <c r="U400" s="62"/>
       <c r="V400" s="62"/>
     </row>
-    <row r="401" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:29" customHeight="1" ht="15.75">
       <c r="P401" s="61"/>
       <c r="Q401" s="61"/>
       <c r="S401" s="61"/>
       <c r="U401" s="62"/>
       <c r="V401" s="62"/>
     </row>
-    <row r="402" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:29" customHeight="1" ht="15.75">
       <c r="P402" s="61"/>
       <c r="Q402" s="61"/>
       <c r="S402" s="61"/>
       <c r="U402" s="62"/>
       <c r="V402" s="62"/>
     </row>
-    <row r="403" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:29" customHeight="1" ht="15.75">
       <c r="P403" s="61"/>
       <c r="Q403" s="61"/>
       <c r="S403" s="61"/>
       <c r="U403" s="62"/>
       <c r="V403" s="62"/>
     </row>
-    <row r="404" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:29" customHeight="1" ht="15.75">
       <c r="P404" s="61"/>
       <c r="Q404" s="61"/>
       <c r="S404" s="61"/>
       <c r="U404" s="62"/>
       <c r="V404" s="62"/>
     </row>
-    <row r="405" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:29" customHeight="1" ht="15.75">
       <c r="P405" s="61"/>
       <c r="Q405" s="61"/>
       <c r="S405" s="61"/>
       <c r="U405" s="62"/>
       <c r="V405" s="62"/>
     </row>
-    <row r="406" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:29" customHeight="1" ht="15.75">
       <c r="P406" s="61"/>
       <c r="Q406" s="61"/>
       <c r="S406" s="61"/>
       <c r="U406" s="62"/>
       <c r="V406" s="62"/>
     </row>
-    <row r="407" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:29" customHeight="1" ht="15.75">
       <c r="P407" s="61"/>
       <c r="Q407" s="61"/>
       <c r="S407" s="61"/>
       <c r="U407" s="62"/>
       <c r="V407" s="62"/>
     </row>
-    <row r="408" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:29" customHeight="1" ht="15.75">
       <c r="P408" s="61"/>
       <c r="Q408" s="61"/>
       <c r="S408" s="61"/>
       <c r="U408" s="62"/>
       <c r="V408" s="62"/>
     </row>
-    <row r="409" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:29" customHeight="1" ht="15.75">
       <c r="P409" s="61"/>
       <c r="Q409" s="61"/>
       <c r="S409" s="61"/>
       <c r="U409" s="62"/>
       <c r="V409" s="62"/>
     </row>
-    <row r="410" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:29" customHeight="1" ht="15.75">
       <c r="P410" s="61"/>
       <c r="Q410" s="61"/>
       <c r="S410" s="61"/>
       <c r="U410" s="62"/>
       <c r="V410" s="62"/>
     </row>
-    <row r="411" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:29" customHeight="1" ht="15.75">
       <c r="P411" s="61"/>
       <c r="Q411" s="61"/>
       <c r="S411" s="61"/>
       <c r="U411" s="62"/>
       <c r="V411" s="62"/>
     </row>
-    <row r="412" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:29" customHeight="1" ht="15.75">
       <c r="P412" s="61"/>
       <c r="Q412" s="61"/>
       <c r="S412" s="61"/>
       <c r="U412" s="62"/>
       <c r="V412" s="62"/>
     </row>
-    <row r="413" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:29" customHeight="1" ht="15.75">
       <c r="P413" s="61"/>
       <c r="Q413" s="61"/>
       <c r="S413" s="61"/>
       <c r="U413" s="62"/>
       <c r="V413" s="62"/>
     </row>
-    <row r="414" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:29" customHeight="1" ht="15.75">
       <c r="P414" s="61"/>
       <c r="Q414" s="61"/>
       <c r="S414" s="61"/>
       <c r="U414" s="62"/>
       <c r="V414" s="62"/>
     </row>
-    <row r="415" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:29" customHeight="1" ht="15.75">
       <c r="P415" s="61"/>
       <c r="Q415" s="61"/>
       <c r="S415" s="61"/>
       <c r="U415" s="62"/>
       <c r="V415" s="62"/>
     </row>
-    <row r="416" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:29" customHeight="1" ht="15.75">
       <c r="P416" s="61"/>
       <c r="Q416" s="61"/>
       <c r="S416" s="61"/>
       <c r="U416" s="62"/>
       <c r="V416" s="62"/>
     </row>
-    <row r="417" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:29" customHeight="1" ht="15.75">
       <c r="P417" s="61"/>
       <c r="Q417" s="61"/>
       <c r="S417" s="61"/>
       <c r="U417" s="62"/>
       <c r="V417" s="62"/>
     </row>
-    <row r="418" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:29" customHeight="1" ht="15.75">
       <c r="P418" s="61"/>
       <c r="Q418" s="61"/>
       <c r="S418" s="61"/>
       <c r="U418" s="62"/>
       <c r="V418" s="62"/>
     </row>
-    <row r="419" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:29" customHeight="1" ht="15.75">
       <c r="P419" s="61"/>
       <c r="Q419" s="61"/>
       <c r="S419" s="61"/>
       <c r="U419" s="62"/>
       <c r="V419" s="62"/>
     </row>
-    <row r="420" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:29" customHeight="1" ht="15.75">
       <c r="P420" s="61"/>
       <c r="Q420" s="61"/>
       <c r="S420" s="61"/>
       <c r="U420" s="62"/>
       <c r="V420" s="62"/>
     </row>
-    <row r="421" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:29" customHeight="1" ht="15.75">
       <c r="P421" s="61"/>
       <c r="Q421" s="61"/>
       <c r="S421" s="61"/>
       <c r="U421" s="62"/>
       <c r="V421" s="62"/>
     </row>
-    <row r="422" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:29" customHeight="1" ht="15.75">
       <c r="P422" s="61"/>
       <c r="Q422" s="61"/>
       <c r="S422" s="61"/>
       <c r="U422" s="62"/>
       <c r="V422" s="62"/>
     </row>
-    <row r="423" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:29" customHeight="1" ht="15.75">
       <c r="P423" s="61"/>
       <c r="Q423" s="61"/>
       <c r="S423" s="61"/>
       <c r="U423" s="62"/>
       <c r="V423" s="62"/>
     </row>
-    <row r="424" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:29" customHeight="1" ht="15.75">
       <c r="P424" s="61"/>
       <c r="Q424" s="61"/>
       <c r="S424" s="61"/>
       <c r="U424" s="62"/>
       <c r="V424" s="62"/>
     </row>
-    <row r="425" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:29" customHeight="1" ht="15.75">
       <c r="P425" s="61"/>
       <c r="Q425" s="61"/>
       <c r="S425" s="61"/>
       <c r="U425" s="62"/>
       <c r="V425" s="62"/>
     </row>
-    <row r="426" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:29" customHeight="1" ht="15.75">
       <c r="P426" s="61"/>
       <c r="Q426" s="61"/>
       <c r="S426" s="61"/>
       <c r="U426" s="62"/>
       <c r="V426" s="62"/>
     </row>
-    <row r="427" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:29" customHeight="1" ht="15.75">
       <c r="P427" s="61"/>
       <c r="Q427" s="61"/>
       <c r="S427" s="61"/>
       <c r="U427" s="62"/>
       <c r="V427" s="62"/>
     </row>
-    <row r="428" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:29" customHeight="1" ht="15.75">
       <c r="P428" s="61"/>
       <c r="Q428" s="61"/>
       <c r="S428" s="61"/>
       <c r="U428" s="62"/>
       <c r="V428" s="62"/>
     </row>
-    <row r="429" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:29" customHeight="1" ht="15.75">
       <c r="P429" s="61"/>
       <c r="Q429" s="61"/>
       <c r="S429" s="61"/>
       <c r="U429" s="62"/>
       <c r="V429" s="62"/>
     </row>
-    <row r="430" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:29" customHeight="1" ht="15.75">
       <c r="P430" s="61"/>
       <c r="Q430" s="61"/>
       <c r="S430" s="61"/>
       <c r="U430" s="62"/>
       <c r="V430" s="62"/>
     </row>
-    <row r="431" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:29" customHeight="1" ht="15.75">
       <c r="P431" s="61"/>
       <c r="Q431" s="61"/>
       <c r="S431" s="61"/>
       <c r="U431" s="62"/>
       <c r="V431" s="62"/>
     </row>
-    <row r="432" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:29" customHeight="1" ht="15.75">
       <c r="P432" s="61"/>
       <c r="Q432" s="61"/>
       <c r="S432" s="61"/>
       <c r="U432" s="62"/>
       <c r="V432" s="62"/>
     </row>
-    <row r="433" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:29" customHeight="1" ht="15.75">
       <c r="P433" s="61"/>
       <c r="Q433" s="61"/>
       <c r="S433" s="61"/>
       <c r="U433" s="62"/>
       <c r="V433" s="62"/>
     </row>
-    <row r="434" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:29" customHeight="1" ht="15.75">
       <c r="P434" s="61"/>
       <c r="Q434" s="61"/>
       <c r="S434" s="61"/>
       <c r="U434" s="62"/>
       <c r="V434" s="62"/>
     </row>
-    <row r="435" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:29" customHeight="1" ht="15.75">
       <c r="P435" s="61"/>
       <c r="Q435" s="61"/>
       <c r="S435" s="61"/>
       <c r="U435" s="62"/>
       <c r="V435" s="62"/>
     </row>
-    <row r="436" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:29" customHeight="1" ht="15.75">
       <c r="P436" s="61"/>
       <c r="Q436" s="61"/>
       <c r="S436" s="61"/>
       <c r="U436" s="62"/>
       <c r="V436" s="62"/>
     </row>
-    <row r="437" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:29" customHeight="1" ht="15.75">
       <c r="P437" s="61"/>
       <c r="Q437" s="61"/>
       <c r="S437" s="61"/>
       <c r="U437" s="62"/>
       <c r="V437" s="62"/>
     </row>
-    <row r="438" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:29" customHeight="1" ht="15.75">
       <c r="P438" s="61"/>
       <c r="Q438" s="61"/>
       <c r="S438" s="61"/>
       <c r="U438" s="62"/>
       <c r="V438" s="62"/>
     </row>
-    <row r="439" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:29" customHeight="1" ht="15.75">
       <c r="P439" s="61"/>
       <c r="Q439" s="61"/>
       <c r="S439" s="61"/>
       <c r="U439" s="62"/>
       <c r="V439" s="62"/>
     </row>
-    <row r="440" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:29" customHeight="1" ht="15.75">
       <c r="P440" s="61"/>
       <c r="Q440" s="61"/>
       <c r="S440" s="61"/>
       <c r="U440" s="62"/>
       <c r="V440" s="62"/>
     </row>
-    <row r="441" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:29" customHeight="1" ht="15.75">
       <c r="P441" s="61"/>
       <c r="Q441" s="61"/>
       <c r="S441" s="61"/>
       <c r="U441" s="62"/>
       <c r="V441" s="62"/>
     </row>
-    <row r="442" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:29" customHeight="1" ht="15.75">
       <c r="P442" s="61"/>
       <c r="Q442" s="61"/>
       <c r="S442" s="61"/>
       <c r="U442" s="62"/>
       <c r="V442" s="62"/>
     </row>
-    <row r="443" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:29" customHeight="1" ht="15.75">
       <c r="P443" s="61"/>
       <c r="Q443" s="61"/>
       <c r="S443" s="61"/>
       <c r="U443" s="62"/>
       <c r="V443" s="62"/>
     </row>
-    <row r="444" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:29" customHeight="1" ht="15.75">
       <c r="P444" s="61"/>
       <c r="Q444" s="61"/>
       <c r="S444" s="61"/>
       <c r="U444" s="62"/>
       <c r="V444" s="62"/>
     </row>
-    <row r="445" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:29" customHeight="1" ht="15.75">
       <c r="P445" s="61"/>
       <c r="Q445" s="61"/>
       <c r="S445" s="61"/>
       <c r="U445" s="62"/>
       <c r="V445" s="62"/>
     </row>
-    <row r="446" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:29" customHeight="1" ht="15.75">
       <c r="P446" s="61"/>
       <c r="Q446" s="61"/>
       <c r="S446" s="61"/>
       <c r="U446" s="62"/>
       <c r="V446" s="62"/>
     </row>
-    <row r="447" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:29" customHeight="1" ht="15.75">
       <c r="P447" s="61"/>
       <c r="Q447" s="61"/>
       <c r="S447" s="61"/>
       <c r="U447" s="62"/>
       <c r="V447" s="62"/>
     </row>
-    <row r="448" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:29" customHeight="1" ht="15.75">
       <c r="P448" s="61"/>
       <c r="Q448" s="61"/>
       <c r="S448" s="61"/>
       <c r="U448" s="62"/>
       <c r="V448" s="62"/>
     </row>
-    <row r="449" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:29" customHeight="1" ht="15.75">
       <c r="P449" s="61"/>
       <c r="Q449" s="61"/>
       <c r="S449" s="61"/>
       <c r="U449" s="62"/>
       <c r="V449" s="62"/>
     </row>
-    <row r="450" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:29" customHeight="1" ht="15.75">
       <c r="P450" s="61"/>
       <c r="Q450" s="61"/>
       <c r="S450" s="61"/>
       <c r="U450" s="62"/>
       <c r="V450" s="62"/>
     </row>
-    <row r="451" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:29" customHeight="1" ht="15.75">
       <c r="P451" s="61"/>
       <c r="Q451" s="61"/>
       <c r="S451" s="61"/>
       <c r="U451" s="62"/>
       <c r="V451" s="62"/>
     </row>
-    <row r="452" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:29" customHeight="1" ht="15.75">
       <c r="P452" s="61"/>
       <c r="Q452" s="61"/>
       <c r="S452" s="61"/>
       <c r="U452" s="62"/>
       <c r="V452" s="62"/>
     </row>
-    <row r="453" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:29" customHeight="1" ht="15.75">
       <c r="P453" s="61"/>
       <c r="Q453" s="61"/>
       <c r="S453" s="61"/>
       <c r="U453" s="62"/>
       <c r="V453" s="62"/>
     </row>
-    <row r="454" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:29" customHeight="1" ht="15.75">
       <c r="P454" s="61"/>
       <c r="Q454" s="61"/>
       <c r="S454" s="61"/>
       <c r="U454" s="62"/>
       <c r="V454" s="62"/>
     </row>
-    <row r="455" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:29" customHeight="1" ht="15.75">
       <c r="P455" s="61"/>
       <c r="Q455" s="61"/>
       <c r="S455" s="61"/>
       <c r="U455" s="62"/>
       <c r="V455" s="62"/>
     </row>
-    <row r="456" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:29" customHeight="1" ht="15.75">
       <c r="P456" s="61"/>
       <c r="Q456" s="61"/>
       <c r="S456" s="61"/>
       <c r="U456" s="62"/>
       <c r="V456" s="62"/>
     </row>
-    <row r="457" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:29" customHeight="1" ht="15.75">
       <c r="P457" s="61"/>
       <c r="Q457" s="61"/>
       <c r="S457" s="61"/>
       <c r="U457" s="62"/>
       <c r="V457" s="62"/>
     </row>
-    <row r="458" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:29" customHeight="1" ht="15.75">
       <c r="P458" s="61"/>
       <c r="Q458" s="61"/>
       <c r="S458" s="61"/>
       <c r="U458" s="62"/>
       <c r="V458" s="62"/>
     </row>
-    <row r="459" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:29" customHeight="1" ht="15.75">
       <c r="P459" s="61"/>
       <c r="Q459" s="61"/>
       <c r="S459" s="61"/>
       <c r="U459" s="62"/>
       <c r="V459" s="62"/>
     </row>
-    <row r="460" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:29" customHeight="1" ht="15.75">
       <c r="P460" s="61"/>
       <c r="Q460" s="61"/>
       <c r="S460" s="61"/>
       <c r="U460" s="62"/>
       <c r="V460" s="62"/>
     </row>
-    <row r="461" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:29" customHeight="1" ht="15.75">
       <c r="P461" s="61"/>
       <c r="Q461" s="61"/>
       <c r="S461" s="61"/>
       <c r="U461" s="62"/>
       <c r="V461" s="62"/>
     </row>
-    <row r="462" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:29" customHeight="1" ht="15.75">
       <c r="P462" s="61"/>
       <c r="Q462" s="61"/>
       <c r="S462" s="61"/>
       <c r="U462" s="62"/>
       <c r="V462" s="62"/>
     </row>
-    <row r="463" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:29" customHeight="1" ht="15.75">
       <c r="P463" s="61"/>
       <c r="Q463" s="61"/>
       <c r="S463" s="61"/>
       <c r="U463" s="62"/>
       <c r="V463" s="62"/>
     </row>
-    <row r="464" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:29" customHeight="1" ht="15.75">
       <c r="P464" s="61"/>
       <c r="Q464" s="61"/>
       <c r="S464" s="61"/>
       <c r="U464" s="62"/>
       <c r="V464" s="62"/>
     </row>
-    <row r="465" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:29" customHeight="1" ht="15.75">
       <c r="P465" s="61"/>
       <c r="Q465" s="61"/>
       <c r="S465" s="61"/>
       <c r="U465" s="62"/>
       <c r="V465" s="62"/>
     </row>
-    <row r="466" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:29" customHeight="1" ht="15.75">
       <c r="P466" s="61"/>
       <c r="Q466" s="61"/>
       <c r="S466" s="61"/>
       <c r="U466" s="62"/>
       <c r="V466" s="62"/>
     </row>
-    <row r="467" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:29" customHeight="1" ht="15.75">
       <c r="P467" s="61"/>
       <c r="Q467" s="61"/>
       <c r="S467" s="61"/>
       <c r="U467" s="62"/>
       <c r="V467" s="62"/>
     </row>
-    <row r="468" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:29" customHeight="1" ht="15.75">
       <c r="P468" s="61"/>
       <c r="Q468" s="61"/>
       <c r="S468" s="61"/>
       <c r="U468" s="62"/>
       <c r="V468" s="62"/>
     </row>
-    <row r="469" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:29" customHeight="1" ht="15.75">
       <c r="P469" s="61"/>
       <c r="Q469" s="61"/>
       <c r="S469" s="61"/>
       <c r="U469" s="62"/>
       <c r="V469" s="62"/>
     </row>
-    <row r="470" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:29" customHeight="1" ht="15.75">
       <c r="P470" s="61"/>
       <c r="Q470" s="61"/>
       <c r="S470" s="61"/>
       <c r="U470" s="62"/>
       <c r="V470" s="62"/>
     </row>
-    <row r="471" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:29" customHeight="1" ht="15.75">
       <c r="P471" s="61"/>
       <c r="Q471" s="61"/>
       <c r="S471" s="61"/>
       <c r="U471" s="62"/>
       <c r="V471" s="62"/>
     </row>
-    <row r="472" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:29" customHeight="1" ht="15.75">
       <c r="P472" s="61"/>
       <c r="Q472" s="61"/>
       <c r="S472" s="61"/>
       <c r="U472" s="62"/>
       <c r="V472" s="62"/>
     </row>
-    <row r="473" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:29" customHeight="1" ht="15.75">
       <c r="P473" s="61"/>
       <c r="Q473" s="61"/>
       <c r="S473" s="61"/>
       <c r="U473" s="62"/>
       <c r="V473" s="62"/>
     </row>
-    <row r="474" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:29" customHeight="1" ht="15.75">
       <c r="P474" s="61"/>
       <c r="Q474" s="61"/>
       <c r="S474" s="61"/>
       <c r="U474" s="62"/>
       <c r="V474" s="62"/>
     </row>
-    <row r="475" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:29" customHeight="1" ht="15.75">
       <c r="P475" s="61"/>
       <c r="Q475" s="61"/>
       <c r="S475" s="61"/>
       <c r="U475" s="62"/>
       <c r="V475" s="62"/>
     </row>
-    <row r="476" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:29" customHeight="1" ht="15.75">
       <c r="P476" s="61"/>
       <c r="Q476" s="61"/>
       <c r="S476" s="61"/>
       <c r="U476" s="62"/>
       <c r="V476" s="62"/>
     </row>
-    <row r="477" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:29" customHeight="1" ht="15.75">
       <c r="P477" s="61"/>
       <c r="Q477" s="61"/>
       <c r="S477" s="61"/>
       <c r="U477" s="62"/>
       <c r="V477" s="62"/>
     </row>
-    <row r="478" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:29" customHeight="1" ht="15.75">
       <c r="P478" s="61"/>
       <c r="Q478" s="61"/>
       <c r="S478" s="61"/>
       <c r="U478" s="62"/>
       <c r="V478" s="62"/>
     </row>
-    <row r="479" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:29" customHeight="1" ht="15.75">
       <c r="P479" s="61"/>
       <c r="Q479" s="61"/>
       <c r="S479" s="61"/>
       <c r="U479" s="62"/>
       <c r="V479" s="62"/>
     </row>
-    <row r="480" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:29" customHeight="1" ht="15.75">
       <c r="P480" s="61"/>
       <c r="Q480" s="61"/>
       <c r="S480" s="61"/>
       <c r="U480" s="62"/>
       <c r="V480" s="62"/>
     </row>
-    <row r="481" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:29" customHeight="1" ht="15.75">
       <c r="P481" s="61"/>
       <c r="Q481" s="61"/>
       <c r="S481" s="61"/>
       <c r="U481" s="62"/>
       <c r="V481" s="62"/>
     </row>
-    <row r="482" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:29" customHeight="1" ht="15.75">
       <c r="P482" s="61"/>
       <c r="Q482" s="61"/>
       <c r="S482" s="61"/>
       <c r="U482" s="62"/>
       <c r="V482" s="62"/>
     </row>
-    <row r="483" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:29" customHeight="1" ht="15.75">
       <c r="P483" s="61"/>
       <c r="Q483" s="61"/>
       <c r="S483" s="61"/>
       <c r="U483" s="62"/>
       <c r="V483" s="62"/>
     </row>
-    <row r="484" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:29" customHeight="1" ht="15.75">
       <c r="P484" s="61"/>
       <c r="Q484" s="61"/>
       <c r="S484" s="61"/>
       <c r="U484" s="62"/>
       <c r="V484" s="62"/>
     </row>
-    <row r="485" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:29" customHeight="1" ht="15.75">
       <c r="P485" s="61"/>
       <c r="Q485" s="61"/>
       <c r="S485" s="61"/>
       <c r="U485" s="62"/>
       <c r="V485" s="62"/>
     </row>
-    <row r="486" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:29" customHeight="1" ht="15.75">
       <c r="P486" s="61"/>
       <c r="Q486" s="61"/>
       <c r="S486" s="61"/>
       <c r="U486" s="62"/>
       <c r="V486" s="62"/>
     </row>
-    <row r="487" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:29" customHeight="1" ht="15.75">
       <c r="P487" s="61"/>
       <c r="Q487" s="61"/>
       <c r="S487" s="61"/>
       <c r="U487" s="62"/>
       <c r="V487" s="62"/>
     </row>
-    <row r="488" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:29" customHeight="1" ht="15.75">
       <c r="P488" s="61"/>
       <c r="Q488" s="61"/>
       <c r="S488" s="61"/>
       <c r="U488" s="62"/>
       <c r="V488" s="62"/>
     </row>
-    <row r="489" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:29" customHeight="1" ht="15.75">
       <c r="P489" s="61"/>
       <c r="Q489" s="61"/>
       <c r="S489" s="61"/>
       <c r="U489" s="62"/>
       <c r="V489" s="62"/>
     </row>
-    <row r="490" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:29" customHeight="1" ht="15.75">
       <c r="P490" s="61"/>
       <c r="Q490" s="61"/>
       <c r="S490" s="61"/>
       <c r="U490" s="62"/>
       <c r="V490" s="62"/>
     </row>
-    <row r="491" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:29" customHeight="1" ht="15.75">
       <c r="P491" s="61"/>
       <c r="Q491" s="61"/>
       <c r="S491" s="61"/>
       <c r="U491" s="62"/>
       <c r="V491" s="62"/>
     </row>
-    <row r="492" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:29" customHeight="1" ht="15.75">
       <c r="P492" s="61"/>
       <c r="Q492" s="61"/>
       <c r="S492" s="61"/>
       <c r="U492" s="62"/>
       <c r="V492" s="62"/>
     </row>
-    <row r="493" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:29" customHeight="1" ht="15.75">
       <c r="P493" s="61"/>
       <c r="Q493" s="61"/>
       <c r="S493" s="61"/>
       <c r="U493" s="62"/>
       <c r="V493" s="62"/>
     </row>
-    <row r="494" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:29" customHeight="1" ht="15.75">
       <c r="P494" s="61"/>
       <c r="Q494" s="61"/>
       <c r="S494" s="61"/>
       <c r="U494" s="62"/>
       <c r="V494" s="62"/>
     </row>
-    <row r="495" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:29" customHeight="1" ht="15.75">
       <c r="P495" s="61"/>
       <c r="Q495" s="61"/>
       <c r="S495" s="61"/>
       <c r="U495" s="62"/>
       <c r="V495" s="62"/>
     </row>
-    <row r="496" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:29" customHeight="1" ht="15.75">
       <c r="P496" s="61"/>
       <c r="Q496" s="61"/>
       <c r="S496" s="61"/>
       <c r="U496" s="62"/>
       <c r="V496" s="62"/>
     </row>
-    <row r="497" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:29" customHeight="1" ht="15.75">
       <c r="P497" s="61"/>
       <c r="Q497" s="61"/>
       <c r="S497" s="61"/>
       <c r="U497" s="62"/>
       <c r="V497" s="62"/>
     </row>
-    <row r="498" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:29" customHeight="1" ht="15.75">
       <c r="P498" s="61"/>
       <c r="Q498" s="61"/>
       <c r="S498" s="61"/>
       <c r="U498" s="62"/>
       <c r="V498" s="62"/>
     </row>
-    <row r="499" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:29" customHeight="1" ht="15.75">
       <c r="P499" s="61"/>
       <c r="Q499" s="61"/>
       <c r="S499" s="61"/>
       <c r="U499" s="62"/>
       <c r="V499" s="62"/>
     </row>
-    <row r="500" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:29" customHeight="1" ht="15.75">
       <c r="P500" s="61"/>
       <c r="Q500" s="61"/>
       <c r="S500" s="61"/>
       <c r="U500" s="62"/>
       <c r="V500" s="62"/>
     </row>
-    <row r="501" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:29" customHeight="1" ht="15.75">
       <c r="P501" s="61"/>
       <c r="Q501" s="61"/>
       <c r="S501" s="61"/>
       <c r="U501" s="62"/>
       <c r="V501" s="62"/>
     </row>
-    <row r="502" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:29" customHeight="1" ht="15.75">
       <c r="P502" s="61"/>
       <c r="Q502" s="61"/>
       <c r="S502" s="61"/>
       <c r="U502" s="62"/>
       <c r="V502" s="62"/>
     </row>
-    <row r="503" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:29" customHeight="1" ht="15.75">
       <c r="P503" s="61"/>
       <c r="Q503" s="61"/>
       <c r="S503" s="61"/>
       <c r="U503" s="62"/>
       <c r="V503" s="62"/>
     </row>
-    <row r="504" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:29" customHeight="1" ht="15.75">
       <c r="P504" s="61"/>
       <c r="Q504" s="61"/>
       <c r="S504" s="61"/>
       <c r="U504" s="62"/>
       <c r="V504" s="62"/>
     </row>
-    <row r="505" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:29" customHeight="1" ht="15.75">
       <c r="P505" s="61"/>
       <c r="Q505" s="61"/>
       <c r="S505" s="61"/>
       <c r="U505" s="62"/>
       <c r="V505" s="62"/>
     </row>
-    <row r="506" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:29" customHeight="1" ht="15.75">
       <c r="P506" s="61"/>
       <c r="Q506" s="61"/>
       <c r="S506" s="61"/>
       <c r="U506" s="62"/>
       <c r="V506" s="62"/>
     </row>
-    <row r="507" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:29" customHeight="1" ht="15.75">
       <c r="P507" s="61"/>
       <c r="Q507" s="61"/>
       <c r="S507" s="61"/>
       <c r="U507" s="62"/>
       <c r="V507" s="62"/>
     </row>
-    <row r="508" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:29" customHeight="1" ht="15.75">
       <c r="P508" s="61"/>
       <c r="Q508" s="61"/>
       <c r="S508" s="61"/>
       <c r="U508" s="62"/>
       <c r="V508" s="62"/>
     </row>
-    <row r="509" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:29" customHeight="1" ht="15.75">
       <c r="P509" s="61"/>
       <c r="Q509" s="61"/>
       <c r="S509" s="61"/>
       <c r="U509" s="62"/>
       <c r="V509" s="62"/>
     </row>
-    <row r="510" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:29" customHeight="1" ht="15.75">
       <c r="P510" s="61"/>
       <c r="Q510" s="61"/>
       <c r="S510" s="61"/>
       <c r="U510" s="62"/>
       <c r="V510" s="62"/>
     </row>
-    <row r="511" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:29" customHeight="1" ht="15.75">
       <c r="P511" s="61"/>
       <c r="Q511" s="61"/>
       <c r="S511" s="61"/>
       <c r="U511" s="62"/>
       <c r="V511" s="62"/>
     </row>
-    <row r="512" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:29" customHeight="1" ht="15.75">
       <c r="P512" s="61"/>
       <c r="Q512" s="61"/>
       <c r="S512" s="61"/>
       <c r="U512" s="62"/>
       <c r="V512" s="62"/>
     </row>
-    <row r="513" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:29" customHeight="1" ht="15.75">
       <c r="P513" s="61"/>
       <c r="Q513" s="61"/>
       <c r="S513" s="61"/>
       <c r="U513" s="62"/>
       <c r="V513" s="62"/>
     </row>
-    <row r="514" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:29" customHeight="1" ht="15.75">
       <c r="P514" s="61"/>
       <c r="Q514" s="61"/>
       <c r="S514" s="61"/>
       <c r="U514" s="62"/>
       <c r="V514" s="62"/>
     </row>
-    <row r="515" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:29" customHeight="1" ht="15.75">
       <c r="P515" s="61"/>
       <c r="Q515" s="61"/>
       <c r="S515" s="61"/>
       <c r="U515" s="62"/>
       <c r="V515" s="62"/>
     </row>
-    <row r="516" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:29" customHeight="1" ht="15.75">
       <c r="P516" s="61"/>
       <c r="Q516" s="61"/>
       <c r="S516" s="61"/>
       <c r="U516" s="62"/>
       <c r="V516" s="62"/>
     </row>
-    <row r="517" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:29" customHeight="1" ht="15.75">
       <c r="P517" s="61"/>
       <c r="Q517" s="61"/>
       <c r="S517" s="61"/>
       <c r="U517" s="62"/>
       <c r="V517" s="62"/>
     </row>
-    <row r="518" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:29" customHeight="1" ht="15.75">
       <c r="P518" s="61"/>
       <c r="Q518" s="61"/>
       <c r="S518" s="61"/>
       <c r="U518" s="62"/>
       <c r="V518" s="62"/>
     </row>
-    <row r="519" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:29" customHeight="1" ht="15.75">
       <c r="P519" s="61"/>
       <c r="Q519" s="61"/>
       <c r="S519" s="61"/>
       <c r="U519" s="62"/>
       <c r="V519" s="62"/>
     </row>
-    <row r="520" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:29" customHeight="1" ht="15.75">
       <c r="P520" s="61"/>
       <c r="Q520" s="61"/>
       <c r="S520" s="61"/>
       <c r="U520" s="62"/>
       <c r="V520" s="62"/>
     </row>
-    <row r="521" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:29" customHeight="1" ht="15.75">
       <c r="P521" s="61"/>
       <c r="Q521" s="61"/>
       <c r="S521" s="61"/>
       <c r="U521" s="62"/>
       <c r="V521" s="62"/>
     </row>
-    <row r="522" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:29" customHeight="1" ht="15.75">
       <c r="P522" s="61"/>
       <c r="Q522" s="61"/>
       <c r="S522" s="61"/>
       <c r="U522" s="62"/>
       <c r="V522" s="62"/>
     </row>
-    <row r="523" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:29" customHeight="1" ht="15.75">
       <c r="P523" s="61"/>
       <c r="Q523" s="61"/>
       <c r="S523" s="61"/>
       <c r="U523" s="62"/>
       <c r="V523" s="62"/>
     </row>
-    <row r="524" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:29" customHeight="1" ht="15.75">
       <c r="P524" s="61"/>
       <c r="Q524" s="61"/>
       <c r="S524" s="61"/>
       <c r="U524" s="62"/>
       <c r="V524" s="62"/>
     </row>
-    <row r="525" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:29" customHeight="1" ht="15.75">
       <c r="P525" s="61"/>
       <c r="Q525" s="61"/>
       <c r="S525" s="61"/>
       <c r="U525" s="62"/>
       <c r="V525" s="62"/>
     </row>
-    <row r="526" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:29" customHeight="1" ht="15.75">
       <c r="P526" s="61"/>
       <c r="Q526" s="61"/>
       <c r="S526" s="61"/>
       <c r="U526" s="62"/>
       <c r="V526" s="62"/>
     </row>
-    <row r="527" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:29" customHeight="1" ht="15.75">
       <c r="P527" s="61"/>
       <c r="Q527" s="61"/>
       <c r="S527" s="61"/>
       <c r="U527" s="62"/>
       <c r="V527" s="62"/>
     </row>
-    <row r="528" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:29" customHeight="1" ht="15.75">
       <c r="P528" s="61"/>
       <c r="Q528" s="61"/>
       <c r="S528" s="61"/>
       <c r="U528" s="62"/>
       <c r="V528" s="62"/>
     </row>
-    <row r="529" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:29" customHeight="1" ht="15.75">
       <c r="P529" s="61"/>
       <c r="Q529" s="61"/>
       <c r="S529" s="61"/>
       <c r="U529" s="62"/>
       <c r="V529" s="62"/>
     </row>
-    <row r="530" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:29" customHeight="1" ht="15.75">
       <c r="P530" s="61"/>
       <c r="Q530" s="61"/>
       <c r="S530" s="61"/>
       <c r="U530" s="62"/>
       <c r="V530" s="62"/>
     </row>
-    <row r="531" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:29" customHeight="1" ht="15.75">
       <c r="P531" s="61"/>
       <c r="Q531" s="61"/>
       <c r="S531" s="61"/>
       <c r="U531" s="62"/>
       <c r="V531" s="62"/>
     </row>
-    <row r="532" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:29" customHeight="1" ht="15.75">
       <c r="P532" s="61"/>
       <c r="Q532" s="61"/>
       <c r="S532" s="61"/>
       <c r="U532" s="62"/>
       <c r="V532" s="62"/>
     </row>
-    <row r="533" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:29" customHeight="1" ht="15.75">
       <c r="P533" s="61"/>
       <c r="Q533" s="61"/>
       <c r="S533" s="61"/>
       <c r="U533" s="62"/>
       <c r="V533" s="62"/>
     </row>
-    <row r="534" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:29" customHeight="1" ht="15.75">
       <c r="P534" s="61"/>
       <c r="Q534" s="61"/>
       <c r="S534" s="61"/>
       <c r="U534" s="62"/>
       <c r="V534" s="62"/>
     </row>
-    <row r="535" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:29" customHeight="1" ht="15.75">
       <c r="P535" s="61"/>
       <c r="Q535" s="61"/>
       <c r="S535" s="61"/>
       <c r="U535" s="62"/>
       <c r="V535" s="62"/>
     </row>
-    <row r="536" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:29" customHeight="1" ht="15.75">
       <c r="P536" s="61"/>
       <c r="Q536" s="61"/>
       <c r="S536" s="61"/>
       <c r="U536" s="62"/>
       <c r="V536" s="62"/>
     </row>
-    <row r="537" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:29" customHeight="1" ht="15.75">
       <c r="P537" s="61"/>
       <c r="Q537" s="61"/>
       <c r="S537" s="61"/>
       <c r="U537" s="62"/>
       <c r="V537" s="62"/>
     </row>
-    <row r="538" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:29" customHeight="1" ht="15.75">
       <c r="P538" s="61"/>
       <c r="Q538" s="61"/>
       <c r="S538" s="61"/>
       <c r="U538" s="62"/>
       <c r="V538" s="62"/>
     </row>
-    <row r="539" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:29" customHeight="1" ht="15.75">
       <c r="P539" s="61"/>
       <c r="Q539" s="61"/>
       <c r="S539" s="61"/>
       <c r="U539" s="62"/>
       <c r="V539" s="62"/>
     </row>
-    <row r="540" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:29" customHeight="1" ht="15.75">
       <c r="P540" s="61"/>
       <c r="Q540" s="61"/>
       <c r="S540" s="61"/>
       <c r="U540" s="62"/>
       <c r="V540" s="62"/>
     </row>
-    <row r="541" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:29" customHeight="1" ht="15.75">
       <c r="P541" s="61"/>
       <c r="Q541" s="61"/>
       <c r="S541" s="61"/>
       <c r="U541" s="62"/>
       <c r="V541" s="62"/>
     </row>
-    <row r="542" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:29" customHeight="1" ht="15.75">
       <c r="P542" s="61"/>
       <c r="Q542" s="61"/>
       <c r="S542" s="61"/>
       <c r="U542" s="62"/>
       <c r="V542" s="62"/>
     </row>
-    <row r="543" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:29" customHeight="1" ht="15.75">
       <c r="P543" s="61"/>
       <c r="Q543" s="61"/>
       <c r="S543" s="61"/>
       <c r="U543" s="62"/>
       <c r="V543" s="62"/>
     </row>
-    <row r="544" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:29" customHeight="1" ht="15.75">
       <c r="P544" s="61"/>
       <c r="Q544" s="61"/>
       <c r="S544" s="61"/>
       <c r="U544" s="62"/>
       <c r="V544" s="62"/>
     </row>
-    <row r="545" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:29" customHeight="1" ht="15.75">
       <c r="P545" s="61"/>
       <c r="Q545" s="61"/>
       <c r="S545" s="61"/>
       <c r="U545" s="62"/>
       <c r="V545" s="62"/>
     </row>
-    <row r="546" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:29" customHeight="1" ht="15.75">
       <c r="P546" s="61"/>
       <c r="Q546" s="61"/>
       <c r="S546" s="61"/>
       <c r="U546" s="62"/>
       <c r="V546" s="62"/>
     </row>
-    <row r="547" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:29" customHeight="1" ht="15.75">
       <c r="P547" s="61"/>
       <c r="Q547" s="61"/>
       <c r="S547" s="61"/>
       <c r="U547" s="62"/>
       <c r="V547" s="62"/>
     </row>
-    <row r="548" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:29" customHeight="1" ht="15.75">
       <c r="P548" s="61"/>
       <c r="Q548" s="61"/>
       <c r="S548" s="61"/>
       <c r="U548" s="62"/>
       <c r="V548" s="62"/>
     </row>
-    <row r="549" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:29" customHeight="1" ht="15.75">
       <c r="P549" s="61"/>
       <c r="Q549" s="61"/>
       <c r="S549" s="61"/>
       <c r="U549" s="62"/>
       <c r="V549" s="62"/>
     </row>
-    <row r="550" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:29" customHeight="1" ht="15.75">
       <c r="P550" s="61"/>
       <c r="Q550" s="61"/>
       <c r="S550" s="61"/>
       <c r="U550" s="62"/>
       <c r="V550" s="62"/>
     </row>
-    <row r="551" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:29" customHeight="1" ht="15.75">
       <c r="P551" s="61"/>
       <c r="Q551" s="61"/>
       <c r="S551" s="61"/>
       <c r="U551" s="62"/>
       <c r="V551" s="62"/>
     </row>
-    <row r="552" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:29" customHeight="1" ht="15.75">
       <c r="P552" s="61"/>
       <c r="Q552" s="61"/>
       <c r="S552" s="61"/>
       <c r="U552" s="62"/>
       <c r="V552" s="62"/>
     </row>
-    <row r="553" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:29" customHeight="1" ht="15.75">
       <c r="P553" s="61"/>
       <c r="Q553" s="61"/>
       <c r="S553" s="61"/>
       <c r="U553" s="62"/>
       <c r="V553" s="62"/>
     </row>
-    <row r="554" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:29" customHeight="1" ht="15.75">
       <c r="P554" s="61"/>
       <c r="Q554" s="61"/>
       <c r="S554" s="61"/>
       <c r="U554" s="62"/>
       <c r="V554" s="62"/>
     </row>
-    <row r="555" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:29" customHeight="1" ht="15.75">
       <c r="P555" s="61"/>
       <c r="Q555" s="61"/>
       <c r="S555" s="61"/>
       <c r="U555" s="62"/>
       <c r="V555" s="62"/>
     </row>
-    <row r="556" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:29" customHeight="1" ht="15.75">
       <c r="P556" s="61"/>
       <c r="Q556" s="61"/>
       <c r="S556" s="61"/>
       <c r="U556" s="62"/>
       <c r="V556" s="62"/>
     </row>
-    <row r="557" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:29" customHeight="1" ht="15.75">
       <c r="P557" s="61"/>
       <c r="Q557" s="61"/>
       <c r="S557" s="61"/>
       <c r="U557" s="62"/>
       <c r="V557" s="62"/>
     </row>
-    <row r="558" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:29" customHeight="1" ht="15.75">
       <c r="P558" s="61"/>
       <c r="Q558" s="61"/>
       <c r="S558" s="61"/>
       <c r="U558" s="62"/>
       <c r="V558" s="62"/>
     </row>
-    <row r="559" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:29" customHeight="1" ht="15.75">
       <c r="P559" s="61"/>
       <c r="Q559" s="61"/>
       <c r="S559" s="61"/>
       <c r="U559" s="62"/>
       <c r="V559" s="62"/>
     </row>
-    <row r="560" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:29" customHeight="1" ht="15.75">
       <c r="P560" s="61"/>
       <c r="Q560" s="61"/>
       <c r="S560" s="61"/>
       <c r="U560" s="62"/>
       <c r="V560" s="62"/>
     </row>
-    <row r="561" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:29" customHeight="1" ht="15.75">
       <c r="P561" s="61"/>
       <c r="Q561" s="61"/>
       <c r="S561" s="61"/>
       <c r="U561" s="62"/>
       <c r="V561" s="62"/>
     </row>
-    <row r="562" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:29" customHeight="1" ht="15.75">
       <c r="P562" s="61"/>
       <c r="Q562" s="61"/>
       <c r="S562" s="61"/>
       <c r="U562" s="62"/>
       <c r="V562" s="62"/>
     </row>
-    <row r="563" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:29" customHeight="1" ht="15.75">
       <c r="P563" s="61"/>
       <c r="Q563" s="61"/>
       <c r="S563" s="61"/>
       <c r="U563" s="62"/>
       <c r="V563" s="62"/>
     </row>
-    <row r="564" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:29" customHeight="1" ht="15.75">
       <c r="P564" s="61"/>
       <c r="Q564" s="61"/>
       <c r="S564" s="61"/>
       <c r="U564" s="62"/>
       <c r="V564" s="62"/>
     </row>
-    <row r="565" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:29" customHeight="1" ht="15.75">
       <c r="P565" s="61"/>
       <c r="Q565" s="61"/>
       <c r="S565" s="61"/>
       <c r="U565" s="62"/>
       <c r="V565" s="62"/>
     </row>
-    <row r="566" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:29" customHeight="1" ht="15.75">
       <c r="P566" s="61"/>
       <c r="Q566" s="61"/>
       <c r="S566" s="61"/>
       <c r="U566" s="62"/>
       <c r="V566" s="62"/>
     </row>
-    <row r="567" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:29" customHeight="1" ht="15.75">
       <c r="P567" s="61"/>
       <c r="Q567" s="61"/>
       <c r="S567" s="61"/>
       <c r="U567" s="62"/>
       <c r="V567" s="62"/>
     </row>
-    <row r="568" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:29" customHeight="1" ht="15.75">
       <c r="P568" s="61"/>
       <c r="Q568" s="61"/>
       <c r="S568" s="61"/>
       <c r="U568" s="62"/>
       <c r="V568" s="62"/>
     </row>
-    <row r="569" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:29" customHeight="1" ht="15.75">
       <c r="P569" s="61"/>
       <c r="Q569" s="61"/>
       <c r="S569" s="61"/>
       <c r="U569" s="62"/>
       <c r="V569" s="62"/>
     </row>
-    <row r="570" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:29" customHeight="1" ht="15.75">
       <c r="P570" s="61"/>
       <c r="Q570" s="61"/>
       <c r="S570" s="61"/>
       <c r="U570" s="62"/>
       <c r="V570" s="62"/>
     </row>
-    <row r="571" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:29" customHeight="1" ht="15.75">
       <c r="P571" s="61"/>
       <c r="Q571" s="61"/>
       <c r="S571" s="61"/>
       <c r="U571" s="62"/>
       <c r="V571" s="62"/>
     </row>
-    <row r="572" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:29" customHeight="1" ht="15.75">
       <c r="P572" s="61"/>
       <c r="Q572" s="61"/>
       <c r="S572" s="61"/>
       <c r="U572" s="62"/>
       <c r="V572" s="62"/>
     </row>
-    <row r="573" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:29" customHeight="1" ht="15.75">
       <c r="P573" s="61"/>
       <c r="Q573" s="61"/>
       <c r="S573" s="61"/>
       <c r="U573" s="62"/>
       <c r="V573" s="62"/>
     </row>
-    <row r="574" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:29" customHeight="1" ht="15.75">
       <c r="P574" s="61"/>
       <c r="Q574" s="61"/>
       <c r="S574" s="61"/>
       <c r="U574" s="62"/>
       <c r="V574" s="62"/>
     </row>
-    <row r="575" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:29" customHeight="1" ht="15.75">
       <c r="P575" s="61"/>
       <c r="Q575" s="61"/>
       <c r="S575" s="61"/>
       <c r="U575" s="62"/>
       <c r="V575" s="62"/>
     </row>
-    <row r="576" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:29" customHeight="1" ht="15.75">
       <c r="P576" s="61"/>
       <c r="Q576" s="61"/>
       <c r="S576" s="61"/>
       <c r="U576" s="62"/>
       <c r="V576" s="62"/>
     </row>
-    <row r="577" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:29" customHeight="1" ht="15.75">
       <c r="P577" s="61"/>
       <c r="Q577" s="61"/>
       <c r="S577" s="61"/>
       <c r="U577" s="62"/>
       <c r="V577" s="62"/>
     </row>
-    <row r="578" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:29" customHeight="1" ht="15.75">
       <c r="P578" s="61"/>
       <c r="Q578" s="61"/>
       <c r="S578" s="61"/>
       <c r="U578" s="62"/>
       <c r="V578" s="62"/>
     </row>
-    <row r="579" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:29" customHeight="1" ht="15.75">
       <c r="P579" s="61"/>
       <c r="Q579" s="61"/>
       <c r="S579" s="61"/>
       <c r="U579" s="62"/>
       <c r="V579" s="62"/>
     </row>
-    <row r="580" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:29" customHeight="1" ht="15.75">
       <c r="P580" s="61"/>
       <c r="Q580" s="61"/>
       <c r="S580" s="61"/>
       <c r="U580" s="62"/>
       <c r="V580" s="62"/>
     </row>
-    <row r="581" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:29" customHeight="1" ht="15.75">
       <c r="P581" s="61"/>
       <c r="Q581" s="61"/>
       <c r="S581" s="61"/>
       <c r="U581" s="62"/>
       <c r="V581" s="62"/>
     </row>
-    <row r="582" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:29" customHeight="1" ht="15.75">
       <c r="P582" s="61"/>
       <c r="Q582" s="61"/>
       <c r="S582" s="61"/>
       <c r="U582" s="62"/>
       <c r="V582" s="62"/>
     </row>
-    <row r="583" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:29" customHeight="1" ht="15.75">
       <c r="P583" s="61"/>
       <c r="Q583" s="61"/>
       <c r="S583" s="61"/>
       <c r="U583" s="62"/>
       <c r="V583" s="62"/>
     </row>
-    <row r="584" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:29" customHeight="1" ht="15.75">
       <c r="P584" s="61"/>
       <c r="Q584" s="61"/>
       <c r="S584" s="61"/>
       <c r="U584" s="62"/>
       <c r="V584" s="62"/>
     </row>
-    <row r="585" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:29" customHeight="1" ht="15.75">
       <c r="P585" s="61"/>
       <c r="Q585" s="61"/>
       <c r="S585" s="61"/>
       <c r="U585" s="62"/>
       <c r="V585" s="62"/>
     </row>
-    <row r="586" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:29" customHeight="1" ht="15.75">
       <c r="P586" s="61"/>
       <c r="Q586" s="61"/>
       <c r="S586" s="61"/>
       <c r="U586" s="62"/>
       <c r="V586" s="62"/>
     </row>
-    <row r="587" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:29" customHeight="1" ht="15.75">
       <c r="P587" s="61"/>
       <c r="Q587" s="61"/>
       <c r="S587" s="61"/>
       <c r="U587" s="62"/>
       <c r="V587" s="62"/>
     </row>
-    <row r="588" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:29" customHeight="1" ht="15.75">
       <c r="P588" s="61"/>
       <c r="Q588" s="61"/>
       <c r="S588" s="61"/>
       <c r="U588" s="62"/>
       <c r="V588" s="62"/>
     </row>
-    <row r="589" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:29" customHeight="1" ht="15.75">
       <c r="P589" s="61"/>
       <c r="Q589" s="61"/>
       <c r="S589" s="61"/>
       <c r="U589" s="62"/>
       <c r="V589" s="62"/>
     </row>
-    <row r="590" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:29" customHeight="1" ht="15.75">
       <c r="P590" s="61"/>
       <c r="Q590" s="61"/>
       <c r="S590" s="61"/>
       <c r="U590" s="62"/>
       <c r="V590" s="62"/>
     </row>
-    <row r="591" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:29" customHeight="1" ht="15.75">
       <c r="P591" s="61"/>
       <c r="Q591" s="61"/>
       <c r="S591" s="61"/>
       <c r="U591" s="62"/>
       <c r="V591" s="62"/>
     </row>
-    <row r="592" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:29" customHeight="1" ht="15.75">
       <c r="P592" s="61"/>
       <c r="Q592" s="61"/>
       <c r="S592" s="61"/>
       <c r="U592" s="62"/>
       <c r="V592" s="62"/>
     </row>
-    <row r="593" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:29" customHeight="1" ht="15.75">
       <c r="P593" s="61"/>
       <c r="Q593" s="61"/>
       <c r="S593" s="61"/>
       <c r="U593" s="62"/>
       <c r="V593" s="62"/>
     </row>
-    <row r="594" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:29" customHeight="1" ht="15.75">
       <c r="P594" s="61"/>
       <c r="Q594" s="61"/>
       <c r="S594" s="61"/>
       <c r="U594" s="62"/>
       <c r="V594" s="62"/>
     </row>
-    <row r="595" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:29" customHeight="1" ht="15.75">
       <c r="P595" s="61"/>
       <c r="Q595" s="61"/>
       <c r="S595" s="61"/>
       <c r="U595" s="62"/>
       <c r="V595" s="62"/>
     </row>
-    <row r="596" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:29" customHeight="1" ht="15.75">
       <c r="P596" s="61"/>
       <c r="Q596" s="61"/>
       <c r="S596" s="61"/>
       <c r="U596" s="62"/>
       <c r="V596" s="62"/>
     </row>
-    <row r="597" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:29" customHeight="1" ht="15.75">
       <c r="P597" s="61"/>
       <c r="Q597" s="61"/>
       <c r="S597" s="61"/>
       <c r="U597" s="62"/>
       <c r="V597" s="62"/>
     </row>
-    <row r="598" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:29" customHeight="1" ht="15.75">
       <c r="P598" s="61"/>
       <c r="Q598" s="61"/>
       <c r="S598" s="61"/>
       <c r="U598" s="62"/>
       <c r="V598" s="62"/>
     </row>
-    <row r="599" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:29" customHeight="1" ht="15.75">
       <c r="P599" s="61"/>
       <c r="Q599" s="61"/>
       <c r="S599" s="61"/>
       <c r="U599" s="62"/>
       <c r="V599" s="62"/>
     </row>
-    <row r="600" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:29" customHeight="1" ht="15.75">
       <c r="P600" s="61"/>
       <c r="Q600" s="61"/>
       <c r="S600" s="61"/>
       <c r="U600" s="62"/>
       <c r="V600" s="62"/>
     </row>
-    <row r="601" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:29" customHeight="1" ht="15.75">
       <c r="P601" s="61"/>
       <c r="Q601" s="61"/>
       <c r="S601" s="61"/>
       <c r="U601" s="62"/>
       <c r="V601" s="62"/>
     </row>
-    <row r="602" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:29" customHeight="1" ht="15.75">
       <c r="P602" s="61"/>
       <c r="Q602" s="61"/>
       <c r="S602" s="61"/>
       <c r="U602" s="62"/>
       <c r="V602" s="62"/>
     </row>
-    <row r="603" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:29" customHeight="1" ht="15.75">
       <c r="P603" s="61"/>
       <c r="Q603" s="61"/>
       <c r="S603" s="61"/>
       <c r="U603" s="62"/>
       <c r="V603" s="62"/>
     </row>
-    <row r="604" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:29" customHeight="1" ht="15.75">
       <c r="P604" s="61"/>
       <c r="Q604" s="61"/>
       <c r="S604" s="61"/>
       <c r="U604" s="62"/>
       <c r="V604" s="62"/>
     </row>
-    <row r="605" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:29" customHeight="1" ht="15.75">
       <c r="P605" s="61"/>
       <c r="Q605" s="61"/>
       <c r="S605" s="61"/>
       <c r="U605" s="62"/>
       <c r="V605" s="62"/>
     </row>
-    <row r="606" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:29" customHeight="1" ht="15.75">
       <c r="P606" s="61"/>
       <c r="Q606" s="61"/>
       <c r="S606" s="61"/>
       <c r="U606" s="62"/>
       <c r="V606" s="62"/>
     </row>
-    <row r="607" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:29" customHeight="1" ht="15.75">
       <c r="P607" s="61"/>
       <c r="Q607" s="61"/>
       <c r="S607" s="61"/>
       <c r="U607" s="62"/>
       <c r="V607" s="62"/>
     </row>
-    <row r="608" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:29" customHeight="1" ht="15.75">
       <c r="P608" s="61"/>
       <c r="Q608" s="61"/>
       <c r="S608" s="61"/>
       <c r="U608" s="62"/>
       <c r="V608" s="62"/>
     </row>
-    <row r="609" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:29" customHeight="1" ht="15.75">
       <c r="P609" s="61"/>
       <c r="Q609" s="61"/>
       <c r="S609" s="61"/>
       <c r="U609" s="62"/>
       <c r="V609" s="62"/>
     </row>
-    <row r="610" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:29" customHeight="1" ht="15.75">
       <c r="P610" s="61"/>
       <c r="Q610" s="61"/>
       <c r="S610" s="61"/>
       <c r="U610" s="62"/>
       <c r="V610" s="62"/>
     </row>
-    <row r="611" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:29" customHeight="1" ht="15.75">
       <c r="P611" s="61"/>
       <c r="Q611" s="61"/>
       <c r="S611" s="61"/>
       <c r="U611" s="62"/>
       <c r="V611" s="62"/>
     </row>
-    <row r="612" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:29" customHeight="1" ht="15.75">
       <c r="P612" s="61"/>
       <c r="Q612" s="61"/>
       <c r="S612" s="61"/>
       <c r="U612" s="62"/>
       <c r="V612" s="62"/>
     </row>
-    <row r="613" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:29" customHeight="1" ht="15.75">
       <c r="P613" s="61"/>
       <c r="Q613" s="61"/>
       <c r="S613" s="61"/>
       <c r="U613" s="62"/>
       <c r="V613" s="62"/>
     </row>
-    <row r="614" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:29" customHeight="1" ht="15.75">
       <c r="P614" s="61"/>
       <c r="Q614" s="61"/>
       <c r="S614" s="61"/>
       <c r="U614" s="62"/>
       <c r="V614" s="62"/>
     </row>
-    <row r="615" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:29" customHeight="1" ht="15.75">
       <c r="P615" s="61"/>
       <c r="Q615" s="61"/>
       <c r="S615" s="61"/>
       <c r="U615" s="62"/>
       <c r="V615" s="62"/>
     </row>
-    <row r="616" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:29" customHeight="1" ht="15.75">
       <c r="P616" s="61"/>
       <c r="Q616" s="61"/>
       <c r="S616" s="61"/>
       <c r="U616" s="62"/>
       <c r="V616" s="62"/>
     </row>
-    <row r="617" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:29" customHeight="1" ht="15.75">
       <c r="P617" s="61"/>
       <c r="Q617" s="61"/>
       <c r="S617" s="61"/>
       <c r="U617" s="62"/>
       <c r="V617" s="62"/>
     </row>
-    <row r="618" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:29" customHeight="1" ht="15.75">
       <c r="P618" s="61"/>
       <c r="Q618" s="61"/>
       <c r="S618" s="61"/>
       <c r="U618" s="62"/>
       <c r="V618" s="62"/>
     </row>
-    <row r="619" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:29" customHeight="1" ht="15.75">
       <c r="P619" s="61"/>
       <c r="Q619" s="61"/>
       <c r="S619" s="61"/>
       <c r="U619" s="62"/>
       <c r="V619" s="62"/>
     </row>
-    <row r="620" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:29" customHeight="1" ht="15.75">
       <c r="P620" s="61"/>
       <c r="Q620" s="61"/>
       <c r="S620" s="61"/>
       <c r="U620" s="62"/>
       <c r="V620" s="62"/>
     </row>
-    <row r="621" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:29" customHeight="1" ht="15.75">
       <c r="P621" s="61"/>
       <c r="Q621" s="61"/>
       <c r="S621" s="61"/>
       <c r="U621" s="62"/>
       <c r="V621" s="62"/>
     </row>
-    <row r="622" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:29" customHeight="1" ht="15.75">
       <c r="P622" s="61"/>
       <c r="Q622" s="61"/>
       <c r="S622" s="61"/>
       <c r="U622" s="62"/>
       <c r="V622" s="62"/>
     </row>
-    <row r="623" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:29" customHeight="1" ht="15.75">
       <c r="P623" s="61"/>
       <c r="Q623" s="61"/>
       <c r="S623" s="61"/>
       <c r="U623" s="62"/>
       <c r="V623" s="62"/>
     </row>
-    <row r="624" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:29" customHeight="1" ht="15.75">
       <c r="P624" s="61"/>
       <c r="Q624" s="61"/>
       <c r="S624" s="61"/>
       <c r="U624" s="62"/>
       <c r="V624" s="62"/>
     </row>
-    <row r="625" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:29" customHeight="1" ht="15.75">
       <c r="P625" s="61"/>
       <c r="Q625" s="61"/>
       <c r="S625" s="61"/>
       <c r="U625" s="62"/>
       <c r="V625" s="62"/>
     </row>
-    <row r="626" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:29" customHeight="1" ht="15.75">
       <c r="P626" s="61"/>
       <c r="Q626" s="61"/>
       <c r="S626" s="61"/>
       <c r="U626" s="62"/>
       <c r="V626" s="62"/>
     </row>
-    <row r="627" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:29" customHeight="1" ht="15.75">
       <c r="P627" s="61"/>
       <c r="Q627" s="61"/>
       <c r="S627" s="61"/>
       <c r="U627" s="62"/>
       <c r="V627" s="62"/>
     </row>
-    <row r="628" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:29" customHeight="1" ht="15.75">
       <c r="P628" s="61"/>
       <c r="Q628" s="61"/>
       <c r="S628" s="61"/>
       <c r="U628" s="62"/>
       <c r="V628" s="62"/>
     </row>
-    <row r="629" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:29" customHeight="1" ht="15.75">
       <c r="P629" s="61"/>
       <c r="Q629" s="61"/>
       <c r="S629" s="61"/>
       <c r="U629" s="62"/>
       <c r="V629" s="62"/>
     </row>
-    <row r="630" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:29" customHeight="1" ht="15.75">
       <c r="P630" s="61"/>
       <c r="Q630" s="61"/>
       <c r="S630" s="61"/>
       <c r="U630" s="62"/>
       <c r="V630" s="62"/>
     </row>
-    <row r="631" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:29" customHeight="1" ht="15.75">
       <c r="P631" s="61"/>
       <c r="Q631" s="61"/>
       <c r="S631" s="61"/>
       <c r="U631" s="62"/>
       <c r="V631" s="62"/>
     </row>
-    <row r="632" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:29" customHeight="1" ht="15.75">
       <c r="P632" s="61"/>
       <c r="Q632" s="61"/>
       <c r="S632" s="61"/>
       <c r="U632" s="62"/>
       <c r="V632" s="62"/>
     </row>
-    <row r="633" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:29" customHeight="1" ht="15.75">
       <c r="P633" s="61"/>
       <c r="Q633" s="61"/>
       <c r="S633" s="61"/>
       <c r="U633" s="62"/>
       <c r="V633" s="62"/>
     </row>
-    <row r="634" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:29" customHeight="1" ht="15.75">
       <c r="P634" s="61"/>
       <c r="Q634" s="61"/>
       <c r="S634" s="61"/>
       <c r="U634" s="62"/>
       <c r="V634" s="62"/>
     </row>
-    <row r="635" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:29" customHeight="1" ht="15.75">
       <c r="P635" s="61"/>
       <c r="Q635" s="61"/>
       <c r="S635" s="61"/>
       <c r="U635" s="62"/>
       <c r="V635" s="62"/>
     </row>
-    <row r="636" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:29" customHeight="1" ht="15.75">
       <c r="P636" s="61"/>
       <c r="Q636" s="61"/>
       <c r="S636" s="61"/>
       <c r="U636" s="62"/>
       <c r="V636" s="62"/>
     </row>
-    <row r="637" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:29" customHeight="1" ht="15.75">
       <c r="P637" s="61"/>
       <c r="Q637" s="61"/>
       <c r="S637" s="61"/>
       <c r="U637" s="62"/>
       <c r="V637" s="62"/>
     </row>
-    <row r="638" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:29" customHeight="1" ht="15.75">
       <c r="P638" s="61"/>
       <c r="Q638" s="61"/>
       <c r="S638" s="61"/>
       <c r="U638" s="62"/>
       <c r="V638" s="62"/>
     </row>
-    <row r="639" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:29" customHeight="1" ht="15.75">
       <c r="P639" s="61"/>
       <c r="Q639" s="61"/>
       <c r="S639" s="61"/>
       <c r="U639" s="62"/>
       <c r="V639" s="62"/>
     </row>
-    <row r="640" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:29" customHeight="1" ht="15.75">
       <c r="P640" s="61"/>
       <c r="Q640" s="61"/>
       <c r="S640" s="61"/>
       <c r="U640" s="62"/>
       <c r="V640" s="62"/>
     </row>
-    <row r="641" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:29" customHeight="1" ht="15.75">
       <c r="P641" s="61"/>
       <c r="Q641" s="61"/>
       <c r="S641" s="61"/>
       <c r="U641" s="62"/>
       <c r="V641" s="62"/>
     </row>
-    <row r="642" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:29" customHeight="1" ht="15.75">
       <c r="P642" s="61"/>
       <c r="Q642" s="61"/>
       <c r="S642" s="61"/>
       <c r="U642" s="62"/>
       <c r="V642" s="62"/>
     </row>
-    <row r="643" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:29" customHeight="1" ht="15.75">
       <c r="P643" s="61"/>
       <c r="Q643" s="61"/>
       <c r="S643" s="61"/>
       <c r="U643" s="62"/>
       <c r="V643" s="62"/>
     </row>
-    <row r="644" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:29" customHeight="1" ht="15.75">
       <c r="P644" s="61"/>
       <c r="Q644" s="61"/>
       <c r="S644" s="61"/>
       <c r="U644" s="62"/>
       <c r="V644" s="62"/>
     </row>
-    <row r="645" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:29" customHeight="1" ht="15.75">
       <c r="P645" s="61"/>
       <c r="Q645" s="61"/>
       <c r="S645" s="61"/>
       <c r="U645" s="62"/>
       <c r="V645" s="62"/>
     </row>
-    <row r="646" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:29" customHeight="1" ht="15.75">
       <c r="P646" s="61"/>
       <c r="Q646" s="61"/>
       <c r="S646" s="61"/>
       <c r="U646" s="62"/>
       <c r="V646" s="62"/>
     </row>
-    <row r="647" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:29" customHeight="1" ht="15.75">
       <c r="P647" s="61"/>
       <c r="Q647" s="61"/>
       <c r="S647" s="61"/>
       <c r="U647" s="62"/>
       <c r="V647" s="62"/>
     </row>
-    <row r="648" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:29" customHeight="1" ht="15.75">
       <c r="P648" s="61"/>
       <c r="Q648" s="61"/>
       <c r="S648" s="61"/>
       <c r="U648" s="62"/>
       <c r="V648" s="62"/>
     </row>
-    <row r="649" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:29" customHeight="1" ht="15.75">
       <c r="P649" s="61"/>
       <c r="Q649" s="61"/>
       <c r="S649" s="61"/>
       <c r="U649" s="62"/>
       <c r="V649" s="62"/>
     </row>
-    <row r="650" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:29" customHeight="1" ht="15.75">
       <c r="P650" s="61"/>
       <c r="Q650" s="61"/>
       <c r="S650" s="61"/>
       <c r="U650" s="62"/>
       <c r="V650" s="62"/>
     </row>
-    <row r="651" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:29" customHeight="1" ht="15.75">
       <c r="P651" s="61"/>
       <c r="Q651" s="61"/>
       <c r="S651" s="61"/>
       <c r="U651" s="62"/>
       <c r="V651" s="62"/>
     </row>
-    <row r="652" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:29" customHeight="1" ht="15.75">
       <c r="P652" s="61"/>
       <c r="Q652" s="61"/>
       <c r="S652" s="61"/>
       <c r="U652" s="62"/>
       <c r="V652" s="62"/>
     </row>
-    <row r="653" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:29" customHeight="1" ht="15.75">
       <c r="P653" s="61"/>
       <c r="Q653" s="61"/>
       <c r="S653" s="61"/>
       <c r="U653" s="62"/>
       <c r="V653" s="62"/>
     </row>
-    <row r="654" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:29" customHeight="1" ht="15.75">
       <c r="P654" s="61"/>
       <c r="Q654" s="61"/>
       <c r="S654" s="61"/>
       <c r="U654" s="62"/>
       <c r="V654" s="62"/>
     </row>
-    <row r="655" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:29" customHeight="1" ht="15.75">
       <c r="P655" s="61"/>
       <c r="Q655" s="61"/>
       <c r="S655" s="61"/>
       <c r="U655" s="62"/>
       <c r="V655" s="62"/>
     </row>
-    <row r="656" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:29" customHeight="1" ht="15.75">
       <c r="P656" s="61"/>
       <c r="Q656" s="61"/>
       <c r="S656" s="61"/>
       <c r="U656" s="62"/>
       <c r="V656" s="62"/>
     </row>
-    <row r="657" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:29" customHeight="1" ht="15.75">
       <c r="P657" s="61"/>
       <c r="Q657" s="61"/>
       <c r="S657" s="61"/>
       <c r="U657" s="62"/>
       <c r="V657" s="62"/>
     </row>
-    <row r="658" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:29" customHeight="1" ht="15.75">
       <c r="P658" s="61"/>
       <c r="Q658" s="61"/>
       <c r="S658" s="61"/>
       <c r="U658" s="62"/>
       <c r="V658" s="62"/>
     </row>
-    <row r="659" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:29" customHeight="1" ht="15.75">
       <c r="P659" s="61"/>
       <c r="Q659" s="61"/>
       <c r="S659" s="61"/>
       <c r="U659" s="62"/>
       <c r="V659" s="62"/>
     </row>
-    <row r="660" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:29" customHeight="1" ht="15.75">
       <c r="P660" s="61"/>
       <c r="Q660" s="61"/>
       <c r="S660" s="61"/>
       <c r="U660" s="62"/>
       <c r="V660" s="62"/>
     </row>
-    <row r="661" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:29" customHeight="1" ht="15.75">
       <c r="P661" s="61"/>
       <c r="Q661" s="61"/>
       <c r="S661" s="61"/>
       <c r="U661" s="62"/>
       <c r="V661" s="62"/>
     </row>
-    <row r="662" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:29" customHeight="1" ht="15.75">
       <c r="P662" s="61"/>
       <c r="Q662" s="61"/>
       <c r="S662" s="61"/>
       <c r="U662" s="62"/>
       <c r="V662" s="62"/>
     </row>
-    <row r="663" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:29" customHeight="1" ht="15.75">
       <c r="P663" s="61"/>
       <c r="Q663" s="61"/>
       <c r="S663" s="61"/>
       <c r="U663" s="62"/>
       <c r="V663" s="62"/>
     </row>
-    <row r="664" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:29" customHeight="1" ht="15.75">
       <c r="P664" s="61"/>
       <c r="Q664" s="61"/>
       <c r="S664" s="61"/>
       <c r="U664" s="62"/>
       <c r="V664" s="62"/>
     </row>
-    <row r="665" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:29" customHeight="1" ht="15.75">
       <c r="P665" s="61"/>
       <c r="Q665" s="61"/>
       <c r="S665" s="61"/>
       <c r="U665" s="62"/>
       <c r="V665" s="62"/>
     </row>
-    <row r="666" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:29" customHeight="1" ht="15.75">
       <c r="P666" s="61"/>
       <c r="Q666" s="61"/>
       <c r="S666" s="61"/>
       <c r="U666" s="62"/>
       <c r="V666" s="62"/>
     </row>
-    <row r="667" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:29" customHeight="1" ht="15.75">
       <c r="P667" s="61"/>
       <c r="Q667" s="61"/>
       <c r="S667" s="61"/>
       <c r="U667" s="62"/>
       <c r="V667" s="62"/>
     </row>
-    <row r="668" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:29" customHeight="1" ht="15.75">
       <c r="P668" s="61"/>
       <c r="Q668" s="61"/>
       <c r="S668" s="61"/>
       <c r="U668" s="62"/>
       <c r="V668" s="62"/>
     </row>
-    <row r="669" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:29" customHeight="1" ht="15.75">
       <c r="P669" s="61"/>
       <c r="Q669" s="61"/>
       <c r="S669" s="61"/>
       <c r="U669" s="62"/>
       <c r="V669" s="62"/>
     </row>
-    <row r="670" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:29" customHeight="1" ht="15.75">
       <c r="P670" s="61"/>
       <c r="Q670" s="61"/>
       <c r="S670" s="61"/>
       <c r="U670" s="62"/>
       <c r="V670" s="62"/>
     </row>
-    <row r="671" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:29" customHeight="1" ht="15.75">
       <c r="P671" s="61"/>
       <c r="Q671" s="61"/>
       <c r="S671" s="61"/>
       <c r="U671" s="62"/>
       <c r="V671" s="62"/>
     </row>
-    <row r="672" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:29" customHeight="1" ht="15.75">
       <c r="P672" s="61"/>
       <c r="Q672" s="61"/>
       <c r="S672" s="61"/>
       <c r="U672" s="62"/>
       <c r="V672" s="62"/>
     </row>
-    <row r="673" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:29" customHeight="1" ht="15.75">
       <c r="P673" s="61"/>
       <c r="Q673" s="61"/>
       <c r="S673" s="61"/>
       <c r="U673" s="62"/>
       <c r="V673" s="62"/>
     </row>
-    <row r="674" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:29" customHeight="1" ht="15.75">
       <c r="P674" s="61"/>
       <c r="Q674" s="61"/>
       <c r="S674" s="61"/>
       <c r="U674" s="62"/>
       <c r="V674" s="62"/>
     </row>
-    <row r="675" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:29" customHeight="1" ht="15.75">
       <c r="P675" s="61"/>
       <c r="Q675" s="61"/>
       <c r="S675" s="61"/>
       <c r="U675" s="62"/>
       <c r="V675" s="62"/>
     </row>
-    <row r="676" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:29" customHeight="1" ht="15.75">
       <c r="P676" s="61"/>
       <c r="Q676" s="61"/>
       <c r="S676" s="61"/>
       <c r="U676" s="62"/>
       <c r="V676" s="62"/>
     </row>
-    <row r="677" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:29" customHeight="1" ht="15.75">
       <c r="P677" s="61"/>
       <c r="Q677" s="61"/>
       <c r="S677" s="61"/>
       <c r="U677" s="62"/>
       <c r="V677" s="62"/>
     </row>
-    <row r="678" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:29" customHeight="1" ht="15.75">
       <c r="P678" s="61"/>
       <c r="Q678" s="61"/>
       <c r="S678" s="61"/>
       <c r="U678" s="62"/>
       <c r="V678" s="62"/>
     </row>
-    <row r="679" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:29" customHeight="1" ht="15.75">
       <c r="P679" s="61"/>
       <c r="Q679" s="61"/>
       <c r="S679" s="61"/>
       <c r="U679" s="62"/>
       <c r="V679" s="62"/>
     </row>
-    <row r="680" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:29" customHeight="1" ht="15.75">
       <c r="P680" s="61"/>
       <c r="Q680" s="61"/>
       <c r="S680" s="61"/>
       <c r="U680" s="62"/>
       <c r="V680" s="62"/>
     </row>
-    <row r="681" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:29" customHeight="1" ht="15.75">
       <c r="P681" s="61"/>
       <c r="Q681" s="61"/>
       <c r="S681" s="61"/>
       <c r="U681" s="62"/>
       <c r="V681" s="62"/>
     </row>
-    <row r="682" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:29" customHeight="1" ht="15.75">
       <c r="P682" s="61"/>
       <c r="Q682" s="61"/>
       <c r="S682" s="61"/>
       <c r="U682" s="62"/>
       <c r="V682" s="62"/>
     </row>
-    <row r="683" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:29" customHeight="1" ht="15.75">
       <c r="P683" s="61"/>
       <c r="Q683" s="61"/>
       <c r="S683" s="61"/>
       <c r="U683" s="62"/>
       <c r="V683" s="62"/>
     </row>
-    <row r="684" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:29" customHeight="1" ht="15.75">
       <c r="P684" s="61"/>
       <c r="Q684" s="61"/>
       <c r="S684" s="61"/>
       <c r="U684" s="62"/>
       <c r="V684" s="62"/>
     </row>
-    <row r="685" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:29" customHeight="1" ht="15.75">
       <c r="P685" s="61"/>
       <c r="Q685" s="61"/>
       <c r="S685" s="61"/>
       <c r="U685" s="62"/>
       <c r="V685" s="62"/>
     </row>
-    <row r="686" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:29" customHeight="1" ht="15.75">
       <c r="P686" s="61"/>
       <c r="Q686" s="61"/>
       <c r="S686" s="61"/>
       <c r="U686" s="62"/>
       <c r="V686" s="62"/>
     </row>
-    <row r="687" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:29" customHeight="1" ht="15.75">
       <c r="P687" s="61"/>
       <c r="Q687" s="61"/>
       <c r="S687" s="61"/>
       <c r="U687" s="62"/>
       <c r="V687" s="62"/>
     </row>
-    <row r="688" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:29" customHeight="1" ht="15.75">
       <c r="P688" s="61"/>
       <c r="Q688" s="61"/>
       <c r="S688" s="61"/>
       <c r="U688" s="62"/>
       <c r="V688" s="62"/>
     </row>
-    <row r="689" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:29" customHeight="1" ht="15.75">
       <c r="P689" s="61"/>
       <c r="Q689" s="61"/>
       <c r="S689" s="61"/>
       <c r="U689" s="62"/>
       <c r="V689" s="62"/>
     </row>
-    <row r="690" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:29" customHeight="1" ht="15.75">
       <c r="P690" s="61"/>
       <c r="Q690" s="61"/>
       <c r="S690" s="61"/>
       <c r="U690" s="62"/>
       <c r="V690" s="62"/>
     </row>
-    <row r="691" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:29" customHeight="1" ht="15.75">
       <c r="P691" s="61"/>
       <c r="Q691" s="61"/>
       <c r="S691" s="61"/>
       <c r="U691" s="62"/>
       <c r="V691" s="62"/>
     </row>
-    <row r="692" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:29" customHeight="1" ht="15.75">
       <c r="P692" s="61"/>
       <c r="Q692" s="61"/>
       <c r="S692" s="61"/>
       <c r="U692" s="62"/>
       <c r="V692" s="62"/>
     </row>
-    <row r="693" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:29" customHeight="1" ht="15.75">
       <c r="P693" s="61"/>
       <c r="Q693" s="61"/>
       <c r="S693" s="61"/>
       <c r="U693" s="62"/>
       <c r="V693" s="62"/>
     </row>
-    <row r="694" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:29" customHeight="1" ht="15.75">
       <c r="P694" s="61"/>
       <c r="Q694" s="61"/>
       <c r="S694" s="61"/>
       <c r="U694" s="62"/>
       <c r="V694" s="62"/>
     </row>
-    <row r="695" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:29" customHeight="1" ht="15.75">
       <c r="P695" s="61"/>
       <c r="Q695" s="61"/>
       <c r="S695" s="61"/>
       <c r="U695" s="62"/>
       <c r="V695" s="62"/>
     </row>
-    <row r="696" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:29" customHeight="1" ht="15.75">
       <c r="P696" s="61"/>
       <c r="Q696" s="61"/>
       <c r="S696" s="61"/>
       <c r="U696" s="62"/>
       <c r="V696" s="62"/>
     </row>
-    <row r="697" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:29" customHeight="1" ht="15.75">
       <c r="P697" s="61"/>
       <c r="Q697" s="61"/>
       <c r="S697" s="61"/>
       <c r="U697" s="62"/>
       <c r="V697" s="62"/>
     </row>
-    <row r="698" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:29" customHeight="1" ht="15.75">
       <c r="P698" s="61"/>
       <c r="Q698" s="61"/>
       <c r="S698" s="61"/>
       <c r="U698" s="62"/>
       <c r="V698" s="62"/>
     </row>
-    <row r="699" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:29" customHeight="1" ht="15.75">
       <c r="P699" s="61"/>
       <c r="Q699" s="61"/>
       <c r="S699" s="61"/>
       <c r="U699" s="62"/>
       <c r="V699" s="62"/>
     </row>
-    <row r="700" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:29" customHeight="1" ht="15.75">
       <c r="P700" s="61"/>
       <c r="Q700" s="61"/>
       <c r="S700" s="61"/>
       <c r="U700" s="62"/>
       <c r="V700" s="62"/>
     </row>
-    <row r="701" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:29" customHeight="1" ht="15.75">
       <c r="P701" s="61"/>
       <c r="Q701" s="61"/>
       <c r="S701" s="61"/>
       <c r="U701" s="62"/>
       <c r="V701" s="62"/>
     </row>
-    <row r="702" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:29" customHeight="1" ht="15.75">
       <c r="P702" s="61"/>
       <c r="Q702" s="61"/>
       <c r="S702" s="61"/>
       <c r="U702" s="62"/>
       <c r="V702" s="62"/>
     </row>
-    <row r="703" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:29" customHeight="1" ht="15.75">
       <c r="P703" s="61"/>
       <c r="Q703" s="61"/>
       <c r="S703" s="61"/>
       <c r="U703" s="62"/>
       <c r="V703" s="62"/>
     </row>
-    <row r="704" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:29" customHeight="1" ht="15.75">
       <c r="P704" s="61"/>
       <c r="Q704" s="61"/>
       <c r="S704" s="61"/>
       <c r="U704" s="62"/>
       <c r="V704" s="62"/>
     </row>
-    <row r="705" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:29" customHeight="1" ht="15.75">
       <c r="P705" s="61"/>
       <c r="Q705" s="61"/>
       <c r="S705" s="61"/>
       <c r="U705" s="62"/>
       <c r="V705" s="62"/>
     </row>
-    <row r="706" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:29" customHeight="1" ht="15.75">
       <c r="P706" s="61"/>
       <c r="Q706" s="61"/>
       <c r="S706" s="61"/>
       <c r="U706" s="62"/>
       <c r="V706" s="62"/>
     </row>
-    <row r="707" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:29" customHeight="1" ht="15.75">
       <c r="P707" s="61"/>
       <c r="Q707" s="61"/>
       <c r="S707" s="61"/>
       <c r="U707" s="62"/>
       <c r="V707" s="62"/>
     </row>
-    <row r="708" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:29" customHeight="1" ht="15.75">
       <c r="P708" s="61"/>
       <c r="Q708" s="61"/>
       <c r="S708" s="61"/>
       <c r="U708" s="62"/>
       <c r="V708" s="62"/>
     </row>
-    <row r="709" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:29" customHeight="1" ht="15.75">
       <c r="P709" s="61"/>
       <c r="Q709" s="61"/>
       <c r="S709" s="61"/>
       <c r="U709" s="62"/>
       <c r="V709" s="62"/>
     </row>
-    <row r="710" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:29" customHeight="1" ht="15.75">
       <c r="P710" s="61"/>
       <c r="Q710" s="61"/>
       <c r="S710" s="61"/>
       <c r="U710" s="62"/>
       <c r="V710" s="62"/>
     </row>
-    <row r="711" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:29" customHeight="1" ht="15.75">
       <c r="P711" s="61"/>
       <c r="Q711" s="61"/>
       <c r="S711" s="61"/>
       <c r="U711" s="62"/>
       <c r="V711" s="62"/>
     </row>
-    <row r="712" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:29" customHeight="1" ht="15.75">
       <c r="P712" s="61"/>
       <c r="Q712" s="61"/>
       <c r="S712" s="61"/>
       <c r="U712" s="62"/>
       <c r="V712" s="62"/>
     </row>
-    <row r="713" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:29" customHeight="1" ht="15.75">
       <c r="P713" s="61"/>
       <c r="Q713" s="61"/>
       <c r="S713" s="61"/>
       <c r="U713" s="62"/>
       <c r="V713" s="62"/>
     </row>
-    <row r="714" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:29" customHeight="1" ht="15.75">
       <c r="P714" s="61"/>
       <c r="Q714" s="61"/>
       <c r="S714" s="61"/>
       <c r="U714" s="62"/>
       <c r="V714" s="62"/>
     </row>
-    <row r="715" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:29" customHeight="1" ht="15.75">
       <c r="P715" s="61"/>
       <c r="Q715" s="61"/>
       <c r="S715" s="61"/>
       <c r="U715" s="62"/>
       <c r="V715" s="62"/>
     </row>
-    <row r="716" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:29" customHeight="1" ht="15.75">
       <c r="P716" s="61"/>
       <c r="Q716" s="61"/>
       <c r="S716" s="61"/>
       <c r="U716" s="62"/>
       <c r="V716" s="62"/>
     </row>
-    <row r="717" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:29" customHeight="1" ht="15.75">
       <c r="P717" s="61"/>
       <c r="Q717" s="61"/>
       <c r="S717" s="61"/>
       <c r="U717" s="62"/>
       <c r="V717" s="62"/>
     </row>
-    <row r="718" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:29" customHeight="1" ht="15.75">
       <c r="P718" s="61"/>
       <c r="Q718" s="61"/>
       <c r="S718" s="61"/>
       <c r="U718" s="62"/>
       <c r="V718" s="62"/>
     </row>
-    <row r="719" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:29" customHeight="1" ht="15.75">
       <c r="P719" s="61"/>
       <c r="Q719" s="61"/>
       <c r="S719" s="61"/>
       <c r="U719" s="62"/>
       <c r="V719" s="62"/>
     </row>
-    <row r="720" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:29" customHeight="1" ht="15.75">
       <c r="P720" s="61"/>
       <c r="Q720" s="61"/>
       <c r="S720" s="61"/>
       <c r="U720" s="62"/>
       <c r="V720" s="62"/>
     </row>
-    <row r="721" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:29" customHeight="1" ht="15.75">
       <c r="P721" s="61"/>
       <c r="Q721" s="61"/>
       <c r="S721" s="61"/>
       <c r="U721" s="62"/>
       <c r="V721" s="62"/>
     </row>
-    <row r="722" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:29" customHeight="1" ht="15.75">
       <c r="P722" s="61"/>
       <c r="Q722" s="61"/>
       <c r="S722" s="61"/>
       <c r="U722" s="62"/>
       <c r="V722" s="62"/>
     </row>
-    <row r="723" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:29" customHeight="1" ht="15.75">
       <c r="P723" s="61"/>
       <c r="Q723" s="61"/>
       <c r="S723" s="61"/>
       <c r="U723" s="62"/>
       <c r="V723" s="62"/>
     </row>
-    <row r="724" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:29" customHeight="1" ht="15.75">
       <c r="P724" s="61"/>
       <c r="Q724" s="61"/>
       <c r="S724" s="61"/>
       <c r="U724" s="62"/>
       <c r="V724" s="62"/>
     </row>
-    <row r="725" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:29" customHeight="1" ht="15.75">
       <c r="P725" s="61"/>
       <c r="Q725" s="61"/>
       <c r="S725" s="61"/>
       <c r="U725" s="62"/>
       <c r="V725" s="62"/>
     </row>
-    <row r="726" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:29" customHeight="1" ht="15.75">
       <c r="P726" s="61"/>
       <c r="Q726" s="61"/>
       <c r="S726" s="61"/>
       <c r="U726" s="62"/>
       <c r="V726" s="62"/>
     </row>
-    <row r="727" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:29" customHeight="1" ht="15.75">
       <c r="P727" s="61"/>
       <c r="Q727" s="61"/>
       <c r="S727" s="61"/>
       <c r="U727" s="62"/>
       <c r="V727" s="62"/>
     </row>
-    <row r="728" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:29" customHeight="1" ht="15.75">
       <c r="P728" s="61"/>
       <c r="Q728" s="61"/>
       <c r="S728" s="61"/>
       <c r="U728" s="62"/>
       <c r="V728" s="62"/>
     </row>
-    <row r="729" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:29" customHeight="1" ht="15.75">
       <c r="P729" s="61"/>
       <c r="Q729" s="61"/>
       <c r="S729" s="61"/>
       <c r="U729" s="62"/>
       <c r="V729" s="62"/>
     </row>
-    <row r="730" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:29" customHeight="1" ht="15.75">
       <c r="P730" s="61"/>
       <c r="Q730" s="61"/>
       <c r="S730" s="61"/>
       <c r="U730" s="62"/>
       <c r="V730" s="62"/>
     </row>
-    <row r="731" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:29" customHeight="1" ht="15.75">
       <c r="P731" s="61"/>
       <c r="Q731" s="61"/>
       <c r="S731" s="61"/>
       <c r="U731" s="62"/>
       <c r="V731" s="62"/>
     </row>
-    <row r="732" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:29" customHeight="1" ht="15.75">
       <c r="P732" s="61"/>
       <c r="Q732" s="61"/>
       <c r="S732" s="61"/>
       <c r="U732" s="62"/>
       <c r="V732" s="62"/>
     </row>
-    <row r="733" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:29" customHeight="1" ht="15.75">
       <c r="P733" s="61"/>
       <c r="Q733" s="61"/>
       <c r="S733" s="61"/>
       <c r="U733" s="62"/>
       <c r="V733" s="62"/>
     </row>
-    <row r="734" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:29" customHeight="1" ht="15.75">
       <c r="P734" s="61"/>
       <c r="Q734" s="61"/>
       <c r="S734" s="61"/>
       <c r="U734" s="62"/>
       <c r="V734" s="62"/>
     </row>
-    <row r="735" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:29" customHeight="1" ht="15.75">
       <c r="P735" s="61"/>
       <c r="Q735" s="61"/>
       <c r="S735" s="61"/>
       <c r="U735" s="62"/>
       <c r="V735" s="62"/>
     </row>
-    <row r="736" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:29" customHeight="1" ht="15.75">
       <c r="P736" s="61"/>
       <c r="Q736" s="61"/>
       <c r="S736" s="61"/>
       <c r="U736" s="62"/>
       <c r="V736" s="62"/>
     </row>
-    <row r="737" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:29" customHeight="1" ht="15.75">
       <c r="P737" s="61"/>
       <c r="Q737" s="61"/>
       <c r="S737" s="61"/>
       <c r="U737" s="62"/>
       <c r="V737" s="62"/>
     </row>
-    <row r="738" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:29" customHeight="1" ht="15.75">
       <c r="P738" s="61"/>
       <c r="Q738" s="61"/>
       <c r="S738" s="61"/>
       <c r="U738" s="62"/>
       <c r="V738" s="62"/>
     </row>
-    <row r="739" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:29" customHeight="1" ht="15.75">
       <c r="P739" s="61"/>
       <c r="Q739" s="61"/>
       <c r="S739" s="61"/>
       <c r="U739" s="62"/>
       <c r="V739" s="62"/>
     </row>
-    <row r="740" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:29" customHeight="1" ht="15.75">
       <c r="P740" s="61"/>
       <c r="Q740" s="61"/>
       <c r="S740" s="61"/>
       <c r="U740" s="62"/>
       <c r="V740" s="62"/>
     </row>
-    <row r="741" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:29" customHeight="1" ht="15.75">
       <c r="P741" s="61"/>
       <c r="Q741" s="61"/>
       <c r="S741" s="61"/>
       <c r="U741" s="62"/>
       <c r="V741" s="62"/>
     </row>
-    <row r="742" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:29" customHeight="1" ht="15.75">
       <c r="P742" s="61"/>
       <c r="Q742" s="61"/>
       <c r="S742" s="61"/>
       <c r="U742" s="62"/>
       <c r="V742" s="62"/>
     </row>
-    <row r="743" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:29" customHeight="1" ht="15.75">
       <c r="P743" s="61"/>
       <c r="Q743" s="61"/>
       <c r="S743" s="61"/>
       <c r="U743" s="62"/>
       <c r="V743" s="62"/>
     </row>
-    <row r="744" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:29" customHeight="1" ht="15.75">
       <c r="P744" s="61"/>
       <c r="Q744" s="61"/>
       <c r="S744" s="61"/>
       <c r="U744" s="62"/>
       <c r="V744" s="62"/>
     </row>
-    <row r="745" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:29" customHeight="1" ht="15.75">
       <c r="P745" s="61"/>
       <c r="Q745" s="61"/>
       <c r="S745" s="61"/>
       <c r="U745" s="62"/>
       <c r="V745" s="62"/>
     </row>
-    <row r="746" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:29" customHeight="1" ht="15.75">
       <c r="P746" s="61"/>
       <c r="Q746" s="61"/>
       <c r="S746" s="61"/>
       <c r="U746" s="62"/>
       <c r="V746" s="62"/>
     </row>
-    <row r="747" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:29" customHeight="1" ht="15.75">
       <c r="P747" s="61"/>
       <c r="Q747" s="61"/>
       <c r="S747" s="61"/>
       <c r="U747" s="62"/>
       <c r="V747" s="62"/>
     </row>
-    <row r="748" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:29" customHeight="1" ht="15.75">
       <c r="P748" s="61"/>
       <c r="Q748" s="61"/>
       <c r="S748" s="61"/>
       <c r="U748" s="62"/>
       <c r="V748" s="62"/>
     </row>
-    <row r="749" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:29" customHeight="1" ht="15.75">
       <c r="P749" s="61"/>
       <c r="Q749" s="61"/>
       <c r="S749" s="61"/>
       <c r="U749" s="62"/>
       <c r="V749" s="62"/>
     </row>
-    <row r="750" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:29" customHeight="1" ht="15.75">
       <c r="P750" s="61"/>
       <c r="Q750" s="61"/>
       <c r="S750" s="61"/>
       <c r="U750" s="62"/>
       <c r="V750" s="62"/>
     </row>
-    <row r="751" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:29" customHeight="1" ht="15.75">
       <c r="P751" s="61"/>
       <c r="Q751" s="61"/>
       <c r="S751" s="61"/>
       <c r="U751" s="62"/>
       <c r="V751" s="62"/>
     </row>
-    <row r="752" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:29" customHeight="1" ht="15.75">
       <c r="P752" s="61"/>
       <c r="Q752" s="61"/>
       <c r="S752" s="61"/>
       <c r="U752" s="62"/>
       <c r="V752" s="62"/>
     </row>
-    <row r="753" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:29" customHeight="1" ht="15.75">
       <c r="P753" s="61"/>
       <c r="Q753" s="61"/>
       <c r="S753" s="61"/>
       <c r="U753" s="62"/>
       <c r="V753" s="62"/>
     </row>
-    <row r="754" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:29" customHeight="1" ht="15.75">
       <c r="P754" s="61"/>
       <c r="Q754" s="61"/>
       <c r="S754" s="61"/>
       <c r="U754" s="62"/>
       <c r="V754" s="62"/>
     </row>
-    <row r="755" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:29" customHeight="1" ht="15.75">
       <c r="P755" s="61"/>
       <c r="Q755" s="61"/>
       <c r="S755" s="61"/>
       <c r="U755" s="62"/>
       <c r="V755" s="62"/>
     </row>
-    <row r="756" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:29" customHeight="1" ht="15.75">
       <c r="P756" s="61"/>
       <c r="Q756" s="61"/>
       <c r="S756" s="61"/>
       <c r="U756" s="62"/>
       <c r="V756" s="62"/>
     </row>
-    <row r="757" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:29" customHeight="1" ht="15.75">
       <c r="P757" s="61"/>
       <c r="Q757" s="61"/>
       <c r="S757" s="61"/>
       <c r="U757" s="62"/>
       <c r="V757" s="62"/>
     </row>
-    <row r="758" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:29" customHeight="1" ht="15.75">
       <c r="P758" s="61"/>
       <c r="Q758" s="61"/>
       <c r="S758" s="61"/>
       <c r="U758" s="62"/>
       <c r="V758" s="62"/>
     </row>
-    <row r="759" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:29" customHeight="1" ht="15.75">
       <c r="P759" s="61"/>
       <c r="Q759" s="61"/>
       <c r="S759" s="61"/>
       <c r="U759" s="62"/>
       <c r="V759" s="62"/>
     </row>
-    <row r="760" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:29" customHeight="1" ht="15.75">
       <c r="P760" s="61"/>
       <c r="Q760" s="61"/>
       <c r="S760" s="61"/>
       <c r="U760" s="62"/>
       <c r="V760" s="62"/>
     </row>
-    <row r="761" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:29" customHeight="1" ht="15.75">
       <c r="P761" s="61"/>
       <c r="Q761" s="61"/>
       <c r="S761" s="61"/>
       <c r="U761" s="62"/>
       <c r="V761" s="62"/>
     </row>
-    <row r="762" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:29" customHeight="1" ht="15.75">
       <c r="P762" s="61"/>
       <c r="Q762" s="61"/>
       <c r="S762" s="61"/>
       <c r="U762" s="62"/>
       <c r="V762" s="62"/>
     </row>
-    <row r="763" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:29" customHeight="1" ht="15.75">
       <c r="P763" s="61"/>
       <c r="Q763" s="61"/>
       <c r="S763" s="61"/>
       <c r="U763" s="62"/>
       <c r="V763" s="62"/>
     </row>
-    <row r="764" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:29" customHeight="1" ht="15.75">
       <c r="P764" s="61"/>
       <c r="Q764" s="61"/>
       <c r="S764" s="61"/>
       <c r="U764" s="62"/>
       <c r="V764" s="62"/>
     </row>
-    <row r="765" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:29" customHeight="1" ht="15.75">
       <c r="P765" s="61"/>
       <c r="Q765" s="61"/>
       <c r="S765" s="61"/>
       <c r="U765" s="62"/>
       <c r="V765" s="62"/>
     </row>
-    <row r="766" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:29" customHeight="1" ht="15.75">
       <c r="P766" s="61"/>
       <c r="Q766" s="61"/>
       <c r="S766" s="61"/>
       <c r="U766" s="62"/>
       <c r="V766" s="62"/>
     </row>
-    <row r="767" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:29" customHeight="1" ht="15.75">
       <c r="P767" s="61"/>
       <c r="Q767" s="61"/>
       <c r="S767" s="61"/>
       <c r="U767" s="62"/>
       <c r="V767" s="62"/>
     </row>
-    <row r="768" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:29" customHeight="1" ht="15.75">
       <c r="P768" s="61"/>
       <c r="Q768" s="61"/>
       <c r="S768" s="61"/>
       <c r="U768" s="62"/>
       <c r="V768" s="62"/>
     </row>
-    <row r="769" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:29" customHeight="1" ht="15.75">
       <c r="P769" s="61"/>
       <c r="Q769" s="61"/>
       <c r="S769" s="61"/>
       <c r="U769" s="62"/>
       <c r="V769" s="62"/>
     </row>
-    <row r="770" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:29" customHeight="1" ht="15.75">
       <c r="P770" s="61"/>
       <c r="Q770" s="61"/>
       <c r="S770" s="61"/>
       <c r="U770" s="62"/>
       <c r="V770" s="62"/>
     </row>
-    <row r="771" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:29" customHeight="1" ht="15.75">
       <c r="P771" s="61"/>
       <c r="Q771" s="61"/>
       <c r="S771" s="61"/>
       <c r="U771" s="62"/>
       <c r="V771" s="62"/>
     </row>
-    <row r="772" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:29" customHeight="1" ht="15.75">
       <c r="P772" s="61"/>
       <c r="Q772" s="61"/>
       <c r="S772" s="61"/>
       <c r="U772" s="62"/>
       <c r="V772" s="62"/>
     </row>
-    <row r="773" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:29" customHeight="1" ht="15.75">
       <c r="P773" s="61"/>
       <c r="Q773" s="61"/>
       <c r="S773" s="61"/>
       <c r="U773" s="62"/>
       <c r="V773" s="62"/>
     </row>
-    <row r="774" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:29" customHeight="1" ht="15.75">
       <c r="P774" s="61"/>
       <c r="Q774" s="61"/>
       <c r="S774" s="61"/>
       <c r="U774" s="62"/>
       <c r="V774" s="62"/>
     </row>
-    <row r="775" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:29" customHeight="1" ht="15.75">
       <c r="P775" s="61"/>
       <c r="Q775" s="61"/>
       <c r="S775" s="61"/>
       <c r="U775" s="62"/>
       <c r="V775" s="62"/>
     </row>
-    <row r="776" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:29" customHeight="1" ht="15.75">
       <c r="P776" s="61"/>
       <c r="Q776" s="61"/>
       <c r="S776" s="61"/>
       <c r="U776" s="62"/>
       <c r="V776" s="62"/>
     </row>
-    <row r="777" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:29" customHeight="1" ht="15.75">
       <c r="P777" s="61"/>
       <c r="Q777" s="61"/>
       <c r="S777" s="61"/>
       <c r="U777" s="62"/>
       <c r="V777" s="62"/>
     </row>
-    <row r="778" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:29" customHeight="1" ht="15.75">
       <c r="P778" s="61"/>
       <c r="Q778" s="61"/>
       <c r="S778" s="61"/>
       <c r="U778" s="62"/>
       <c r="V778" s="62"/>
     </row>
-    <row r="779" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:29" customHeight="1" ht="15.75">
       <c r="P779" s="61"/>
       <c r="Q779" s="61"/>
       <c r="S779" s="61"/>
       <c r="U779" s="62"/>
       <c r="V779" s="62"/>
     </row>
-    <row r="780" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:29" customHeight="1" ht="15.75">
       <c r="P780" s="61"/>
       <c r="Q780" s="61"/>
       <c r="S780" s="61"/>
       <c r="U780" s="62"/>
       <c r="V780" s="62"/>
     </row>
-    <row r="781" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:29" customHeight="1" ht="15.75">
       <c r="P781" s="61"/>
       <c r="Q781" s="61"/>
       <c r="S781" s="61"/>
       <c r="U781" s="62"/>
       <c r="V781" s="62"/>
     </row>
-    <row r="782" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:29" customHeight="1" ht="15.75">
       <c r="P782" s="61"/>
       <c r="Q782" s="61"/>
       <c r="S782" s="61"/>
       <c r="U782" s="62"/>
       <c r="V782" s="62"/>
     </row>
-    <row r="783" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:29" customHeight="1" ht="15.75">
       <c r="P783" s="61"/>
       <c r="Q783" s="61"/>
       <c r="S783" s="61"/>
       <c r="U783" s="62"/>
       <c r="V783" s="62"/>
     </row>
-    <row r="784" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:29" customHeight="1" ht="15.75">
       <c r="P784" s="61"/>
       <c r="Q784" s="61"/>
       <c r="S784" s="61"/>
       <c r="U784" s="62"/>
       <c r="V784" s="62"/>
     </row>
-    <row r="785" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:29" customHeight="1" ht="15.75">
       <c r="P785" s="61"/>
       <c r="Q785" s="61"/>
       <c r="S785" s="61"/>
       <c r="U785" s="62"/>
       <c r="V785" s="62"/>
     </row>
-    <row r="786" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:29" customHeight="1" ht="15.75">
       <c r="P786" s="61"/>
       <c r="Q786" s="61"/>
       <c r="S786" s="61"/>
       <c r="U786" s="62"/>
       <c r="V786" s="62"/>
     </row>
-    <row r="787" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:29" customHeight="1" ht="15.75">
       <c r="P787" s="61"/>
       <c r="Q787" s="61"/>
       <c r="S787" s="61"/>
       <c r="U787" s="62"/>
       <c r="V787" s="62"/>
     </row>
-    <row r="788" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:29" customHeight="1" ht="15.75">
       <c r="P788" s="61"/>
       <c r="Q788" s="61"/>
       <c r="S788" s="61"/>
       <c r="U788" s="62"/>
       <c r="V788" s="62"/>
     </row>
-    <row r="789" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:29" customHeight="1" ht="15.75">
       <c r="P789" s="61"/>
       <c r="Q789" s="61"/>
       <c r="S789" s="61"/>
       <c r="U789" s="62"/>
       <c r="V789" s="62"/>
     </row>
-    <row r="790" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:29" customHeight="1" ht="15.75">
       <c r="P790" s="61"/>
       <c r="Q790" s="61"/>
       <c r="S790" s="61"/>
       <c r="U790" s="62"/>
       <c r="V790" s="62"/>
     </row>
-    <row r="791" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:29" customHeight="1" ht="15.75">
       <c r="P791" s="61"/>
       <c r="Q791" s="61"/>
       <c r="S791" s="61"/>
       <c r="U791" s="62"/>
       <c r="V791" s="62"/>
     </row>
-    <row r="792" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:29" customHeight="1" ht="15.75">
       <c r="P792" s="61"/>
       <c r="Q792" s="61"/>
       <c r="S792" s="61"/>
       <c r="U792" s="62"/>
       <c r="V792" s="62"/>
     </row>
-    <row r="793" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:29" customHeight="1" ht="15.75">
       <c r="P793" s="61"/>
       <c r="Q793" s="61"/>
       <c r="S793" s="61"/>
       <c r="U793" s="62"/>
       <c r="V793" s="62"/>
     </row>
-    <row r="794" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:29" customHeight="1" ht="15.75">
       <c r="P794" s="61"/>
       <c r="Q794" s="61"/>
       <c r="S794" s="61"/>
       <c r="U794" s="62"/>
       <c r="V794" s="62"/>
     </row>
-    <row r="795" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:29" customHeight="1" ht="15.75">
       <c r="P795" s="61"/>
       <c r="Q795" s="61"/>
       <c r="S795" s="61"/>
       <c r="U795" s="62"/>
       <c r="V795" s="62"/>
     </row>
-    <row r="796" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:29" customHeight="1" ht="15.75">
       <c r="P796" s="61"/>
       <c r="Q796" s="61"/>
       <c r="S796" s="61"/>
       <c r="U796" s="62"/>
       <c r="V796" s="62"/>
     </row>
-    <row r="797" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:29" customHeight="1" ht="15.75">
       <c r="P797" s="61"/>
       <c r="Q797" s="61"/>
       <c r="S797" s="61"/>
       <c r="U797" s="62"/>
       <c r="V797" s="62"/>
     </row>
-    <row r="798" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:29" customHeight="1" ht="15.75">
       <c r="P798" s="61"/>
       <c r="Q798" s="61"/>
       <c r="S798" s="61"/>
       <c r="U798" s="62"/>
       <c r="V798" s="62"/>
     </row>
-    <row r="799" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:29" customHeight="1" ht="15.75">
       <c r="P799" s="61"/>
       <c r="Q799" s="61"/>
       <c r="S799" s="61"/>
       <c r="U799" s="62"/>
       <c r="V799" s="62"/>
     </row>
-    <row r="800" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:29" customHeight="1" ht="15.75">
       <c r="P800" s="61"/>
       <c r="Q800" s="61"/>
       <c r="S800" s="61"/>
       <c r="U800" s="62"/>
       <c r="V800" s="62"/>
     </row>
-    <row r="801" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:29" customHeight="1" ht="15.75">
       <c r="P801" s="61"/>
       <c r="Q801" s="61"/>
       <c r="S801" s="61"/>
       <c r="U801" s="62"/>
       <c r="V801" s="62"/>
     </row>
-    <row r="802" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:29" customHeight="1" ht="15.75">
       <c r="P802" s="61"/>
       <c r="Q802" s="61"/>
       <c r="S802" s="61"/>
       <c r="U802" s="62"/>
       <c r="V802" s="62"/>
     </row>
-    <row r="803" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:29" customHeight="1" ht="15.75">
       <c r="P803" s="61"/>
       <c r="Q803" s="61"/>
       <c r="S803" s="61"/>
       <c r="U803" s="62"/>
       <c r="V803" s="62"/>
     </row>
-    <row r="804" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:29" customHeight="1" ht="15.75">
       <c r="P804" s="61"/>
       <c r="Q804" s="61"/>
       <c r="S804" s="61"/>
       <c r="U804" s="62"/>
       <c r="V804" s="62"/>
     </row>
-    <row r="805" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:29" customHeight="1" ht="15.75">
       <c r="P805" s="61"/>
       <c r="Q805" s="61"/>
       <c r="S805" s="61"/>
       <c r="U805" s="62"/>
       <c r="V805" s="62"/>
     </row>
-    <row r="806" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:29" customHeight="1" ht="15.75">
       <c r="P806" s="61"/>
       <c r="Q806" s="61"/>
       <c r="S806" s="61"/>
       <c r="U806" s="62"/>
       <c r="V806" s="62"/>
     </row>
-    <row r="807" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:29" customHeight="1" ht="15.75">
       <c r="P807" s="61"/>
       <c r="Q807" s="61"/>
       <c r="S807" s="61"/>
       <c r="U807" s="62"/>
       <c r="V807" s="62"/>
     </row>
-    <row r="808" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:29" customHeight="1" ht="15.75">
       <c r="P808" s="61"/>
       <c r="Q808" s="61"/>
       <c r="S808" s="61"/>
       <c r="U808" s="62"/>
       <c r="V808" s="62"/>
     </row>
-    <row r="809" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:29" customHeight="1" ht="15.75">
       <c r="P809" s="61"/>
       <c r="Q809" s="61"/>
       <c r="S809" s="61"/>
       <c r="U809" s="62"/>
       <c r="V809" s="62"/>
     </row>
-    <row r="810" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:29" customHeight="1" ht="15.75">
       <c r="P810" s="61"/>
       <c r="Q810" s="61"/>
       <c r="S810" s="61"/>
       <c r="U810" s="62"/>
       <c r="V810" s="62"/>
     </row>
-    <row r="811" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:29" customHeight="1" ht="15.75">
       <c r="P811" s="61"/>
       <c r="Q811" s="61"/>
       <c r="S811" s="61"/>
       <c r="U811" s="62"/>
       <c r="V811" s="62"/>
     </row>
-    <row r="812" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:29" customHeight="1" ht="15.75">
       <c r="P812" s="61"/>
       <c r="Q812" s="61"/>
       <c r="S812" s="61"/>
       <c r="U812" s="62"/>
       <c r="V812" s="62"/>
     </row>
-    <row r="813" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:29" customHeight="1" ht="15.75">
       <c r="P813" s="61"/>
       <c r="Q813" s="61"/>
       <c r="S813" s="61"/>
       <c r="U813" s="62"/>
       <c r="V813" s="62"/>
     </row>
-    <row r="814" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:29" customHeight="1" ht="15.75">
       <c r="P814" s="61"/>
       <c r="Q814" s="61"/>
       <c r="S814" s="61"/>
       <c r="U814" s="62"/>
       <c r="V814" s="62"/>
     </row>
-    <row r="815" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:29" customHeight="1" ht="15.75">
       <c r="P815" s="61"/>
       <c r="Q815" s="61"/>
       <c r="S815" s="61"/>
       <c r="U815" s="62"/>
       <c r="V815" s="62"/>
     </row>
-    <row r="816" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:29" customHeight="1" ht="15.75">
       <c r="P816" s="61"/>
       <c r="Q816" s="61"/>
       <c r="S816" s="61"/>
       <c r="U816" s="62"/>
       <c r="V816" s="62"/>
     </row>
-    <row r="817" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:29" customHeight="1" ht="15.75">
       <c r="P817" s="61"/>
       <c r="Q817" s="61"/>
       <c r="S817" s="61"/>
       <c r="U817" s="62"/>
       <c r="V817" s="62"/>
     </row>
-    <row r="818" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:29" customHeight="1" ht="15.75">
       <c r="P818" s="61"/>
       <c r="Q818" s="61"/>
       <c r="S818" s="61"/>
       <c r="U818" s="62"/>
       <c r="V818" s="62"/>
     </row>
-    <row r="819" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:29" customHeight="1" ht="15.75">
       <c r="P819" s="61"/>
       <c r="Q819" s="61"/>
       <c r="S819" s="61"/>
       <c r="U819" s="62"/>
       <c r="V819" s="62"/>
     </row>
-    <row r="820" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:29" customHeight="1" ht="15.75">
       <c r="P820" s="61"/>
       <c r="Q820" s="61"/>
       <c r="S820" s="61"/>
       <c r="U820" s="62"/>
       <c r="V820" s="62"/>
     </row>
-    <row r="821" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:29" customHeight="1" ht="15.75">
       <c r="P821" s="61"/>
       <c r="Q821" s="61"/>
       <c r="S821" s="61"/>
       <c r="U821" s="62"/>
       <c r="V821" s="62"/>
     </row>
-    <row r="822" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:29" customHeight="1" ht="15.75">
       <c r="P822" s="61"/>
       <c r="Q822" s="61"/>
       <c r="S822" s="61"/>
       <c r="U822" s="62"/>
       <c r="V822" s="62"/>
     </row>
-    <row r="823" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:29" customHeight="1" ht="15.75">
       <c r="P823" s="61"/>
       <c r="Q823" s="61"/>
       <c r="S823" s="61"/>
       <c r="U823" s="62"/>
       <c r="V823" s="62"/>
     </row>
-    <row r="824" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:29" customHeight="1" ht="15.75">
       <c r="P824" s="61"/>
       <c r="Q824" s="61"/>
       <c r="S824" s="61"/>
       <c r="U824" s="62"/>
       <c r="V824" s="62"/>
     </row>
-    <row r="825" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:29" customHeight="1" ht="15.75">
       <c r="P825" s="61"/>
       <c r="Q825" s="61"/>
       <c r="S825" s="61"/>
       <c r="U825" s="62"/>
       <c r="V825" s="62"/>
     </row>
-    <row r="826" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:29" customHeight="1" ht="15.75">
       <c r="P826" s="61"/>
       <c r="Q826" s="61"/>
       <c r="S826" s="61"/>
       <c r="U826" s="62"/>
       <c r="V826" s="62"/>
     </row>
-    <row r="827" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:29" customHeight="1" ht="15.75">
       <c r="P827" s="61"/>
       <c r="Q827" s="61"/>
       <c r="S827" s="61"/>
       <c r="U827" s="62"/>
       <c r="V827" s="62"/>
     </row>
-    <row r="828" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:29" customHeight="1" ht="15.75">
       <c r="P828" s="61"/>
       <c r="Q828" s="61"/>
       <c r="S828" s="61"/>
       <c r="U828" s="62"/>
       <c r="V828" s="62"/>
     </row>
-    <row r="829" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:29" customHeight="1" ht="15.75">
       <c r="P829" s="61"/>
       <c r="Q829" s="61"/>
       <c r="S829" s="61"/>
       <c r="U829" s="62"/>
       <c r="V829" s="62"/>
     </row>
-    <row r="830" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:29" customHeight="1" ht="15.75">
       <c r="P830" s="61"/>
       <c r="Q830" s="61"/>
       <c r="S830" s="61"/>
       <c r="U830" s="62"/>
       <c r="V830" s="62"/>
     </row>
-    <row r="831" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:29" customHeight="1" ht="15.75">
       <c r="P831" s="61"/>
       <c r="Q831" s="61"/>
       <c r="S831" s="61"/>
       <c r="U831" s="62"/>
       <c r="V831" s="62"/>
     </row>
-    <row r="832" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:29" customHeight="1" ht="15.75">
       <c r="P832" s="61"/>
       <c r="Q832" s="61"/>
       <c r="S832" s="61"/>
       <c r="U832" s="62"/>
       <c r="V832" s="62"/>
     </row>
-    <row r="833" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:29" customHeight="1" ht="15.75">
       <c r="P833" s="61"/>
       <c r="Q833" s="61"/>
       <c r="S833" s="61"/>
       <c r="U833" s="62"/>
       <c r="V833" s="62"/>
     </row>
-    <row r="834" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:29" customHeight="1" ht="15.75">
       <c r="P834" s="61"/>
       <c r="Q834" s="61"/>
       <c r="S834" s="61"/>
       <c r="U834" s="62"/>
       <c r="V834" s="62"/>
     </row>
-    <row r="835" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:29" customHeight="1" ht="15.75">
       <c r="P835" s="61"/>
       <c r="Q835" s="61"/>
       <c r="S835" s="61"/>
       <c r="U835" s="62"/>
       <c r="V835" s="62"/>
     </row>
-    <row r="836" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:29" customHeight="1" ht="15.75">
       <c r="P836" s="61"/>
       <c r="Q836" s="61"/>
       <c r="S836" s="61"/>
       <c r="U836" s="62"/>
       <c r="V836" s="62"/>
     </row>
-    <row r="837" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:29" customHeight="1" ht="15.75">
       <c r="P837" s="61"/>
       <c r="Q837" s="61"/>
       <c r="S837" s="61"/>
       <c r="U837" s="62"/>
       <c r="V837" s="62"/>
     </row>
-    <row r="838" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:29" customHeight="1" ht="15.75">
       <c r="P838" s="61"/>
       <c r="Q838" s="61"/>
       <c r="S838" s="61"/>
       <c r="U838" s="62"/>
       <c r="V838" s="62"/>
     </row>
-    <row r="839" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:29" customHeight="1" ht="15.75">
       <c r="P839" s="61"/>
       <c r="Q839" s="61"/>
       <c r="S839" s="61"/>
       <c r="U839" s="62"/>
       <c r="V839" s="62"/>
     </row>
-    <row r="840" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:29" customHeight="1" ht="15.75">
       <c r="P840" s="61"/>
       <c r="Q840" s="61"/>
       <c r="S840" s="61"/>
       <c r="U840" s="62"/>
       <c r="V840" s="62"/>
     </row>
-    <row r="841" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:29" customHeight="1" ht="15.75">
       <c r="P841" s="61"/>
       <c r="Q841" s="61"/>
       <c r="S841" s="61"/>
       <c r="U841" s="62"/>
       <c r="V841" s="62"/>
     </row>
-    <row r="842" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:29" customHeight="1" ht="15.75">
       <c r="P842" s="61"/>
       <c r="Q842" s="61"/>
       <c r="S842" s="61"/>
       <c r="U842" s="62"/>
       <c r="V842" s="62"/>
     </row>
-    <row r="843" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:29" customHeight="1" ht="15.75">
       <c r="P843" s="61"/>
       <c r="Q843" s="61"/>
       <c r="S843" s="61"/>
       <c r="U843" s="62"/>
       <c r="V843" s="62"/>
     </row>
-    <row r="844" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:29" customHeight="1" ht="15.75">
       <c r="P844" s="61"/>
       <c r="Q844" s="61"/>
       <c r="S844" s="61"/>
       <c r="U844" s="62"/>
       <c r="V844" s="62"/>
     </row>
-    <row r="845" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:29" customHeight="1" ht="15.75">
       <c r="P845" s="61"/>
       <c r="Q845" s="61"/>
       <c r="S845" s="61"/>
       <c r="U845" s="62"/>
       <c r="V845" s="62"/>
     </row>
-    <row r="846" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:29" customHeight="1" ht="15.75">
       <c r="P846" s="61"/>
       <c r="Q846" s="61"/>
       <c r="S846" s="61"/>
       <c r="U846" s="62"/>
       <c r="V846" s="62"/>
     </row>
-    <row r="847" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:29" customHeight="1" ht="15.75">
       <c r="P847" s="61"/>
       <c r="Q847" s="61"/>
       <c r="S847" s="61"/>
       <c r="U847" s="62"/>
       <c r="V847" s="62"/>
     </row>
-    <row r="848" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:29" customHeight="1" ht="15.75">
       <c r="P848" s="61"/>
       <c r="Q848" s="61"/>
       <c r="S848" s="61"/>
       <c r="U848" s="62"/>
       <c r="V848" s="62"/>
     </row>
-    <row r="849" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:29" customHeight="1" ht="15.75">
       <c r="P849" s="61"/>
       <c r="Q849" s="61"/>
       <c r="S849" s="61"/>
       <c r="U849" s="62"/>
       <c r="V849" s="62"/>
     </row>
-    <row r="850" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:29" customHeight="1" ht="15.75">
       <c r="P850" s="61"/>
       <c r="Q850" s="61"/>
       <c r="S850" s="61"/>
       <c r="U850" s="62"/>
       <c r="V850" s="62"/>
     </row>
-    <row r="851" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:29" customHeight="1" ht="15.75">
       <c r="P851" s="61"/>
       <c r="Q851" s="61"/>
       <c r="S851" s="61"/>
       <c r="U851" s="62"/>
       <c r="V851" s="62"/>
     </row>
-    <row r="852" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:29" customHeight="1" ht="15.75">
       <c r="P852" s="61"/>
       <c r="Q852" s="61"/>
       <c r="S852" s="61"/>
       <c r="U852" s="62"/>
       <c r="V852" s="62"/>
     </row>
-    <row r="853" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:29" customHeight="1" ht="15.75">
       <c r="P853" s="61"/>
       <c r="Q853" s="61"/>
       <c r="S853" s="61"/>
       <c r="U853" s="62"/>
       <c r="V853" s="62"/>
     </row>
-    <row r="854" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:29" customHeight="1" ht="15.75">
       <c r="P854" s="61"/>
       <c r="Q854" s="61"/>
       <c r="S854" s="61"/>
       <c r="U854" s="62"/>
       <c r="V854" s="62"/>
     </row>
-    <row r="855" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:29" customHeight="1" ht="15.75">
       <c r="P855" s="61"/>
       <c r="Q855" s="61"/>
       <c r="S855" s="61"/>
       <c r="U855" s="62"/>
       <c r="V855" s="62"/>
     </row>
-    <row r="856" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:29" customHeight="1" ht="15.75">
       <c r="P856" s="61"/>
       <c r="Q856" s="61"/>
       <c r="S856" s="61"/>
       <c r="U856" s="62"/>
       <c r="V856" s="62"/>
     </row>
-    <row r="857" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:29" customHeight="1" ht="15.75">
       <c r="P857" s="61"/>
       <c r="Q857" s="61"/>
       <c r="S857" s="61"/>
       <c r="U857" s="62"/>
       <c r="V857" s="62"/>
     </row>
-    <row r="858" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:29" customHeight="1" ht="15.75">
       <c r="P858" s="61"/>
       <c r="Q858" s="61"/>
       <c r="S858" s="61"/>
       <c r="U858" s="62"/>
       <c r="V858" s="62"/>
     </row>
-    <row r="859" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:29" customHeight="1" ht="15.75">
       <c r="P859" s="61"/>
       <c r="Q859" s="61"/>
       <c r="S859" s="61"/>
       <c r="U859" s="62"/>
       <c r="V859" s="62"/>
     </row>
-    <row r="860" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:29" customHeight="1" ht="15.75">
       <c r="P860" s="61"/>
       <c r="Q860" s="61"/>
       <c r="S860" s="61"/>
       <c r="U860" s="62"/>
       <c r="V860" s="62"/>
     </row>
-    <row r="861" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:29" customHeight="1" ht="15.75">
       <c r="P861" s="61"/>
       <c r="Q861" s="61"/>
       <c r="S861" s="61"/>
       <c r="U861" s="62"/>
       <c r="V861" s="62"/>
     </row>
-    <row r="862" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:29" customHeight="1" ht="15.75">
       <c r="P862" s="61"/>
       <c r="Q862" s="61"/>
       <c r="S862" s="61"/>
       <c r="U862" s="62"/>
       <c r="V862" s="62"/>
     </row>
-    <row r="863" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:29" customHeight="1" ht="15.75">
       <c r="P863" s="61"/>
       <c r="Q863" s="61"/>
       <c r="S863" s="61"/>
       <c r="U863" s="62"/>
       <c r="V863" s="62"/>
     </row>
-    <row r="864" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:29" customHeight="1" ht="15.75">
       <c r="P864" s="61"/>
       <c r="Q864" s="61"/>
       <c r="S864" s="61"/>
       <c r="U864" s="62"/>
       <c r="V864" s="62"/>
     </row>
-    <row r="865" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:29" customHeight="1" ht="15.75">
       <c r="P865" s="61"/>
       <c r="Q865" s="61"/>
       <c r="S865" s="61"/>
       <c r="U865" s="62"/>
       <c r="V865" s="62"/>
     </row>
-    <row r="866" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:29" customHeight="1" ht="15.75">
       <c r="P866" s="61"/>
       <c r="Q866" s="61"/>
       <c r="S866" s="61"/>
       <c r="U866" s="62"/>
       <c r="V866" s="62"/>
     </row>
-    <row r="867" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:29" customHeight="1" ht="15.75">
       <c r="P867" s="61"/>
       <c r="Q867" s="61"/>
       <c r="S867" s="61"/>
       <c r="U867" s="62"/>
       <c r="V867" s="62"/>
     </row>
-    <row r="868" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:29" customHeight="1" ht="15.75">
       <c r="P868" s="61"/>
       <c r="Q868" s="61"/>
       <c r="S868" s="61"/>
       <c r="U868" s="62"/>
       <c r="V868" s="62"/>
     </row>
-    <row r="869" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:29" customHeight="1" ht="15.75">
       <c r="P869" s="61"/>
       <c r="Q869" s="61"/>
       <c r="S869" s="61"/>
       <c r="U869" s="62"/>
       <c r="V869" s="62"/>
     </row>
-    <row r="870" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:29" customHeight="1" ht="15.75">
       <c r="P870" s="61"/>
       <c r="Q870" s="61"/>
       <c r="S870" s="61"/>
       <c r="U870" s="62"/>
       <c r="V870" s="62"/>
     </row>
-    <row r="871" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:29" customHeight="1" ht="15.75">
       <c r="P871" s="61"/>
       <c r="Q871" s="61"/>
       <c r="S871" s="61"/>
       <c r="U871" s="62"/>
       <c r="V871" s="62"/>
     </row>
-    <row r="872" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:29" customHeight="1" ht="15.75">
       <c r="P872" s="61"/>
       <c r="Q872" s="61"/>
       <c r="S872" s="61"/>
       <c r="U872" s="62"/>
       <c r="V872" s="62"/>
     </row>
-    <row r="873" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:29" customHeight="1" ht="15.75">
       <c r="P873" s="61"/>
       <c r="Q873" s="61"/>
       <c r="S873" s="61"/>
       <c r="U873" s="62"/>
       <c r="V873" s="62"/>
     </row>
-    <row r="874" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:29" customHeight="1" ht="15.75">
       <c r="P874" s="61"/>
       <c r="Q874" s="61"/>
       <c r="S874" s="61"/>
       <c r="U874" s="62"/>
       <c r="V874" s="62"/>
     </row>
-    <row r="875" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:29" customHeight="1" ht="15.75">
       <c r="P875" s="61"/>
       <c r="Q875" s="61"/>
       <c r="S875" s="61"/>
       <c r="U875" s="62"/>
       <c r="V875" s="62"/>
     </row>
-    <row r="876" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:29" customHeight="1" ht="15.75">
       <c r="P876" s="61"/>
       <c r="Q876" s="61"/>
       <c r="S876" s="61"/>
       <c r="U876" s="62"/>
       <c r="V876" s="62"/>
     </row>
-    <row r="877" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:29" customHeight="1" ht="15.75">
       <c r="P877" s="61"/>
       <c r="Q877" s="61"/>
       <c r="S877" s="61"/>
       <c r="U877" s="62"/>
       <c r="V877" s="62"/>
     </row>
-    <row r="878" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:29" customHeight="1" ht="15.75">
       <c r="P878" s="61"/>
       <c r="Q878" s="61"/>
       <c r="S878" s="61"/>
       <c r="U878" s="62"/>
       <c r="V878" s="62"/>
     </row>
-    <row r="879" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:29" customHeight="1" ht="15.75">
       <c r="P879" s="61"/>
       <c r="Q879" s="61"/>
       <c r="S879" s="61"/>
       <c r="U879" s="62"/>
       <c r="V879" s="62"/>
     </row>
-    <row r="880" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:29" customHeight="1" ht="15.75">
       <c r="P880" s="61"/>
       <c r="Q880" s="61"/>
       <c r="S880" s="61"/>
       <c r="U880" s="62"/>
       <c r="V880" s="62"/>
     </row>
-    <row r="881" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:29" customHeight="1" ht="15.75">
       <c r="P881" s="61"/>
       <c r="Q881" s="61"/>
       <c r="S881" s="61"/>
       <c r="U881" s="62"/>
       <c r="V881" s="62"/>
     </row>
-    <row r="882" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:29" customHeight="1" ht="15.75">
       <c r="P882" s="61"/>
       <c r="Q882" s="61"/>
       <c r="S882" s="61"/>
       <c r="U882" s="62"/>
       <c r="V882" s="62"/>
     </row>
-    <row r="883" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:29" customHeight="1" ht="15.75">
       <c r="P883" s="61"/>
       <c r="Q883" s="61"/>
       <c r="S883" s="61"/>
       <c r="U883" s="62"/>
       <c r="V883" s="62"/>
     </row>
-    <row r="884" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:29" customHeight="1" ht="15.75">
       <c r="P884" s="61"/>
       <c r="Q884" s="61"/>
       <c r="S884" s="61"/>
       <c r="U884" s="62"/>
       <c r="V884" s="62"/>
     </row>
-    <row r="885" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:29" customHeight="1" ht="15.75">
       <c r="P885" s="61"/>
       <c r="Q885" s="61"/>
       <c r="S885" s="61"/>
       <c r="U885" s="62"/>
       <c r="V885" s="62"/>
     </row>
-    <row r="886" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:29" customHeight="1" ht="15.75">
       <c r="P886" s="61"/>
       <c r="Q886" s="61"/>
       <c r="S886" s="61"/>
       <c r="U886" s="62"/>
       <c r="V886" s="62"/>
     </row>
-    <row r="887" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:29" customHeight="1" ht="15.75">
       <c r="P887" s="61"/>
       <c r="Q887" s="61"/>
       <c r="S887" s="61"/>
       <c r="U887" s="62"/>
       <c r="V887" s="62"/>
     </row>
-    <row r="888" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:29" customHeight="1" ht="15.75">
       <c r="P888" s="61"/>
       <c r="Q888" s="61"/>
       <c r="S888" s="61"/>
       <c r="U888" s="62"/>
       <c r="V888" s="62"/>
     </row>
-    <row r="889" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:29" customHeight="1" ht="15.75">
       <c r="P889" s="61"/>
       <c r="Q889" s="61"/>
       <c r="S889" s="61"/>
       <c r="U889" s="62"/>
       <c r="V889" s="62"/>
     </row>
-    <row r="890" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:29" customHeight="1" ht="15.75">
       <c r="P890" s="61"/>
       <c r="Q890" s="61"/>
       <c r="S890" s="61"/>
       <c r="U890" s="62"/>
       <c r="V890" s="62"/>
     </row>
-    <row r="891" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:29" customHeight="1" ht="15.75">
       <c r="P891" s="61"/>
       <c r="Q891" s="61"/>
       <c r="S891" s="61"/>
       <c r="U891" s="62"/>
       <c r="V891" s="62"/>
     </row>
-    <row r="892" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:29" customHeight="1" ht="15.75">
       <c r="P892" s="61"/>
       <c r="Q892" s="61"/>
       <c r="S892" s="61"/>
       <c r="U892" s="62"/>
       <c r="V892" s="62"/>
     </row>
-    <row r="893" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:29" customHeight="1" ht="15.75">
       <c r="P893" s="61"/>
       <c r="Q893" s="61"/>
       <c r="S893" s="61"/>
       <c r="U893" s="62"/>
       <c r="V893" s="62"/>
     </row>
-    <row r="894" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:29" customHeight="1" ht="15.75">
       <c r="P894" s="61"/>
       <c r="Q894" s="61"/>
       <c r="S894" s="61"/>
       <c r="U894" s="62"/>
       <c r="V894" s="62"/>
     </row>
-    <row r="895" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:29" customHeight="1" ht="15.75">
       <c r="P895" s="61"/>
       <c r="Q895" s="61"/>
       <c r="S895" s="61"/>
       <c r="U895" s="62"/>
       <c r="V895" s="62"/>
     </row>
-    <row r="896" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:29" customHeight="1" ht="15.75">
       <c r="P896" s="61"/>
       <c r="Q896" s="61"/>
       <c r="S896" s="61"/>
       <c r="U896" s="62"/>
       <c r="V896" s="62"/>
     </row>
-    <row r="897" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:29" customHeight="1" ht="15.75">
       <c r="P897" s="61"/>
       <c r="Q897" s="61"/>
       <c r="S897" s="61"/>
       <c r="U897" s="62"/>
       <c r="V897" s="62"/>
     </row>
-    <row r="898" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:29" customHeight="1" ht="15.75">
       <c r="P898" s="61"/>
       <c r="Q898" s="61"/>
       <c r="S898" s="61"/>
       <c r="U898" s="62"/>
       <c r="V898" s="62"/>
     </row>
-    <row r="899" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:29" customHeight="1" ht="15.75">
       <c r="P899" s="61"/>
       <c r="Q899" s="61"/>
       <c r="S899" s="61"/>
       <c r="U899" s="62"/>
       <c r="V899" s="62"/>
     </row>
-    <row r="900" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:29" customHeight="1" ht="15.75">
       <c r="P900" s="61"/>
       <c r="Q900" s="61"/>
       <c r="S900" s="61"/>
       <c r="U900" s="62"/>
       <c r="V900" s="62"/>
     </row>
-    <row r="901" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:29" customHeight="1" ht="15.75">
       <c r="P901" s="61"/>
       <c r="Q901" s="61"/>
       <c r="S901" s="61"/>
       <c r="U901" s="62"/>
       <c r="V901" s="62"/>
     </row>
-    <row r="902" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:29" customHeight="1" ht="15.75">
       <c r="P902" s="61"/>
       <c r="Q902" s="61"/>
       <c r="S902" s="61"/>
       <c r="U902" s="62"/>
       <c r="V902" s="62"/>
     </row>
-    <row r="903" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:29" customHeight="1" ht="15.75">
       <c r="P903" s="61"/>
       <c r="Q903" s="61"/>
       <c r="S903" s="61"/>
       <c r="U903" s="62"/>
       <c r="V903" s="62"/>
     </row>
-    <row r="904" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:29" customHeight="1" ht="15.75">
       <c r="P904" s="61"/>
       <c r="Q904" s="61"/>
       <c r="S904" s="61"/>
       <c r="U904" s="62"/>
       <c r="V904" s="62"/>
     </row>
-    <row r="905" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:29" customHeight="1" ht="15.75">
       <c r="P905" s="61"/>
       <c r="Q905" s="61"/>
       <c r="S905" s="61"/>
       <c r="U905" s="62"/>
       <c r="V905" s="62"/>
     </row>
-    <row r="906" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:29" customHeight="1" ht="15.75">
       <c r="P906" s="61"/>
       <c r="Q906" s="61"/>
       <c r="S906" s="61"/>
       <c r="U906" s="62"/>
       <c r="V906" s="62"/>
     </row>
-    <row r="907" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:29" customHeight="1" ht="15.75">
       <c r="P907" s="61"/>
       <c r="Q907" s="61"/>
       <c r="S907" s="61"/>
       <c r="U907" s="62"/>
       <c r="V907" s="62"/>
     </row>
-    <row r="908" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:29" customHeight="1" ht="15.75">
       <c r="P908" s="61"/>
       <c r="Q908" s="61"/>
       <c r="S908" s="61"/>
       <c r="U908" s="62"/>
       <c r="V908" s="62"/>
     </row>
-    <row r="909" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:29" customHeight="1" ht="15.75">
       <c r="P909" s="61"/>
       <c r="Q909" s="61"/>
       <c r="S909" s="61"/>
       <c r="U909" s="62"/>
       <c r="V909" s="62"/>
     </row>
-    <row r="910" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:29" customHeight="1" ht="15.75">
       <c r="P910" s="61"/>
       <c r="Q910" s="61"/>
       <c r="S910" s="61"/>
       <c r="U910" s="62"/>
       <c r="V910" s="62"/>
     </row>
-    <row r="911" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:29" customHeight="1" ht="15.75">
       <c r="P911" s="61"/>
       <c r="Q911" s="61"/>
       <c r="S911" s="61"/>
       <c r="U911" s="62"/>
       <c r="V911" s="62"/>
     </row>
-    <row r="912" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:29" customHeight="1" ht="15.75">
       <c r="P912" s="61"/>
       <c r="Q912" s="61"/>
       <c r="S912" s="61"/>
       <c r="U912" s="62"/>
       <c r="V912" s="62"/>
     </row>
-    <row r="913" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:29" customHeight="1" ht="15.75">
       <c r="P913" s="61"/>
       <c r="Q913" s="61"/>
       <c r="S913" s="61"/>
       <c r="U913" s="62"/>
       <c r="V913" s="62"/>
     </row>
-    <row r="914" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:29" customHeight="1" ht="15.75">
       <c r="P914" s="61"/>
       <c r="Q914" s="61"/>
       <c r="S914" s="61"/>
       <c r="U914" s="62"/>
       <c r="V914" s="62"/>
     </row>
-    <row r="915" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:29" customHeight="1" ht="15.75">
       <c r="P915" s="61"/>
       <c r="Q915" s="61"/>
       <c r="S915" s="61"/>
       <c r="U915" s="62"/>
       <c r="V915" s="62"/>
     </row>
-    <row r="916" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:29" customHeight="1" ht="15.75">
       <c r="P916" s="61"/>
       <c r="Q916" s="61"/>
       <c r="S916" s="61"/>
       <c r="U916" s="62"/>
       <c r="V916" s="62"/>
     </row>
-    <row r="917" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:29" customHeight="1" ht="15.75">
       <c r="P917" s="61"/>
       <c r="Q917" s="61"/>
       <c r="S917" s="61"/>
       <c r="U917" s="62"/>
       <c r="V917" s="62"/>
     </row>
-    <row r="918" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:29" customHeight="1" ht="15.75">
       <c r="P918" s="61"/>
       <c r="Q918" s="61"/>
       <c r="S918" s="61"/>
       <c r="U918" s="62"/>
       <c r="V918" s="62"/>
     </row>
-    <row r="919" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:29" customHeight="1" ht="15.75">
       <c r="P919" s="61"/>
       <c r="Q919" s="61"/>
       <c r="S919" s="61"/>
       <c r="U919" s="62"/>
       <c r="V919" s="62"/>
     </row>
-    <row r="920" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:29" customHeight="1" ht="15.75">
       <c r="P920" s="61"/>
       <c r="Q920" s="61"/>
       <c r="S920" s="61"/>
       <c r="U920" s="62"/>
       <c r="V920" s="62"/>
     </row>
-    <row r="921" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:29" customHeight="1" ht="15.75">
       <c r="P921" s="61"/>
       <c r="Q921" s="61"/>
       <c r="S921" s="61"/>
       <c r="U921" s="62"/>
       <c r="V921" s="62"/>
     </row>
-    <row r="922" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:29" customHeight="1" ht="15.75">
       <c r="P922" s="61"/>
       <c r="Q922" s="61"/>
       <c r="S922" s="61"/>
       <c r="U922" s="62"/>
       <c r="V922" s="62"/>
     </row>
-    <row r="923" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:29" customHeight="1" ht="15.75">
       <c r="P923" s="61"/>
       <c r="Q923" s="61"/>
       <c r="S923" s="61"/>
       <c r="U923" s="62"/>
       <c r="V923" s="62"/>
     </row>
-    <row r="924" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:29" customHeight="1" ht="15.75">
       <c r="P924" s="61"/>
       <c r="Q924" s="61"/>
       <c r="S924" s="61"/>
       <c r="U924" s="62"/>
       <c r="V924" s="62"/>
     </row>
-    <row r="925" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:29" customHeight="1" ht="15.75">
       <c r="P925" s="61"/>
       <c r="Q925" s="61"/>
       <c r="S925" s="61"/>
       <c r="U925" s="62"/>
       <c r="V925" s="62"/>
     </row>
-    <row r="926" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:29" customHeight="1" ht="15.75">
       <c r="P926" s="61"/>
       <c r="Q926" s="61"/>
       <c r="S926" s="61"/>
       <c r="U926" s="62"/>
       <c r="V926" s="62"/>
     </row>
-    <row r="927" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:29" customHeight="1" ht="15.75">
       <c r="P927" s="61"/>
       <c r="Q927" s="61"/>
       <c r="S927" s="61"/>
       <c r="U927" s="62"/>
       <c r="V927" s="62"/>
     </row>
-    <row r="928" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:29" customHeight="1" ht="15.75">
       <c r="P928" s="61"/>
       <c r="Q928" s="61"/>
       <c r="S928" s="61"/>
       <c r="U928" s="62"/>
       <c r="V928" s="62"/>
     </row>
-    <row r="929" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:29" customHeight="1" ht="15.75">
       <c r="P929" s="61"/>
       <c r="Q929" s="61"/>
       <c r="S929" s="61"/>
       <c r="U929" s="62"/>
       <c r="V929" s="62"/>
     </row>
-    <row r="930" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:29" customHeight="1" ht="15.75">
       <c r="P930" s="61"/>
       <c r="Q930" s="61"/>
       <c r="S930" s="61"/>
       <c r="U930" s="62"/>
       <c r="V930" s="62"/>
     </row>
-    <row r="931" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:29" customHeight="1" ht="15.75">
       <c r="P931" s="61"/>
       <c r="Q931" s="61"/>
       <c r="S931" s="61"/>
       <c r="U931" s="62"/>
       <c r="V931" s="62"/>
     </row>
-    <row r="932" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:29" customHeight="1" ht="15.75">
       <c r="P932" s="61"/>
       <c r="Q932" s="61"/>
       <c r="S932" s="61"/>
       <c r="U932" s="62"/>
       <c r="V932" s="62"/>
     </row>
-    <row r="933" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:29" customHeight="1" ht="15.75">
       <c r="P933" s="61"/>
       <c r="Q933" s="61"/>
       <c r="S933" s="61"/>
       <c r="U933" s="62"/>
       <c r="V933" s="62"/>
     </row>
-    <row r="934" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:29" customHeight="1" ht="15.75">
       <c r="P934" s="61"/>
       <c r="Q934" s="61"/>
       <c r="S934" s="61"/>
       <c r="U934" s="62"/>
       <c r="V934" s="62"/>
     </row>
-    <row r="935" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:29" customHeight="1" ht="15.75">
       <c r="P935" s="61"/>
       <c r="Q935" s="61"/>
       <c r="S935" s="61"/>
       <c r="U935" s="62"/>
       <c r="V935" s="62"/>
     </row>
-    <row r="936" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:29" customHeight="1" ht="15.75">
       <c r="P936" s="61"/>
       <c r="Q936" s="61"/>
       <c r="S936" s="61"/>
       <c r="U936" s="62"/>
       <c r="V936" s="62"/>
     </row>
-    <row r="937" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:29" customHeight="1" ht="15.75">
       <c r="P937" s="61"/>
       <c r="Q937" s="61"/>
       <c r="S937" s="61"/>
       <c r="U937" s="62"/>
       <c r="V937" s="62"/>
     </row>
-    <row r="938" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:29" customHeight="1" ht="15.75">
       <c r="P938" s="61"/>
       <c r="Q938" s="61"/>
       <c r="S938" s="61"/>
       <c r="U938" s="62"/>
       <c r="V938" s="62"/>
     </row>
-    <row r="939" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:29" customHeight="1" ht="15.75">
       <c r="P939" s="61"/>
       <c r="Q939" s="61"/>
       <c r="S939" s="61"/>
       <c r="U939" s="62"/>
       <c r="V939" s="62"/>
     </row>
-    <row r="940" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:29" customHeight="1" ht="15.75">
       <c r="P940" s="61"/>
       <c r="Q940" s="61"/>
       <c r="S940" s="61"/>
       <c r="U940" s="62"/>
       <c r="V940" s="62"/>
     </row>
-    <row r="941" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:29" customHeight="1" ht="15.75">
       <c r="P941" s="61"/>
       <c r="Q941" s="61"/>
       <c r="S941" s="61"/>
       <c r="U941" s="62"/>
       <c r="V941" s="62"/>
     </row>
-    <row r="942" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:29" customHeight="1" ht="15.75">
       <c r="P942" s="61"/>
       <c r="Q942" s="61"/>
       <c r="S942" s="61"/>
       <c r="U942" s="62"/>
       <c r="V942" s="62"/>
     </row>
-    <row r="943" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:29" customHeight="1" ht="15.75">
       <c r="P943" s="61"/>
       <c r="Q943" s="61"/>
       <c r="S943" s="61"/>
       <c r="U943" s="62"/>
       <c r="V943" s="62"/>
     </row>
-    <row r="944" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:29" customHeight="1" ht="15.75">
       <c r="P944" s="61"/>
       <c r="Q944" s="61"/>
       <c r="S944" s="61"/>
       <c r="U944" s="62"/>
       <c r="V944" s="62"/>
     </row>
-    <row r="945" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:29" customHeight="1" ht="15.75">
       <c r="P945" s="61"/>
       <c r="Q945" s="61"/>
       <c r="S945" s="61"/>
       <c r="U945" s="62"/>
       <c r="V945" s="62"/>
     </row>
-    <row r="946" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:29" customHeight="1" ht="15.75">
       <c r="P946" s="61"/>
       <c r="Q946" s="61"/>
       <c r="S946" s="61"/>
       <c r="U946" s="62"/>
       <c r="V946" s="62"/>
     </row>
-    <row r="947" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:29" customHeight="1" ht="15.75">
       <c r="P947" s="61"/>
       <c r="Q947" s="61"/>
       <c r="S947" s="61"/>
       <c r="U947" s="62"/>
       <c r="V947" s="62"/>
     </row>
-    <row r="948" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:29" customHeight="1" ht="15.75">
       <c r="P948" s="61"/>
       <c r="Q948" s="61"/>
       <c r="S948" s="61"/>
       <c r="U948" s="62"/>
       <c r="V948" s="62"/>
     </row>
-    <row r="949" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:29" customHeight="1" ht="15.75">
       <c r="P949" s="61"/>
       <c r="Q949" s="61"/>
       <c r="S949" s="61"/>
       <c r="U949" s="62"/>
       <c r="V949" s="62"/>
     </row>
-    <row r="950" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:29" customHeight="1" ht="15.75">
       <c r="P950" s="61"/>
       <c r="Q950" s="61"/>
       <c r="S950" s="61"/>
       <c r="U950" s="62"/>
       <c r="V950" s="62"/>
     </row>
-    <row r="951" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:29" customHeight="1" ht="15.75">
       <c r="P951" s="61"/>
       <c r="Q951" s="61"/>
       <c r="S951" s="61"/>
       <c r="U951" s="62"/>
       <c r="V951" s="62"/>
     </row>
-    <row r="952" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:29" customHeight="1" ht="15.75">
       <c r="P952" s="61"/>
       <c r="Q952" s="61"/>
       <c r="S952" s="61"/>
       <c r="U952" s="62"/>
       <c r="V952" s="62"/>
     </row>
-    <row r="953" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:29" customHeight="1" ht="15.75">
       <c r="P953" s="61"/>
       <c r="Q953" s="61"/>
       <c r="S953" s="61"/>
       <c r="U953" s="62"/>
       <c r="V953" s="62"/>
     </row>
-    <row r="954" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:29" customHeight="1" ht="15.75">
       <c r="P954" s="61"/>
       <c r="Q954" s="61"/>
       <c r="S954" s="61"/>
       <c r="U954" s="62"/>
       <c r="V954" s="62"/>
     </row>
-    <row r="955" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:29" customHeight="1" ht="15.75">
       <c r="P955" s="61"/>
       <c r="Q955" s="61"/>
       <c r="S955" s="61"/>
       <c r="U955" s="62"/>
       <c r="V955" s="62"/>
     </row>
-    <row r="956" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:29" customHeight="1" ht="15.75">
       <c r="P956" s="61"/>
       <c r="Q956" s="61"/>
       <c r="S956" s="61"/>
       <c r="U956" s="62"/>
       <c r="V956" s="62"/>
     </row>
-    <row r="957" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:29" customHeight="1" ht="15.75">
       <c r="P957" s="61"/>
       <c r="Q957" s="61"/>
       <c r="S957" s="61"/>
       <c r="U957" s="62"/>
       <c r="V957" s="62"/>
     </row>
-    <row r="958" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:29" customHeight="1" ht="15.75">
       <c r="P958" s="61"/>
       <c r="Q958" s="61"/>
       <c r="S958" s="61"/>
       <c r="U958" s="62"/>
       <c r="V958" s="62"/>
     </row>
-    <row r="959" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:29" customHeight="1" ht="15.75">
       <c r="P959" s="61"/>
       <c r="Q959" s="61"/>
       <c r="S959" s="61"/>
       <c r="U959" s="62"/>
       <c r="V959" s="62"/>
     </row>
-    <row r="960" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:29" customHeight="1" ht="15.75">
       <c r="P960" s="61"/>
       <c r="Q960" s="61"/>
       <c r="S960" s="61"/>
       <c r="U960" s="62"/>
       <c r="V960" s="62"/>
     </row>
-    <row r="961" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:29" customHeight="1" ht="15.75">
       <c r="P961" s="61"/>
       <c r="Q961" s="61"/>
       <c r="S961" s="61"/>
       <c r="U961" s="62"/>
       <c r="V961" s="62"/>
     </row>
-    <row r="962" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:29" customHeight="1" ht="15.75">
       <c r="P962" s="61"/>
       <c r="Q962" s="61"/>
       <c r="S962" s="61"/>
       <c r="U962" s="62"/>
       <c r="V962" s="62"/>
     </row>
-    <row r="963" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:29" customHeight="1" ht="15.75">
       <c r="P963" s="61"/>
       <c r="Q963" s="61"/>
       <c r="S963" s="61"/>
       <c r="U963" s="62"/>
       <c r="V963" s="62"/>
     </row>
-    <row r="964" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:29" customHeight="1" ht="15.75">
       <c r="P964" s="61"/>
       <c r="Q964" s="61"/>
       <c r="S964" s="61"/>
       <c r="U964" s="62"/>
       <c r="V964" s="62"/>
     </row>
-    <row r="965" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:29" customHeight="1" ht="15.75">
       <c r="P965" s="61"/>
       <c r="Q965" s="61"/>
       <c r="S965" s="61"/>
       <c r="U965" s="62"/>
       <c r="V965" s="62"/>
     </row>
-    <row r="966" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:29" customHeight="1" ht="15.75">
       <c r="P966" s="61"/>
       <c r="Q966" s="61"/>
       <c r="S966" s="61"/>
       <c r="U966" s="62"/>
       <c r="V966" s="62"/>
     </row>
-    <row r="967" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:29" customHeight="1" ht="15.75">
       <c r="P967" s="61"/>
       <c r="Q967" s="61"/>
       <c r="S967" s="61"/>
       <c r="U967" s="62"/>
       <c r="V967" s="62"/>
     </row>
-    <row r="968" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:29" customHeight="1" ht="15.75">
       <c r="P968" s="61"/>
       <c r="Q968" s="61"/>
       <c r="S968" s="61"/>
       <c r="U968" s="62"/>
       <c r="V968" s="62"/>
     </row>
-    <row r="969" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:29" customHeight="1" ht="15.75">
       <c r="P969" s="61"/>
       <c r="Q969" s="61"/>
       <c r="S969" s="61"/>
       <c r="U969" s="62"/>
       <c r="V969" s="62"/>
     </row>
-    <row r="970" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:29" customHeight="1" ht="15.75">
       <c r="P970" s="61"/>
       <c r="Q970" s="61"/>
       <c r="S970" s="61"/>
       <c r="U970" s="62"/>
       <c r="V970" s="62"/>
     </row>
-    <row r="971" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:29" customHeight="1" ht="15.75">
       <c r="P971" s="61"/>
       <c r="Q971" s="61"/>
       <c r="S971" s="61"/>
       <c r="U971" s="62"/>
       <c r="V971" s="62"/>
     </row>
-    <row r="972" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:29" customHeight="1" ht="15.75">
       <c r="P972" s="61"/>
       <c r="Q972" s="61"/>
       <c r="S972" s="61"/>
       <c r="U972" s="62"/>
       <c r="V972" s="62"/>
     </row>
-    <row r="973" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:29" customHeight="1" ht="15.75">
       <c r="P973" s="61"/>
       <c r="Q973" s="61"/>
       <c r="S973" s="61"/>
       <c r="U973" s="62"/>
       <c r="V973" s="62"/>
     </row>
-    <row r="974" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:29" customHeight="1" ht="15.75">
       <c r="P974" s="61"/>
       <c r="Q974" s="61"/>
       <c r="S974" s="61"/>
       <c r="U974" s="62"/>
       <c r="V974" s="62"/>
     </row>
-    <row r="975" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:29" customHeight="1" ht="15.75">
       <c r="P975" s="61"/>
       <c r="Q975" s="61"/>
       <c r="S975" s="61"/>
       <c r="U975" s="62"/>
       <c r="V975" s="62"/>
     </row>
-    <row r="976" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:29" customHeight="1" ht="15.75">
       <c r="P976" s="61"/>
       <c r="Q976" s="61"/>
       <c r="S976" s="61"/>
       <c r="U976" s="62"/>
       <c r="V976" s="62"/>
     </row>
-    <row r="977" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:29" customHeight="1" ht="15.75">
       <c r="P977" s="61"/>
       <c r="Q977" s="61"/>
       <c r="S977" s="61"/>
       <c r="U977" s="62"/>
       <c r="V977" s="62"/>
     </row>
-    <row r="978" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:29" customHeight="1" ht="15.75">
       <c r="P978" s="61"/>
       <c r="Q978" s="61"/>
       <c r="S978" s="61"/>
       <c r="U978" s="62"/>
       <c r="V978" s="62"/>
     </row>
-    <row r="979" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:29" customHeight="1" ht="15.75">
       <c r="P979" s="61"/>
       <c r="Q979" s="61"/>
       <c r="S979" s="61"/>
       <c r="U979" s="62"/>
       <c r="V979" s="62"/>
     </row>
-    <row r="980" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:29" customHeight="1" ht="15.75">
       <c r="P980" s="61"/>
       <c r="Q980" s="61"/>
       <c r="S980" s="61"/>
       <c r="U980" s="62"/>
       <c r="V980" s="62"/>
     </row>
-    <row r="981" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:29" customHeight="1" ht="15.75">
       <c r="P981" s="61"/>
       <c r="Q981" s="61"/>
       <c r="S981" s="61"/>
       <c r="U981" s="62"/>
       <c r="V981" s="62"/>
     </row>
-    <row r="982" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:29" customHeight="1" ht="15.75">
       <c r="P982" s="61"/>
       <c r="Q982" s="61"/>
       <c r="S982" s="61"/>
       <c r="U982" s="62"/>
       <c r="V982" s="62"/>
     </row>
-    <row r="983" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:29" customHeight="1" ht="15.75">
       <c r="P983" s="61"/>
       <c r="Q983" s="61"/>
       <c r="S983" s="61"/>
       <c r="U983" s="62"/>
       <c r="V983" s="62"/>
     </row>
-    <row r="984" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:29" customHeight="1" ht="15.75">
       <c r="P984" s="61"/>
       <c r="Q984" s="61"/>
       <c r="S984" s="61"/>
       <c r="U984" s="62"/>
       <c r="V984" s="62"/>
     </row>
-    <row r="985" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:29" customHeight="1" ht="15.75">
       <c r="P985" s="61"/>
       <c r="Q985" s="61"/>
       <c r="S985" s="61"/>
       <c r="U985" s="62"/>
       <c r="V985" s="62"/>
     </row>
-    <row r="986" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:29" customHeight="1" ht="15.75">
       <c r="P986" s="61"/>
       <c r="Q986" s="61"/>
       <c r="S986" s="61"/>
       <c r="U986" s="62"/>
       <c r="V986" s="62"/>
     </row>
-    <row r="987" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:29" customHeight="1" ht="15.75">
       <c r="P987" s="61"/>
       <c r="Q987" s="61"/>
       <c r="S987" s="61"/>
       <c r="U987" s="62"/>
       <c r="V987" s="62"/>
     </row>
-    <row r="988" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:29" customHeight="1" ht="15.75">
       <c r="P988" s="61"/>
       <c r="Q988" s="61"/>
       <c r="S988" s="61"/>
       <c r="U988" s="62"/>
       <c r="V988" s="62"/>
     </row>
-    <row r="989" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:29" customHeight="1" ht="15.75">
       <c r="P989" s="61"/>
       <c r="Q989" s="61"/>
       <c r="S989" s="61"/>
       <c r="U989" s="62"/>
       <c r="V989" s="62"/>
     </row>
-    <row r="990" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:29" customHeight="1" ht="15.75">
       <c r="P990" s="61"/>
       <c r="Q990" s="61"/>
       <c r="S990" s="61"/>
       <c r="U990" s="62"/>
       <c r="V990" s="62"/>
     </row>
-    <row r="991" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:29" customHeight="1" ht="15.75">
       <c r="P991" s="61"/>
       <c r="Q991" s="61"/>
       <c r="S991" s="61"/>
       <c r="U991" s="62"/>
       <c r="V991" s="62"/>
     </row>
-    <row r="992" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:29" customHeight="1" ht="15.75">
       <c r="P992" s="61"/>
       <c r="Q992" s="61"/>
       <c r="S992" s="61"/>
       <c r="U992" s="62"/>
       <c r="V992" s="62"/>
     </row>
-    <row r="993" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:29" customHeight="1" ht="15.75">
       <c r="P993" s="61"/>
       <c r="Q993" s="61"/>
       <c r="S993" s="61"/>
       <c r="U993" s="62"/>
       <c r="V993" s="62"/>
     </row>
-    <row r="994" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:29" customHeight="1" ht="15.75">
       <c r="P994" s="61"/>
       <c r="Q994" s="61"/>
       <c r="S994" s="61"/>
       <c r="U994" s="62"/>
       <c r="V994" s="62"/>
     </row>
-    <row r="995" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:29" customHeight="1" ht="15.75">
       <c r="P995" s="61"/>
       <c r="Q995" s="61"/>
       <c r="S995" s="61"/>
       <c r="U995" s="62"/>
       <c r="V995" s="62"/>
     </row>
-    <row r="996" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:29" customHeight="1" ht="15.75">
       <c r="P996" s="61"/>
       <c r="Q996" s="61"/>
       <c r="S996" s="61"/>
       <c r="U996" s="62"/>
       <c r="V996" s="62"/>
     </row>
-    <row r="997" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:29" customHeight="1" ht="15.75">
       <c r="P997" s="61"/>
       <c r="Q997" s="61"/>
       <c r="S997" s="61"/>
       <c r="U997" s="62"/>
       <c r="V997" s="62"/>
     </row>
-    <row r="998" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:29" customHeight="1" ht="15.75">
       <c r="P998" s="61"/>
       <c r="Q998" s="61"/>
       <c r="S998" s="61"/>
       <c r="U998" s="62"/>
       <c r="V998" s="62"/>
     </row>
-    <row r="999" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:29" customHeight="1" ht="15.75">
       <c r="P999" s="61"/>
       <c r="Q999" s="61"/>
       <c r="S999" s="61"/>
       <c r="U999" s="62"/>
       <c r="V999" s="62"/>
     </row>
-    <row r="1000" spans="16:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:29" customHeight="1" ht="15.75">
       <c r="P1000" s="61"/>
       <c r="Q1000" s="61"/>
       <c r="S1000" s="61"/>
@@ -13692,8 +13578,8 @@
       <c r="V1000" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:AC103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="6">
+  <autoFilter ref="A8:AC103"/>
+  <mergeCells>
     <mergeCell ref="B2:C6"/>
     <mergeCell ref="D2:R4"/>
     <mergeCell ref="S2:W2"/>
@@ -13702,21 +13588,21 @@
     <mergeCell ref="S5:W6"/>
   </mergeCells>
   <conditionalFormatting sqref="T8 T9:X103">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"PROGRAMAR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:X1 T9:X1000">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"VENCIDO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"VIGENTE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="7.8740157480315001E-2" right="7.8740157480315001E-2" top="0.118110236220472" bottom="0.118110236220472" header="0" footer="0"/>
-  <pageSetup scale="56" pageOrder="overThenDown" orientation="landscape" r:id="rId1"/>
+  <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
+  <pageMargins left="0.078740157480315" right="0.078740157480315" top="0.11811023622047" bottom="0.11811023622047" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape" scale="56" fitToHeight="1" fitToWidth="1" pageOrder="overThenDown" r:id="rId1ps"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>